--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60bd3766fe3b56c0/Nova pasta/Nova pasta/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C66AA5-2F67-4010-B837-35B29476A991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEED880-5822-4A30-B3FE-E0773491E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +111,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;R$&quot;\ #,##0.00;\-&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="mmmm\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -144,7 +144,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -246,7 +246,7 @@
             <v>109</v>
           </cell>
           <cell r="BL93">
-            <v>54</v>
+            <v>61</v>
           </cell>
         </row>
         <row r="94">
@@ -290,7 +290,7 @@
             <v>108</v>
           </cell>
           <cell r="BL94">
-            <v>68</v>
+            <v>88</v>
           </cell>
         </row>
         <row r="95">
@@ -334,7 +334,7 @@
             <v>277</v>
           </cell>
           <cell r="BL95">
-            <v>116</v>
+            <v>177</v>
           </cell>
         </row>
         <row r="96">
@@ -378,7 +378,7 @@
             <v>5</v>
           </cell>
           <cell r="BL96">
-            <v>4</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="97">
@@ -422,7 +422,7 @@
             <v>40</v>
           </cell>
           <cell r="BL97">
-            <v>28</v>
+            <v>32</v>
           </cell>
         </row>
         <row r="98">
@@ -466,7 +466,7 @@
             <v>78</v>
           </cell>
           <cell r="BL98">
-            <v>57</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="99">
@@ -554,7 +554,7 @@
             <v>892</v>
           </cell>
           <cell r="BL100">
-            <v>547</v>
+            <v>726</v>
           </cell>
         </row>
         <row r="101">
@@ -598,7 +598,7 @@
             <v>425</v>
           </cell>
           <cell r="BL101">
-            <v>390</v>
+            <v>508</v>
           </cell>
         </row>
         <row r="102">
@@ -642,7 +642,7 @@
             <v>775</v>
           </cell>
           <cell r="BL102">
-            <v>420</v>
+            <v>543</v>
           </cell>
         </row>
         <row r="103">
@@ -903,7 +903,7 @@
             <v>0</v>
           </cell>
           <cell r="BL120">
-            <v>1047.4000000000001</v>
+            <v>1041.4000000000001</v>
           </cell>
         </row>
         <row r="121">
@@ -953,7 +953,7 @@
             <v>523.79</v>
           </cell>
           <cell r="BL121">
-            <v>173.1</v>
+            <v>397.25</v>
           </cell>
         </row>
         <row r="122">
@@ -1003,7 +1003,7 @@
             <v>599.47</v>
           </cell>
           <cell r="BL122">
-            <v>537.89</v>
+            <v>530.91</v>
           </cell>
         </row>
         <row r="123">
@@ -1103,7 +1103,7 @@
             <v>51.99</v>
           </cell>
           <cell r="BL124">
-            <v>41.3</v>
+            <v>37.4</v>
           </cell>
         </row>
         <row r="125">
@@ -1303,7 +1303,7 @@
             <v>1664.01</v>
           </cell>
           <cell r="BL128">
-            <v>217</v>
+            <v>4848</v>
           </cell>
         </row>
         <row r="129">
@@ -1353,7 +1353,7 @@
             <v>1644.31</v>
           </cell>
           <cell r="BL129">
-            <v>2027.17</v>
+            <v>2100.16</v>
           </cell>
         </row>
         <row r="130">
@@ -1503,7 +1503,7 @@
             <v>508.18</v>
           </cell>
           <cell r="BL132">
-            <v>66.7</v>
+            <v>66.400000000000006</v>
           </cell>
         </row>
         <row r="133">
@@ -1553,7 +1553,7 @@
             <v>548.19000000000005</v>
           </cell>
           <cell r="BL133">
-            <v>114.6</v>
+            <v>737.05</v>
           </cell>
         </row>
         <row r="134">
@@ -2053,7 +2053,7 @@
             <v>0</v>
           </cell>
           <cell r="BL145">
-            <v>163</v>
+            <v>959.3</v>
           </cell>
         </row>
         <row r="146">
@@ -2103,7 +2103,7 @@
             <v>423.9</v>
           </cell>
           <cell r="BL146">
-            <v>579.05999999999995</v>
+            <v>619.61</v>
           </cell>
         </row>
         <row r="147">
@@ -2153,7 +2153,7 @@
             <v>6771.6</v>
           </cell>
           <cell r="BL147">
-            <v>907.53</v>
+            <v>994.28</v>
           </cell>
         </row>
         <row r="148">
@@ -2203,7 +2203,7 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>441.39</v>
+            <v>507.14</v>
           </cell>
         </row>
         <row r="149">
@@ -2253,7 +2253,7 @@
             <v>392.52</v>
           </cell>
           <cell r="BL149">
-            <v>49.3</v>
+            <v>65.3</v>
           </cell>
         </row>
         <row r="150">
@@ -2353,7 +2353,7 @@
             <v>475.55</v>
           </cell>
           <cell r="BL151">
-            <v>29.94</v>
+            <v>51.64</v>
           </cell>
         </row>
         <row r="152">
@@ -2453,7 +2453,7 @@
             <v>6968.14</v>
           </cell>
           <cell r="BL153">
-            <v>731.48</v>
+            <v>743.18</v>
           </cell>
         </row>
         <row r="154">
@@ -2503,7 +2503,7 @@
             <v>351.6</v>
           </cell>
           <cell r="BL154">
-            <v>936.84</v>
+            <v>964.24</v>
           </cell>
         </row>
         <row r="155">
@@ -2553,7 +2553,7 @@
             <v>275.2</v>
           </cell>
           <cell r="BL155">
-            <v>281.3</v>
+            <v>334.8</v>
           </cell>
         </row>
         <row r="156">
@@ -2653,7 +2653,7 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>492.81</v>
+            <v>632.67999999999995</v>
           </cell>
         </row>
         <row r="158">
@@ -2703,7 +2703,7 @@
             <v>87.73</v>
           </cell>
           <cell r="BL158">
-            <v>245.3</v>
+            <v>246.3</v>
           </cell>
         </row>
         <row r="159">
@@ -3053,7 +3053,7 @@
             <v>1528.85</v>
           </cell>
           <cell r="BL167">
-            <v>1238.8</v>
+            <v>1436.72</v>
           </cell>
         </row>
         <row r="168">
@@ -3203,7 +3203,7 @@
             <v>806.7</v>
           </cell>
           <cell r="BL170">
-            <v>579.29999999999995</v>
+            <v>699.1</v>
           </cell>
         </row>
         <row r="171">
@@ -3253,7 +3253,7 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>331.3</v>
+            <v>923.53</v>
           </cell>
         </row>
         <row r="172">
@@ -3303,7 +3303,7 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>850.52</v>
+            <v>1279.26</v>
           </cell>
         </row>
         <row r="173">
@@ -3353,7 +3353,7 @@
             <v>5782.77</v>
           </cell>
           <cell r="BL173">
-            <v>882.29</v>
+            <v>1377.73</v>
           </cell>
         </row>
         <row r="174">
@@ -3403,7 +3403,7 @@
             <v>360.6</v>
           </cell>
           <cell r="BL174">
-            <v>117.8</v>
+            <v>159.35</v>
           </cell>
         </row>
         <row r="175">
@@ -3503,7 +3503,7 @@
             <v>276.93</v>
           </cell>
           <cell r="BL176">
-            <v>150.47999999999999</v>
+            <v>215.83</v>
           </cell>
         </row>
         <row r="177">
@@ -3603,7 +3603,7 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>2479.83</v>
+            <v>4924.63</v>
           </cell>
         </row>
         <row r="179">
@@ -3653,7 +3653,7 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>664.76</v>
+            <v>2211.31</v>
           </cell>
         </row>
         <row r="180">
@@ -3703,7 +3703,7 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>552.47</v>
+            <v>586.82000000000005</v>
           </cell>
         </row>
         <row r="181">
@@ -3803,7 +3803,7 @@
             <v>2160.71</v>
           </cell>
           <cell r="BL182">
-            <v>1177.83</v>
+            <v>2155.6799999999998</v>
           </cell>
         </row>
         <row r="183">
@@ -3853,7 +3853,7 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>2421.7399999999998</v>
+            <v>2663.63</v>
           </cell>
         </row>
         <row r="184">
@@ -4453,7 +4453,7 @@
             <v>32.49</v>
           </cell>
           <cell r="BL197">
-            <v>0.01</v>
+            <v>78.959999999999994</v>
           </cell>
         </row>
         <row r="198">
@@ -4653,7 +4653,7 @@
             <v>0</v>
           </cell>
           <cell r="BL201">
-            <v>0</v>
+            <v>5.56</v>
           </cell>
         </row>
         <row r="202">
@@ -4803,7 +4803,7 @@
             <v>64.069999999999993</v>
           </cell>
           <cell r="BL204">
-            <v>0</v>
+            <v>4.96</v>
           </cell>
         </row>
         <row r="205">
@@ -5553,7 +5553,7 @@
             <v>203.03</v>
           </cell>
           <cell r="BL221">
-            <v>17.89</v>
+            <v>21.49</v>
           </cell>
         </row>
         <row r="222">
@@ -5653,7 +5653,7 @@
             <v>788.08</v>
           </cell>
           <cell r="BL223">
-            <v>241.87</v>
+            <v>262.37</v>
           </cell>
         </row>
         <row r="224">
@@ -5953,7 +5953,7 @@
             <v>128.09</v>
           </cell>
           <cell r="BL229">
-            <v>466.05</v>
+            <v>460.75</v>
           </cell>
         </row>
         <row r="230">
@@ -6103,7 +6103,7 @@
             <v>347.7</v>
           </cell>
           <cell r="BL232">
-            <v>193.03</v>
+            <v>236.83</v>
           </cell>
         </row>
         <row r="233">
@@ -6703,7 +6703,7 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>436.87</v>
+            <v>493.17</v>
           </cell>
         </row>
         <row r="247">
@@ -6753,7 +6753,7 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>304.58999999999997</v>
+            <v>354.19</v>
           </cell>
         </row>
         <row r="248">
@@ -6803,7 +6803,7 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>563.29999999999995</v>
+            <v>597.6</v>
           </cell>
         </row>
         <row r="249">
@@ -7053,7 +7053,7 @@
             <v>1212.5</v>
           </cell>
           <cell r="BL253">
-            <v>129.5</v>
+            <v>299.39999999999998</v>
           </cell>
         </row>
         <row r="254">
@@ -7103,7 +7103,7 @@
             <v>1217.27</v>
           </cell>
           <cell r="BL254">
-            <v>199.18</v>
+            <v>213.08</v>
           </cell>
         </row>
         <row r="255">
@@ -7253,7 +7253,7 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>470.95</v>
+            <v>482.65</v>
           </cell>
         </row>
         <row r="258">
@@ -7303,7 +7303,7 @@
             <v>282.8</v>
           </cell>
           <cell r="BL258">
-            <v>313.75</v>
+            <v>585.54999999999995</v>
           </cell>
         </row>
         <row r="259">
@@ -8803,7 +8803,7 @@
             <v>10911.5</v>
           </cell>
           <cell r="BL292">
-            <v>7867.21</v>
+            <v>21505.040000000001</v>
           </cell>
         </row>
         <row r="293">
@@ -8953,7 +8953,7 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>4716.7</v>
+            <v>5286.1</v>
           </cell>
         </row>
         <row r="296">
@@ -9003,7 +9003,7 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>5330.29</v>
+            <v>9589.81</v>
           </cell>
         </row>
         <row r="297">
@@ -9053,7 +9053,7 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>8063.34</v>
+            <v>9748.14</v>
           </cell>
         </row>
         <row r="298">
@@ -9103,7 +9103,7 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>10665.79</v>
+            <v>15233.71</v>
           </cell>
         </row>
         <row r="299">
@@ -9153,7 +9153,7 @@
             <v>819.93</v>
           </cell>
           <cell r="BL299">
-            <v>649.42999999999995</v>
+            <v>1123.31</v>
           </cell>
         </row>
         <row r="300">
@@ -9253,7 +9253,7 @@
             <v>1498.34</v>
           </cell>
           <cell r="BL301">
-            <v>1403.55</v>
+            <v>2654.75</v>
           </cell>
         </row>
         <row r="302">
@@ -9303,7 +9303,7 @@
             <v>2807.35</v>
           </cell>
           <cell r="BL302">
-            <v>1867.65</v>
+            <v>3277.5</v>
           </cell>
         </row>
         <row r="303">
@@ -9353,7 +9353,7 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>80514.02</v>
+            <v>104267.16</v>
           </cell>
         </row>
         <row r="304">
@@ -9403,7 +9403,7 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>6680.78</v>
+            <v>9025.65</v>
           </cell>
         </row>
         <row r="305">
@@ -9453,7 +9453,7 @@
             <v>3782.99</v>
           </cell>
           <cell r="BL305">
-            <v>728.05</v>
+            <v>738.95</v>
           </cell>
         </row>
         <row r="306">
@@ -9503,7 +9503,7 @@
             <v>2317.5500000000002</v>
           </cell>
           <cell r="BL306">
-            <v>290</v>
+            <v>433</v>
           </cell>
         </row>
         <row r="307">
@@ -9553,7 +9553,7 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>3988.82</v>
+            <v>5317.21</v>
           </cell>
         </row>
         <row r="308">
@@ -9603,7 +9603,7 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>16613.75</v>
+            <v>29440.46</v>
           </cell>
         </row>
         <row r="309">
@@ -9953,7 +9953,7 @@
             <v>5408.2</v>
           </cell>
           <cell r="BL317">
-            <v>1786.26</v>
+            <v>6111.44</v>
           </cell>
         </row>
         <row r="318">
@@ -10103,7 +10103,7 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>5449.8</v>
+            <v>6599.3</v>
           </cell>
         </row>
         <row r="321">
@@ -10153,7 +10153,7 @@
             <v>2748.05</v>
           </cell>
           <cell r="BL321">
-            <v>3777.22</v>
+            <v>4311.3900000000003</v>
           </cell>
         </row>
         <row r="322">
@@ -10203,7 +10203,7 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>2263.23</v>
+            <v>3322.26</v>
           </cell>
         </row>
         <row r="323">
@@ -10253,7 +10253,7 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>9542.5</v>
+            <v>11467.41</v>
           </cell>
         </row>
         <row r="324">
@@ -10303,7 +10303,7 @@
             <v>630.75</v>
           </cell>
           <cell r="BL324">
-            <v>306.55</v>
+            <v>334.6</v>
           </cell>
         </row>
         <row r="325">
@@ -10403,7 +10403,7 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>2485.46</v>
+            <v>3023.3</v>
           </cell>
         </row>
         <row r="327">
@@ -10453,7 +10453,7 @@
             <v>3384.9</v>
           </cell>
           <cell r="BL327">
-            <v>581.79999999999995</v>
+            <v>933.45</v>
           </cell>
         </row>
         <row r="328">
@@ -10503,7 +10503,7 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>21101.45</v>
+            <v>27058.66</v>
           </cell>
         </row>
         <row r="329">
@@ -10553,7 +10553,7 @@
             <v>4790.9799999999996</v>
           </cell>
           <cell r="BL329">
-            <v>4777.58</v>
+            <v>5364.02</v>
           </cell>
         </row>
         <row r="330">
@@ -10603,7 +10603,7 @@
             <v>2022.35</v>
           </cell>
           <cell r="BL330">
-            <v>1928.74</v>
+            <v>2293.94</v>
           </cell>
         </row>
         <row r="331">
@@ -10703,7 +10703,7 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>2746.48</v>
+            <v>3385.8</v>
           </cell>
         </row>
         <row r="333">
@@ -10753,7 +10753,7 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>7410.16</v>
+            <v>9179.16</v>
           </cell>
         </row>
         <row r="334">
@@ -11103,7 +11103,7 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>2730.14</v>
+            <v>3672.38</v>
           </cell>
         </row>
         <row r="343">
@@ -11253,7 +11253,7 @@
             <v>1706.35</v>
           </cell>
           <cell r="BL345">
-            <v>3425.04</v>
+            <v>4098.6400000000003</v>
           </cell>
         </row>
         <row r="346">
@@ -11303,7 +11303,7 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>2342.2600000000002</v>
+            <v>3043.23</v>
           </cell>
         </row>
         <row r="347">
@@ -11353,7 +11353,7 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>9462.0300000000007</v>
+            <v>10696.59</v>
           </cell>
         </row>
         <row r="348">
@@ -11403,7 +11403,7 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>8491.7800000000007</v>
+            <v>9913.24</v>
           </cell>
         </row>
         <row r="349">
@@ -11453,7 +11453,7 @@
             <v>1478.26</v>
           </cell>
           <cell r="BL349">
-            <v>557.72</v>
+            <v>685.42</v>
           </cell>
         </row>
         <row r="350">
@@ -11553,7 +11553,7 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>740.1</v>
+            <v>1029.7</v>
           </cell>
         </row>
         <row r="352">
@@ -11653,7 +11653,7 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>19624.55</v>
+            <v>25009.18</v>
           </cell>
         </row>
         <row r="354">
@@ -11703,7 +11703,7 @@
             <v>6679.21</v>
           </cell>
           <cell r="BL354">
-            <v>5071.66</v>
+            <v>5383.88</v>
           </cell>
         </row>
         <row r="355">
@@ -11753,7 +11753,7 @@
             <v>3019.73</v>
           </cell>
           <cell r="BL355">
-            <v>1557.26</v>
+            <v>1681.76</v>
           </cell>
         </row>
         <row r="356">
@@ -11853,7 +11853,7 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>2570.84</v>
+            <v>4047.07</v>
           </cell>
         </row>
         <row r="358">
@@ -11903,7 +11903,7 @@
             <v>18146.46</v>
           </cell>
           <cell r="BL358">
-            <v>13052.18</v>
+            <v>21315.65</v>
           </cell>
         </row>
         <row r="359">
@@ -13059,7 +13059,7 @@
         <v>109</v>
       </c>
       <c r="P4">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -13247,7 +13247,7 @@
         <v>108</v>
       </c>
       <c r="P5">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -13435,7 +13435,7 @@
         <v>277</v>
       </c>
       <c r="P6">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -13811,7 +13811,7 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -13999,7 +13999,7 @@
         <v>78</v>
       </c>
       <c r="P9">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -14375,7 +14375,7 @@
         <v>892</v>
       </c>
       <c r="P11">
-        <v>547</v>
+        <v>726</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -14563,7 +14563,7 @@
         <v>425</v>
       </c>
       <c r="P12">
-        <v>390</v>
+        <v>508</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>775</v>
       </c>
       <c r="P13">
-        <v>420</v>
+        <v>543</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1047.4000000000001</v>
+        <v>1041.4000000000001</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -15522,7 +15522,7 @@
         <v>523.79</v>
       </c>
       <c r="P23">
-        <v>173.1</v>
+        <v>397.25</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -15599,7 +15599,7 @@
         <v>599.47</v>
       </c>
       <c r="P24">
-        <v>537.89</v>
+        <v>530.91</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>51.99</v>
       </c>
       <c r="P26">
-        <v>41.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         <v>1664.01</v>
       </c>
       <c r="P30">
-        <v>217</v>
+        <v>4848</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -16138,7 +16138,7 @@
         <v>1644.31</v>
       </c>
       <c r="P31">
-        <v>2027.17</v>
+        <v>2100.16</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -16369,7 +16369,7 @@
         <v>508.18</v>
       </c>
       <c r="P34">
-        <v>66.7</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         <v>548.19000000000005</v>
       </c>
       <c r="P35">
-        <v>114.6</v>
+        <v>737.05</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -17370,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>163</v>
+        <v>959.3</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         <v>423.9</v>
       </c>
       <c r="P48">
-        <v>579.05999999999995</v>
+        <v>619.61</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -17524,7 +17524,7 @@
         <v>6771.6</v>
       </c>
       <c r="P49">
-        <v>907.53</v>
+        <v>994.28</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -17601,7 +17601,7 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>441.39</v>
+        <v>507.14</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -17678,7 +17678,7 @@
         <v>392.52</v>
       </c>
       <c r="P51">
-        <v>49.3</v>
+        <v>65.3</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -17832,7 +17832,7 @@
         <v>475.55</v>
       </c>
       <c r="P53">
-        <v>29.94</v>
+        <v>51.64</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>6968.14</v>
       </c>
       <c r="P55">
-        <v>731.48</v>
+        <v>743.18</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -18063,7 +18063,7 @@
         <v>351.6</v>
       </c>
       <c r="P56">
-        <v>936.84</v>
+        <v>964.24</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -18140,7 +18140,7 @@
         <v>275.2</v>
       </c>
       <c r="P57">
-        <v>281.3</v>
+        <v>334.8</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -18294,7 +18294,7 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>492.81</v>
+        <v>632.67999999999995</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -18371,7 +18371,7 @@
         <v>87.73</v>
       </c>
       <c r="P60">
-        <v>245.3</v>
+        <v>246.3</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -19064,7 +19064,7 @@
         <v>1528.85</v>
       </c>
       <c r="P69">
-        <v>1238.8</v>
+        <v>1436.72</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -19295,7 +19295,7 @@
         <v>806.7</v>
       </c>
       <c r="P72">
-        <v>579.29999999999995</v>
+        <v>699.1</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -19372,7 +19372,7 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>331.3</v>
+        <v>923.53</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -19449,7 +19449,7 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>850.52</v>
+        <v>1279.26</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -19526,7 +19526,7 @@
         <v>5782.77</v>
       </c>
       <c r="P75">
-        <v>882.29</v>
+        <v>1377.73</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -19603,7 +19603,7 @@
         <v>360.6</v>
       </c>
       <c r="P76">
-        <v>117.8</v>
+        <v>159.35</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -19757,7 +19757,7 @@
         <v>276.93</v>
       </c>
       <c r="P78">
-        <v>150.47999999999999</v>
+        <v>215.83</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -19911,7 +19911,7 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>2479.83</v>
+        <v>4924.63</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -19988,7 +19988,7 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>664.76</v>
+        <v>2211.31</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -20065,7 +20065,7 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>552.47</v>
+        <v>586.82000000000005</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -20219,7 +20219,7 @@
         <v>2160.71</v>
       </c>
       <c r="P84">
-        <v>1177.83</v>
+        <v>2155.6799999999998</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -20296,7 +20296,7 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>2421.7399999999998</v>
+        <v>2663.63</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -21374,7 +21374,7 @@
         <v>32.49</v>
       </c>
       <c r="P99">
-        <v>0.01</v>
+        <v>78.959999999999994</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -21682,7 +21682,7 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -21913,7 +21913,7 @@
         <v>64.069999999999993</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -23222,7 +23222,7 @@
         <v>203.03</v>
       </c>
       <c r="P123">
-        <v>17.89</v>
+        <v>21.49</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>788.08</v>
       </c>
       <c r="P125">
-        <v>241.87</v>
+        <v>262.37</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -23838,7 +23838,7 @@
         <v>128.09</v>
       </c>
       <c r="P131">
-        <v>466.05</v>
+        <v>460.75</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -24069,7 +24069,7 @@
         <v>347.7</v>
       </c>
       <c r="P134">
-        <v>193.03</v>
+        <v>236.83</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -25147,7 +25147,7 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>436.87</v>
+        <v>493.17</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -25224,7 +25224,7 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>304.58999999999997</v>
+        <v>354.19</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -25301,7 +25301,7 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>563.29999999999995</v>
+        <v>597.6</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>1212.5</v>
       </c>
       <c r="P155">
-        <v>129.5</v>
+        <v>299.39999999999998</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>1217.27</v>
       </c>
       <c r="P156">
-        <v>199.18</v>
+        <v>213.08</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25994,7 +25994,7 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>470.95</v>
+        <v>482.65</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26071,7 +26071,7 @@
         <v>282.8</v>
       </c>
       <c r="P160">
-        <v>313.75</v>
+        <v>585.54999999999995</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -28689,7 +28689,7 @@
         <v>10911.5</v>
       </c>
       <c r="P194">
-        <v>7867.21</v>
+        <v>21505.040000000001</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -28920,7 +28920,7 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>4716.7</v>
+        <v>5286.1</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -28997,7 +28997,7 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>5330.29</v>
+        <v>9589.81</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -29074,7 +29074,7 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>8063.34</v>
+        <v>9748.14</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -29151,7 +29151,7 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>10665.79</v>
+        <v>15233.71</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -29228,7 +29228,7 @@
         <v>819.93</v>
       </c>
       <c r="P201">
-        <v>649.42999999999995</v>
+        <v>1123.31</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -29382,7 +29382,7 @@
         <v>1498.34</v>
       </c>
       <c r="P203">
-        <v>1403.55</v>
+        <v>2654.75</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -29459,7 +29459,7 @@
         <v>2807.35</v>
       </c>
       <c r="P204">
-        <v>1867.65</v>
+        <v>3277.5</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -29536,7 +29536,7 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>80514.02</v>
+        <v>104267.16</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -29613,7 +29613,7 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>6680.78</v>
+        <v>9025.65</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>3782.99</v>
       </c>
       <c r="P207">
-        <v>728.05</v>
+        <v>738.95</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -29767,7 +29767,7 @@
         <v>2317.5500000000002</v>
       </c>
       <c r="P208">
-        <v>290</v>
+        <v>433</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -29844,7 +29844,7 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>3988.82</v>
+        <v>5317.21</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -29921,7 +29921,7 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>16613.75</v>
+        <v>29440.46</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -30614,7 +30614,7 @@
         <v>5408.2</v>
       </c>
       <c r="P219">
-        <v>1786.26</v>
+        <v>6111.44</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -30845,7 +30845,7 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>5449.8</v>
+        <v>6599.3</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -30922,7 +30922,7 @@
         <v>2748.05</v>
       </c>
       <c r="P223">
-        <v>3777.22</v>
+        <v>4311.3900000000003</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -30999,7 +30999,7 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>2263.23</v>
+        <v>3322.26</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -31076,7 +31076,7 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>9542.5</v>
+        <v>11467.41</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -31153,7 +31153,7 @@
         <v>630.75</v>
       </c>
       <c r="P226">
-        <v>306.55</v>
+        <v>334.6</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -31307,7 +31307,7 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>2485.46</v>
+        <v>3023.3</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -31384,7 +31384,7 @@
         <v>3384.9</v>
       </c>
       <c r="P229">
-        <v>581.79999999999995</v>
+        <v>933.45</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -31461,7 +31461,7 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>21101.45</v>
+        <v>27058.66</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -31538,7 +31538,7 @@
         <v>4790.9799999999996</v>
       </c>
       <c r="P231">
-        <v>4777.58</v>
+        <v>5364.02</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -31615,7 +31615,7 @@
         <v>2022.35</v>
       </c>
       <c r="P232">
-        <v>1928.74</v>
+        <v>2293.94</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -31769,7 +31769,7 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>2746.48</v>
+        <v>3385.8</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -31846,7 +31846,7 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>7410.16</v>
+        <v>9179.16</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -32539,7 +32539,7 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>2730.14</v>
+        <v>3672.38</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -32770,7 +32770,7 @@
         <v>1706.35</v>
       </c>
       <c r="P247">
-        <v>3425.04</v>
+        <v>4098.6400000000003</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -32847,7 +32847,7 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>2342.2600000000002</v>
+        <v>3043.23</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -32924,7 +32924,7 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>9462.0300000000007</v>
+        <v>10696.59</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>8491.7800000000007</v>
+        <v>9913.24</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -33078,7 +33078,7 @@
         <v>1478.26</v>
       </c>
       <c r="P251">
-        <v>557.72</v>
+        <v>685.42</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -33232,7 +33232,7 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>740.1</v>
+        <v>1029.7</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -33386,7 +33386,7 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>19624.55</v>
+        <v>25009.18</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -33463,7 +33463,7 @@
         <v>6679.21</v>
       </c>
       <c r="P256">
-        <v>5071.66</v>
+        <v>5383.88</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -33540,7 +33540,7 @@
         <v>3019.73</v>
       </c>
       <c r="P257">
-        <v>1557.26</v>
+        <v>1681.76</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -33694,7 +33694,7 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>2570.84</v>
+        <v>4047.07</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -33771,7 +33771,7 @@
         <v>18146.46</v>
       </c>
       <c r="P260">
-        <v>13052.18</v>
+        <v>21315.65</v>
       </c>
       <c r="Q260">
         <v>0</v>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60bd3766fe3b56c0/Nova pasta/Nova pasta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEED880-5822-4A30-B3FE-E0773491E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C66AA5-2F67-4010-B837-35B29476A991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +111,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;R$&quot;\ #,##0.00;\-&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="164" formatCode="mmmm\,\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -144,7 +144,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -246,7 +246,7 @@
             <v>109</v>
           </cell>
           <cell r="BL93">
-            <v>61</v>
+            <v>54</v>
           </cell>
         </row>
         <row r="94">
@@ -290,7 +290,7 @@
             <v>108</v>
           </cell>
           <cell r="BL94">
-            <v>88</v>
+            <v>68</v>
           </cell>
         </row>
         <row r="95">
@@ -334,7 +334,7 @@
             <v>277</v>
           </cell>
           <cell r="BL95">
-            <v>177</v>
+            <v>116</v>
           </cell>
         </row>
         <row r="96">
@@ -378,7 +378,7 @@
             <v>5</v>
           </cell>
           <cell r="BL96">
-            <v>6</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="97">
@@ -422,7 +422,7 @@
             <v>40</v>
           </cell>
           <cell r="BL97">
-            <v>32</v>
+            <v>28</v>
           </cell>
         </row>
         <row r="98">
@@ -466,7 +466,7 @@
             <v>78</v>
           </cell>
           <cell r="BL98">
-            <v>70</v>
+            <v>57</v>
           </cell>
         </row>
         <row r="99">
@@ -554,7 +554,7 @@
             <v>892</v>
           </cell>
           <cell r="BL100">
-            <v>726</v>
+            <v>547</v>
           </cell>
         </row>
         <row r="101">
@@ -598,7 +598,7 @@
             <v>425</v>
           </cell>
           <cell r="BL101">
-            <v>508</v>
+            <v>390</v>
           </cell>
         </row>
         <row r="102">
@@ -642,7 +642,7 @@
             <v>775</v>
           </cell>
           <cell r="BL102">
-            <v>543</v>
+            <v>420</v>
           </cell>
         </row>
         <row r="103">
@@ -903,7 +903,7 @@
             <v>0</v>
           </cell>
           <cell r="BL120">
-            <v>1041.4000000000001</v>
+            <v>1047.4000000000001</v>
           </cell>
         </row>
         <row r="121">
@@ -953,7 +953,7 @@
             <v>523.79</v>
           </cell>
           <cell r="BL121">
-            <v>397.25</v>
+            <v>173.1</v>
           </cell>
         </row>
         <row r="122">
@@ -1003,7 +1003,7 @@
             <v>599.47</v>
           </cell>
           <cell r="BL122">
-            <v>530.91</v>
+            <v>537.89</v>
           </cell>
         </row>
         <row r="123">
@@ -1103,7 +1103,7 @@
             <v>51.99</v>
           </cell>
           <cell r="BL124">
-            <v>37.4</v>
+            <v>41.3</v>
           </cell>
         </row>
         <row r="125">
@@ -1303,7 +1303,7 @@
             <v>1664.01</v>
           </cell>
           <cell r="BL128">
-            <v>4848</v>
+            <v>217</v>
           </cell>
         </row>
         <row r="129">
@@ -1353,7 +1353,7 @@
             <v>1644.31</v>
           </cell>
           <cell r="BL129">
-            <v>2100.16</v>
+            <v>2027.17</v>
           </cell>
         </row>
         <row r="130">
@@ -1503,7 +1503,7 @@
             <v>508.18</v>
           </cell>
           <cell r="BL132">
-            <v>66.400000000000006</v>
+            <v>66.7</v>
           </cell>
         </row>
         <row r="133">
@@ -1553,7 +1553,7 @@
             <v>548.19000000000005</v>
           </cell>
           <cell r="BL133">
-            <v>737.05</v>
+            <v>114.6</v>
           </cell>
         </row>
         <row r="134">
@@ -2053,7 +2053,7 @@
             <v>0</v>
           </cell>
           <cell r="BL145">
-            <v>959.3</v>
+            <v>163</v>
           </cell>
         </row>
         <row r="146">
@@ -2103,7 +2103,7 @@
             <v>423.9</v>
           </cell>
           <cell r="BL146">
-            <v>619.61</v>
+            <v>579.05999999999995</v>
           </cell>
         </row>
         <row r="147">
@@ -2153,7 +2153,7 @@
             <v>6771.6</v>
           </cell>
           <cell r="BL147">
-            <v>994.28</v>
+            <v>907.53</v>
           </cell>
         </row>
         <row r="148">
@@ -2203,7 +2203,7 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>507.14</v>
+            <v>441.39</v>
           </cell>
         </row>
         <row r="149">
@@ -2253,7 +2253,7 @@
             <v>392.52</v>
           </cell>
           <cell r="BL149">
-            <v>65.3</v>
+            <v>49.3</v>
           </cell>
         </row>
         <row r="150">
@@ -2353,7 +2353,7 @@
             <v>475.55</v>
           </cell>
           <cell r="BL151">
-            <v>51.64</v>
+            <v>29.94</v>
           </cell>
         </row>
         <row r="152">
@@ -2453,7 +2453,7 @@
             <v>6968.14</v>
           </cell>
           <cell r="BL153">
-            <v>743.18</v>
+            <v>731.48</v>
           </cell>
         </row>
         <row r="154">
@@ -2503,7 +2503,7 @@
             <v>351.6</v>
           </cell>
           <cell r="BL154">
-            <v>964.24</v>
+            <v>936.84</v>
           </cell>
         </row>
         <row r="155">
@@ -2553,7 +2553,7 @@
             <v>275.2</v>
           </cell>
           <cell r="BL155">
-            <v>334.8</v>
+            <v>281.3</v>
           </cell>
         </row>
         <row r="156">
@@ -2653,7 +2653,7 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>632.67999999999995</v>
+            <v>492.81</v>
           </cell>
         </row>
         <row r="158">
@@ -2703,7 +2703,7 @@
             <v>87.73</v>
           </cell>
           <cell r="BL158">
-            <v>246.3</v>
+            <v>245.3</v>
           </cell>
         </row>
         <row r="159">
@@ -3053,7 +3053,7 @@
             <v>1528.85</v>
           </cell>
           <cell r="BL167">
-            <v>1436.72</v>
+            <v>1238.8</v>
           </cell>
         </row>
         <row r="168">
@@ -3203,7 +3203,7 @@
             <v>806.7</v>
           </cell>
           <cell r="BL170">
-            <v>699.1</v>
+            <v>579.29999999999995</v>
           </cell>
         </row>
         <row r="171">
@@ -3253,7 +3253,7 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>923.53</v>
+            <v>331.3</v>
           </cell>
         </row>
         <row r="172">
@@ -3303,7 +3303,7 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>1279.26</v>
+            <v>850.52</v>
           </cell>
         </row>
         <row r="173">
@@ -3353,7 +3353,7 @@
             <v>5782.77</v>
           </cell>
           <cell r="BL173">
-            <v>1377.73</v>
+            <v>882.29</v>
           </cell>
         </row>
         <row r="174">
@@ -3403,7 +3403,7 @@
             <v>360.6</v>
           </cell>
           <cell r="BL174">
-            <v>159.35</v>
+            <v>117.8</v>
           </cell>
         </row>
         <row r="175">
@@ -3503,7 +3503,7 @@
             <v>276.93</v>
           </cell>
           <cell r="BL176">
-            <v>215.83</v>
+            <v>150.47999999999999</v>
           </cell>
         </row>
         <row r="177">
@@ -3603,7 +3603,7 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>4924.63</v>
+            <v>2479.83</v>
           </cell>
         </row>
         <row r="179">
@@ -3653,7 +3653,7 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>2211.31</v>
+            <v>664.76</v>
           </cell>
         </row>
         <row r="180">
@@ -3703,7 +3703,7 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>586.82000000000005</v>
+            <v>552.47</v>
           </cell>
         </row>
         <row r="181">
@@ -3803,7 +3803,7 @@
             <v>2160.71</v>
           </cell>
           <cell r="BL182">
-            <v>2155.6799999999998</v>
+            <v>1177.83</v>
           </cell>
         </row>
         <row r="183">
@@ -3853,7 +3853,7 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>2663.63</v>
+            <v>2421.7399999999998</v>
           </cell>
         </row>
         <row r="184">
@@ -4453,7 +4453,7 @@
             <v>32.49</v>
           </cell>
           <cell r="BL197">
-            <v>78.959999999999994</v>
+            <v>0.01</v>
           </cell>
         </row>
         <row r="198">
@@ -4653,7 +4653,7 @@
             <v>0</v>
           </cell>
           <cell r="BL201">
-            <v>5.56</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="202">
@@ -4803,7 +4803,7 @@
             <v>64.069999999999993</v>
           </cell>
           <cell r="BL204">
-            <v>4.96</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="205">
@@ -5553,7 +5553,7 @@
             <v>203.03</v>
           </cell>
           <cell r="BL221">
-            <v>21.49</v>
+            <v>17.89</v>
           </cell>
         </row>
         <row r="222">
@@ -5653,7 +5653,7 @@
             <v>788.08</v>
           </cell>
           <cell r="BL223">
-            <v>262.37</v>
+            <v>241.87</v>
           </cell>
         </row>
         <row r="224">
@@ -5953,7 +5953,7 @@
             <v>128.09</v>
           </cell>
           <cell r="BL229">
-            <v>460.75</v>
+            <v>466.05</v>
           </cell>
         </row>
         <row r="230">
@@ -6103,7 +6103,7 @@
             <v>347.7</v>
           </cell>
           <cell r="BL232">
-            <v>236.83</v>
+            <v>193.03</v>
           </cell>
         </row>
         <row r="233">
@@ -6703,7 +6703,7 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>493.17</v>
+            <v>436.87</v>
           </cell>
         </row>
         <row r="247">
@@ -6753,7 +6753,7 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>354.19</v>
+            <v>304.58999999999997</v>
           </cell>
         </row>
         <row r="248">
@@ -6803,7 +6803,7 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>597.6</v>
+            <v>563.29999999999995</v>
           </cell>
         </row>
         <row r="249">
@@ -7053,7 +7053,7 @@
             <v>1212.5</v>
           </cell>
           <cell r="BL253">
-            <v>299.39999999999998</v>
+            <v>129.5</v>
           </cell>
         </row>
         <row r="254">
@@ -7103,7 +7103,7 @@
             <v>1217.27</v>
           </cell>
           <cell r="BL254">
-            <v>213.08</v>
+            <v>199.18</v>
           </cell>
         </row>
         <row r="255">
@@ -7253,7 +7253,7 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>482.65</v>
+            <v>470.95</v>
           </cell>
         </row>
         <row r="258">
@@ -7303,7 +7303,7 @@
             <v>282.8</v>
           </cell>
           <cell r="BL258">
-            <v>585.54999999999995</v>
+            <v>313.75</v>
           </cell>
         </row>
         <row r="259">
@@ -8803,7 +8803,7 @@
             <v>10911.5</v>
           </cell>
           <cell r="BL292">
-            <v>21505.040000000001</v>
+            <v>7867.21</v>
           </cell>
         </row>
         <row r="293">
@@ -8953,7 +8953,7 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>5286.1</v>
+            <v>4716.7</v>
           </cell>
         </row>
         <row r="296">
@@ -9003,7 +9003,7 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>9589.81</v>
+            <v>5330.29</v>
           </cell>
         </row>
         <row r="297">
@@ -9053,7 +9053,7 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>9748.14</v>
+            <v>8063.34</v>
           </cell>
         </row>
         <row r="298">
@@ -9103,7 +9103,7 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>15233.71</v>
+            <v>10665.79</v>
           </cell>
         </row>
         <row r="299">
@@ -9153,7 +9153,7 @@
             <v>819.93</v>
           </cell>
           <cell r="BL299">
-            <v>1123.31</v>
+            <v>649.42999999999995</v>
           </cell>
         </row>
         <row r="300">
@@ -9253,7 +9253,7 @@
             <v>1498.34</v>
           </cell>
           <cell r="BL301">
-            <v>2654.75</v>
+            <v>1403.55</v>
           </cell>
         </row>
         <row r="302">
@@ -9303,7 +9303,7 @@
             <v>2807.35</v>
           </cell>
           <cell r="BL302">
-            <v>3277.5</v>
+            <v>1867.65</v>
           </cell>
         </row>
         <row r="303">
@@ -9353,7 +9353,7 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>104267.16</v>
+            <v>80514.02</v>
           </cell>
         </row>
         <row r="304">
@@ -9403,7 +9403,7 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>9025.65</v>
+            <v>6680.78</v>
           </cell>
         </row>
         <row r="305">
@@ -9453,7 +9453,7 @@
             <v>3782.99</v>
           </cell>
           <cell r="BL305">
-            <v>738.95</v>
+            <v>728.05</v>
           </cell>
         </row>
         <row r="306">
@@ -9503,7 +9503,7 @@
             <v>2317.5500000000002</v>
           </cell>
           <cell r="BL306">
-            <v>433</v>
+            <v>290</v>
           </cell>
         </row>
         <row r="307">
@@ -9553,7 +9553,7 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>5317.21</v>
+            <v>3988.82</v>
           </cell>
         </row>
         <row r="308">
@@ -9603,7 +9603,7 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>29440.46</v>
+            <v>16613.75</v>
           </cell>
         </row>
         <row r="309">
@@ -9953,7 +9953,7 @@
             <v>5408.2</v>
           </cell>
           <cell r="BL317">
-            <v>6111.44</v>
+            <v>1786.26</v>
           </cell>
         </row>
         <row r="318">
@@ -10103,7 +10103,7 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>6599.3</v>
+            <v>5449.8</v>
           </cell>
         </row>
         <row r="321">
@@ -10153,7 +10153,7 @@
             <v>2748.05</v>
           </cell>
           <cell r="BL321">
-            <v>4311.3900000000003</v>
+            <v>3777.22</v>
           </cell>
         </row>
         <row r="322">
@@ -10203,7 +10203,7 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>3322.26</v>
+            <v>2263.23</v>
           </cell>
         </row>
         <row r="323">
@@ -10253,7 +10253,7 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>11467.41</v>
+            <v>9542.5</v>
           </cell>
         </row>
         <row r="324">
@@ -10303,7 +10303,7 @@
             <v>630.75</v>
           </cell>
           <cell r="BL324">
-            <v>334.6</v>
+            <v>306.55</v>
           </cell>
         </row>
         <row r="325">
@@ -10403,7 +10403,7 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>3023.3</v>
+            <v>2485.46</v>
           </cell>
         </row>
         <row r="327">
@@ -10453,7 +10453,7 @@
             <v>3384.9</v>
           </cell>
           <cell r="BL327">
-            <v>933.45</v>
+            <v>581.79999999999995</v>
           </cell>
         </row>
         <row r="328">
@@ -10503,7 +10503,7 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>27058.66</v>
+            <v>21101.45</v>
           </cell>
         </row>
         <row r="329">
@@ -10553,7 +10553,7 @@
             <v>4790.9799999999996</v>
           </cell>
           <cell r="BL329">
-            <v>5364.02</v>
+            <v>4777.58</v>
           </cell>
         </row>
         <row r="330">
@@ -10603,7 +10603,7 @@
             <v>2022.35</v>
           </cell>
           <cell r="BL330">
-            <v>2293.94</v>
+            <v>1928.74</v>
           </cell>
         </row>
         <row r="331">
@@ -10703,7 +10703,7 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>3385.8</v>
+            <v>2746.48</v>
           </cell>
         </row>
         <row r="333">
@@ -10753,7 +10753,7 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>9179.16</v>
+            <v>7410.16</v>
           </cell>
         </row>
         <row r="334">
@@ -11103,7 +11103,7 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>3672.38</v>
+            <v>2730.14</v>
           </cell>
         </row>
         <row r="343">
@@ -11253,7 +11253,7 @@
             <v>1706.35</v>
           </cell>
           <cell r="BL345">
-            <v>4098.6400000000003</v>
+            <v>3425.04</v>
           </cell>
         </row>
         <row r="346">
@@ -11303,7 +11303,7 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>3043.23</v>
+            <v>2342.2600000000002</v>
           </cell>
         </row>
         <row r="347">
@@ -11353,7 +11353,7 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>10696.59</v>
+            <v>9462.0300000000007</v>
           </cell>
         </row>
         <row r="348">
@@ -11403,7 +11403,7 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>9913.24</v>
+            <v>8491.7800000000007</v>
           </cell>
         </row>
         <row r="349">
@@ -11453,7 +11453,7 @@
             <v>1478.26</v>
           </cell>
           <cell r="BL349">
-            <v>685.42</v>
+            <v>557.72</v>
           </cell>
         </row>
         <row r="350">
@@ -11553,7 +11553,7 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>1029.7</v>
+            <v>740.1</v>
           </cell>
         </row>
         <row r="352">
@@ -11653,7 +11653,7 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>25009.18</v>
+            <v>19624.55</v>
           </cell>
         </row>
         <row r="354">
@@ -11703,7 +11703,7 @@
             <v>6679.21</v>
           </cell>
           <cell r="BL354">
-            <v>5383.88</v>
+            <v>5071.66</v>
           </cell>
         </row>
         <row r="355">
@@ -11753,7 +11753,7 @@
             <v>3019.73</v>
           </cell>
           <cell r="BL355">
-            <v>1681.76</v>
+            <v>1557.26</v>
           </cell>
         </row>
         <row r="356">
@@ -11853,7 +11853,7 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>4047.07</v>
+            <v>2570.84</v>
           </cell>
         </row>
         <row r="358">
@@ -11903,7 +11903,7 @@
             <v>18146.46</v>
           </cell>
           <cell r="BL358">
-            <v>21315.65</v>
+            <v>13052.18</v>
           </cell>
         </row>
         <row r="359">
@@ -13059,7 +13059,7 @@
         <v>109</v>
       </c>
       <c r="P4">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -13247,7 +13247,7 @@
         <v>108</v>
       </c>
       <c r="P5">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -13435,7 +13435,7 @@
         <v>277</v>
       </c>
       <c r="P6">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -13811,7 +13811,7 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -13999,7 +13999,7 @@
         <v>78</v>
       </c>
       <c r="P9">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -14375,7 +14375,7 @@
         <v>892</v>
       </c>
       <c r="P11">
-        <v>726</v>
+        <v>547</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -14563,7 +14563,7 @@
         <v>425</v>
       </c>
       <c r="P12">
-        <v>508</v>
+        <v>390</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>775</v>
       </c>
       <c r="P13">
-        <v>543</v>
+        <v>420</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1041.4000000000001</v>
+        <v>1047.4000000000001</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -15522,7 +15522,7 @@
         <v>523.79</v>
       </c>
       <c r="P23">
-        <v>397.25</v>
+        <v>173.1</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -15599,7 +15599,7 @@
         <v>599.47</v>
       </c>
       <c r="P24">
-        <v>530.91</v>
+        <v>537.89</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>51.99</v>
       </c>
       <c r="P26">
-        <v>37.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         <v>1664.01</v>
       </c>
       <c r="P30">
-        <v>4848</v>
+        <v>217</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -16138,7 +16138,7 @@
         <v>1644.31</v>
       </c>
       <c r="P31">
-        <v>2100.16</v>
+        <v>2027.17</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -16369,7 +16369,7 @@
         <v>508.18</v>
       </c>
       <c r="P34">
-        <v>66.400000000000006</v>
+        <v>66.7</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         <v>548.19000000000005</v>
       </c>
       <c r="P35">
-        <v>737.05</v>
+        <v>114.6</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -17370,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>959.3</v>
+        <v>163</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         <v>423.9</v>
       </c>
       <c r="P48">
-        <v>619.61</v>
+        <v>579.05999999999995</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -17524,7 +17524,7 @@
         <v>6771.6</v>
       </c>
       <c r="P49">
-        <v>994.28</v>
+        <v>907.53</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -17601,7 +17601,7 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>507.14</v>
+        <v>441.39</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -17678,7 +17678,7 @@
         <v>392.52</v>
       </c>
       <c r="P51">
-        <v>65.3</v>
+        <v>49.3</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -17832,7 +17832,7 @@
         <v>475.55</v>
       </c>
       <c r="P53">
-        <v>51.64</v>
+        <v>29.94</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>6968.14</v>
       </c>
       <c r="P55">
-        <v>743.18</v>
+        <v>731.48</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -18063,7 +18063,7 @@
         <v>351.6</v>
       </c>
       <c r="P56">
-        <v>964.24</v>
+        <v>936.84</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -18140,7 +18140,7 @@
         <v>275.2</v>
       </c>
       <c r="P57">
-        <v>334.8</v>
+        <v>281.3</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -18294,7 +18294,7 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>632.67999999999995</v>
+        <v>492.81</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -18371,7 +18371,7 @@
         <v>87.73</v>
       </c>
       <c r="P60">
-        <v>246.3</v>
+        <v>245.3</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -19064,7 +19064,7 @@
         <v>1528.85</v>
       </c>
       <c r="P69">
-        <v>1436.72</v>
+        <v>1238.8</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -19295,7 +19295,7 @@
         <v>806.7</v>
       </c>
       <c r="P72">
-        <v>699.1</v>
+        <v>579.29999999999995</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -19372,7 +19372,7 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>923.53</v>
+        <v>331.3</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -19449,7 +19449,7 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>1279.26</v>
+        <v>850.52</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -19526,7 +19526,7 @@
         <v>5782.77</v>
       </c>
       <c r="P75">
-        <v>1377.73</v>
+        <v>882.29</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -19603,7 +19603,7 @@
         <v>360.6</v>
       </c>
       <c r="P76">
-        <v>159.35</v>
+        <v>117.8</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -19757,7 +19757,7 @@
         <v>276.93</v>
       </c>
       <c r="P78">
-        <v>215.83</v>
+        <v>150.47999999999999</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -19911,7 +19911,7 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>4924.63</v>
+        <v>2479.83</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -19988,7 +19988,7 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>2211.31</v>
+        <v>664.76</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -20065,7 +20065,7 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>586.82000000000005</v>
+        <v>552.47</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -20219,7 +20219,7 @@
         <v>2160.71</v>
       </c>
       <c r="P84">
-        <v>2155.6799999999998</v>
+        <v>1177.83</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -20296,7 +20296,7 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>2663.63</v>
+        <v>2421.7399999999998</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -21374,7 +21374,7 @@
         <v>32.49</v>
       </c>
       <c r="P99">
-        <v>78.959999999999994</v>
+        <v>0.01</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -21682,7 +21682,7 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -21913,7 +21913,7 @@
         <v>64.069999999999993</v>
       </c>
       <c r="P106">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -23222,7 +23222,7 @@
         <v>203.03</v>
       </c>
       <c r="P123">
-        <v>21.49</v>
+        <v>17.89</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>788.08</v>
       </c>
       <c r="P125">
-        <v>262.37</v>
+        <v>241.87</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -23838,7 +23838,7 @@
         <v>128.09</v>
       </c>
       <c r="P131">
-        <v>460.75</v>
+        <v>466.05</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -24069,7 +24069,7 @@
         <v>347.7</v>
       </c>
       <c r="P134">
-        <v>236.83</v>
+        <v>193.03</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -25147,7 +25147,7 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>493.17</v>
+        <v>436.87</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -25224,7 +25224,7 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>354.19</v>
+        <v>304.58999999999997</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -25301,7 +25301,7 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>597.6</v>
+        <v>563.29999999999995</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>1212.5</v>
       </c>
       <c r="P155">
-        <v>299.39999999999998</v>
+        <v>129.5</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>1217.27</v>
       </c>
       <c r="P156">
-        <v>213.08</v>
+        <v>199.18</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25994,7 +25994,7 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>482.65</v>
+        <v>470.95</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26071,7 +26071,7 @@
         <v>282.8</v>
       </c>
       <c r="P160">
-        <v>585.54999999999995</v>
+        <v>313.75</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -28689,7 +28689,7 @@
         <v>10911.5</v>
       </c>
       <c r="P194">
-        <v>21505.040000000001</v>
+        <v>7867.21</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -28920,7 +28920,7 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>5286.1</v>
+        <v>4716.7</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -28997,7 +28997,7 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>9589.81</v>
+        <v>5330.29</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -29074,7 +29074,7 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>9748.14</v>
+        <v>8063.34</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -29151,7 +29151,7 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>15233.71</v>
+        <v>10665.79</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -29228,7 +29228,7 @@
         <v>819.93</v>
       </c>
       <c r="P201">
-        <v>1123.31</v>
+        <v>649.42999999999995</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -29382,7 +29382,7 @@
         <v>1498.34</v>
       </c>
       <c r="P203">
-        <v>2654.75</v>
+        <v>1403.55</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -29459,7 +29459,7 @@
         <v>2807.35</v>
       </c>
       <c r="P204">
-        <v>3277.5</v>
+        <v>1867.65</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -29536,7 +29536,7 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>104267.16</v>
+        <v>80514.02</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -29613,7 +29613,7 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>9025.65</v>
+        <v>6680.78</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>3782.99</v>
       </c>
       <c r="P207">
-        <v>738.95</v>
+        <v>728.05</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -29767,7 +29767,7 @@
         <v>2317.5500000000002</v>
       </c>
       <c r="P208">
-        <v>433</v>
+        <v>290</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -29844,7 +29844,7 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>5317.21</v>
+        <v>3988.82</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -29921,7 +29921,7 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>29440.46</v>
+        <v>16613.75</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -30614,7 +30614,7 @@
         <v>5408.2</v>
       </c>
       <c r="P219">
-        <v>6111.44</v>
+        <v>1786.26</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -30845,7 +30845,7 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>6599.3</v>
+        <v>5449.8</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -30922,7 +30922,7 @@
         <v>2748.05</v>
       </c>
       <c r="P223">
-        <v>4311.3900000000003</v>
+        <v>3777.22</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -30999,7 +30999,7 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>3322.26</v>
+        <v>2263.23</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -31076,7 +31076,7 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>11467.41</v>
+        <v>9542.5</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -31153,7 +31153,7 @@
         <v>630.75</v>
       </c>
       <c r="P226">
-        <v>334.6</v>
+        <v>306.55</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -31307,7 +31307,7 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>3023.3</v>
+        <v>2485.46</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -31384,7 +31384,7 @@
         <v>3384.9</v>
       </c>
       <c r="P229">
-        <v>933.45</v>
+        <v>581.79999999999995</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -31461,7 +31461,7 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>27058.66</v>
+        <v>21101.45</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -31538,7 +31538,7 @@
         <v>4790.9799999999996</v>
       </c>
       <c r="P231">
-        <v>5364.02</v>
+        <v>4777.58</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -31615,7 +31615,7 @@
         <v>2022.35</v>
       </c>
       <c r="P232">
-        <v>2293.94</v>
+        <v>1928.74</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -31769,7 +31769,7 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>3385.8</v>
+        <v>2746.48</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -31846,7 +31846,7 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>9179.16</v>
+        <v>7410.16</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -32539,7 +32539,7 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>3672.38</v>
+        <v>2730.14</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -32770,7 +32770,7 @@
         <v>1706.35</v>
       </c>
       <c r="P247">
-        <v>4098.6400000000003</v>
+        <v>3425.04</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -32847,7 +32847,7 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>3043.23</v>
+        <v>2342.2600000000002</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -32924,7 +32924,7 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>10696.59</v>
+        <v>9462.0300000000007</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>9913.24</v>
+        <v>8491.7800000000007</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -33078,7 +33078,7 @@
         <v>1478.26</v>
       </c>
       <c r="P251">
-        <v>685.42</v>
+        <v>557.72</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -33232,7 +33232,7 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>1029.7</v>
+        <v>740.1</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -33386,7 +33386,7 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>25009.18</v>
+        <v>19624.55</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -33463,7 +33463,7 @@
         <v>6679.21</v>
       </c>
       <c r="P256">
-        <v>5383.88</v>
+        <v>5071.66</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -33540,7 +33540,7 @@
         <v>3019.73</v>
       </c>
       <c r="P257">
-        <v>1681.76</v>
+        <v>1557.26</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -33694,7 +33694,7 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>4047.07</v>
+        <v>2570.84</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -33771,7 +33771,7 @@
         <v>18146.46</v>
       </c>
       <c r="P260">
-        <v>21315.65</v>
+        <v>13052.18</v>
       </c>
       <c r="Q260">
         <v>0</v>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60bd3766fe3b56c0/Nova pasta/Nova pasta/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C66AA5-2F67-4010-B837-35B29476A991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D37CA-6BA6-4568-ACB2-341A1391D80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Qtd. vendas por funcionário</t>
   </si>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">vendas por setores </t>
   </si>
+  <si>
+    <t xml:space="preserve">TOTAL ENTRADA </t>
+  </si>
 </sst>
 </file>
 
@@ -111,7 +114,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="7" formatCode="&quot;R$&quot;\ #,##0.00;\-&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="mmmm\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -144,7 +147,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -246,7 +249,7 @@
             <v>109</v>
           </cell>
           <cell r="BL93">
-            <v>54</v>
+            <v>67</v>
           </cell>
         </row>
         <row r="94">
@@ -290,7 +293,7 @@
             <v>108</v>
           </cell>
           <cell r="BL94">
-            <v>68</v>
+            <v>91</v>
           </cell>
         </row>
         <row r="95">
@@ -334,7 +337,7 @@
             <v>277</v>
           </cell>
           <cell r="BL95">
-            <v>116</v>
+            <v>185</v>
           </cell>
         </row>
         <row r="96">
@@ -378,7 +381,7 @@
             <v>5</v>
           </cell>
           <cell r="BL96">
-            <v>4</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="97">
@@ -422,7 +425,7 @@
             <v>40</v>
           </cell>
           <cell r="BL97">
-            <v>28</v>
+            <v>36</v>
           </cell>
         </row>
         <row r="98">
@@ -466,7 +469,7 @@
             <v>78</v>
           </cell>
           <cell r="BL98">
-            <v>57</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="99">
@@ -554,7 +557,7 @@
             <v>892</v>
           </cell>
           <cell r="BL100">
-            <v>547</v>
+            <v>751</v>
           </cell>
         </row>
         <row r="101">
@@ -598,7 +601,7 @@
             <v>425</v>
           </cell>
           <cell r="BL101">
-            <v>390</v>
+            <v>561</v>
           </cell>
         </row>
         <row r="102">
@@ -642,7 +645,7 @@
             <v>775</v>
           </cell>
           <cell r="BL102">
-            <v>420</v>
+            <v>588</v>
           </cell>
         </row>
         <row r="103">
@@ -903,7 +906,7 @@
             <v>0</v>
           </cell>
           <cell r="BL120">
-            <v>1047.4000000000001</v>
+            <v>1041.4000000000001</v>
           </cell>
         </row>
         <row r="121">
@@ -953,7 +956,7 @@
             <v>523.79</v>
           </cell>
           <cell r="BL121">
-            <v>173.1</v>
+            <v>444.05</v>
           </cell>
         </row>
         <row r="122">
@@ -1003,7 +1006,7 @@
             <v>599.47</v>
           </cell>
           <cell r="BL122">
-            <v>537.89</v>
+            <v>545.91</v>
           </cell>
         </row>
         <row r="123">
@@ -1053,7 +1056,7 @@
             <v>963.68</v>
           </cell>
           <cell r="BL123">
-            <v>421.07</v>
+            <v>580.96</v>
           </cell>
         </row>
         <row r="124">
@@ -1103,7 +1106,7 @@
             <v>51.99</v>
           </cell>
           <cell r="BL124">
-            <v>41.3</v>
+            <v>37.4</v>
           </cell>
         </row>
         <row r="125">
@@ -1203,7 +1206,7 @@
             <v>213.94</v>
           </cell>
           <cell r="BL126">
-            <v>86</v>
+            <v>95.9</v>
           </cell>
         </row>
         <row r="127">
@@ -1303,7 +1306,7 @@
             <v>1664.01</v>
           </cell>
           <cell r="BL128">
-            <v>217</v>
+            <v>4848</v>
           </cell>
         </row>
         <row r="129">
@@ -1353,7 +1356,7 @@
             <v>1644.31</v>
           </cell>
           <cell r="BL129">
-            <v>2027.17</v>
+            <v>2100.16</v>
           </cell>
         </row>
         <row r="130">
@@ -1403,7 +1406,7 @@
             <v>251.68</v>
           </cell>
           <cell r="BL130">
-            <v>517.14</v>
+            <v>530.04</v>
           </cell>
         </row>
         <row r="131">
@@ -1503,7 +1506,7 @@
             <v>508.18</v>
           </cell>
           <cell r="BL132">
-            <v>66.7</v>
+            <v>86.4</v>
           </cell>
         </row>
         <row r="133">
@@ -1553,7 +1556,7 @@
             <v>548.19000000000005</v>
           </cell>
           <cell r="BL133">
-            <v>114.6</v>
+            <v>758.05</v>
           </cell>
         </row>
         <row r="134">
@@ -2053,7 +2056,7 @@
             <v>0</v>
           </cell>
           <cell r="BL145">
-            <v>163</v>
+            <v>959.3</v>
           </cell>
         </row>
         <row r="146">
@@ -2103,7 +2106,7 @@
             <v>423.9</v>
           </cell>
           <cell r="BL146">
-            <v>579.05999999999995</v>
+            <v>619.61</v>
           </cell>
         </row>
         <row r="147">
@@ -2153,7 +2156,7 @@
             <v>6771.6</v>
           </cell>
           <cell r="BL147">
-            <v>907.53</v>
+            <v>991.28</v>
           </cell>
         </row>
         <row r="148">
@@ -2203,7 +2206,7 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>441.39</v>
+            <v>505.85</v>
           </cell>
         </row>
         <row r="149">
@@ -2253,7 +2256,7 @@
             <v>392.52</v>
           </cell>
           <cell r="BL149">
-            <v>49.3</v>
+            <v>65.3</v>
           </cell>
         </row>
         <row r="150">
@@ -2353,7 +2356,7 @@
             <v>475.55</v>
           </cell>
           <cell r="BL151">
-            <v>29.94</v>
+            <v>74.64</v>
           </cell>
         </row>
         <row r="152">
@@ -2453,7 +2456,7 @@
             <v>6968.14</v>
           </cell>
           <cell r="BL153">
-            <v>731.48</v>
+            <v>743.18</v>
           </cell>
         </row>
         <row r="154">
@@ -2503,7 +2506,7 @@
             <v>351.6</v>
           </cell>
           <cell r="BL154">
-            <v>936.84</v>
+            <v>1244.1199999999999</v>
           </cell>
         </row>
         <row r="155">
@@ -2553,7 +2556,7 @@
             <v>275.2</v>
           </cell>
           <cell r="BL155">
-            <v>281.3</v>
+            <v>334.8</v>
           </cell>
         </row>
         <row r="156">
@@ -2653,7 +2656,7 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>492.81</v>
+            <v>667.68</v>
           </cell>
         </row>
         <row r="158">
@@ -2703,7 +2706,7 @@
             <v>87.73</v>
           </cell>
           <cell r="BL158">
-            <v>245.3</v>
+            <v>266.25</v>
           </cell>
         </row>
         <row r="159">
@@ -3053,7 +3056,7 @@
             <v>1528.85</v>
           </cell>
           <cell r="BL167">
-            <v>1238.8</v>
+            <v>2994.32</v>
           </cell>
         </row>
         <row r="168">
@@ -3203,7 +3206,7 @@
             <v>806.7</v>
           </cell>
           <cell r="BL170">
-            <v>579.29999999999995</v>
+            <v>699.1</v>
           </cell>
         </row>
         <row r="171">
@@ -3253,7 +3256,7 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>331.3</v>
+            <v>946.13</v>
           </cell>
         </row>
         <row r="172">
@@ -3303,7 +3306,7 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>850.52</v>
+            <v>1296.3599999999999</v>
           </cell>
         </row>
         <row r="173">
@@ -3353,7 +3356,7 @@
             <v>5782.77</v>
           </cell>
           <cell r="BL173">
-            <v>882.29</v>
+            <v>1352.67</v>
           </cell>
         </row>
         <row r="174">
@@ -3403,7 +3406,7 @@
             <v>360.6</v>
           </cell>
           <cell r="BL174">
-            <v>117.8</v>
+            <v>163.25</v>
           </cell>
         </row>
         <row r="175">
@@ -3503,7 +3506,7 @@
             <v>276.93</v>
           </cell>
           <cell r="BL176">
-            <v>150.47999999999999</v>
+            <v>209.83</v>
           </cell>
         </row>
         <row r="177">
@@ -3603,7 +3606,7 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>2479.83</v>
+            <v>4804.8999999999996</v>
           </cell>
         </row>
         <row r="179">
@@ -3653,7 +3656,7 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>664.76</v>
+            <v>2210.5100000000002</v>
           </cell>
         </row>
         <row r="180">
@@ -3703,7 +3706,7 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>552.47</v>
+            <v>603.72</v>
           </cell>
         </row>
         <row r="181">
@@ -3803,7 +3806,7 @@
             <v>2160.71</v>
           </cell>
           <cell r="BL182">
-            <v>1177.83</v>
+            <v>2207.09</v>
           </cell>
         </row>
         <row r="183">
@@ -3853,7 +3856,7 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>2421.7399999999998</v>
+            <v>3423.97</v>
           </cell>
         </row>
         <row r="184">
@@ -4453,7 +4456,7 @@
             <v>32.49</v>
           </cell>
           <cell r="BL197">
-            <v>0.01</v>
+            <v>78.959999999999994</v>
           </cell>
         </row>
         <row r="198">
@@ -4653,7 +4656,7 @@
             <v>0</v>
           </cell>
           <cell r="BL201">
-            <v>0</v>
+            <v>5.56</v>
           </cell>
         </row>
         <row r="202">
@@ -4803,7 +4806,7 @@
             <v>64.069999999999993</v>
           </cell>
           <cell r="BL204">
-            <v>0</v>
+            <v>4.96</v>
           </cell>
         </row>
         <row r="205">
@@ -5553,7 +5556,7 @@
             <v>203.03</v>
           </cell>
           <cell r="BL221">
-            <v>17.89</v>
+            <v>21.49</v>
           </cell>
         </row>
         <row r="222">
@@ -5603,7 +5606,7 @@
             <v>540.03</v>
           </cell>
           <cell r="BL222">
-            <v>207.8</v>
+            <v>215.71</v>
           </cell>
         </row>
         <row r="223">
@@ -5653,7 +5656,7 @@
             <v>788.08</v>
           </cell>
           <cell r="BL223">
-            <v>241.87</v>
+            <v>253.37</v>
           </cell>
         </row>
         <row r="224">
@@ -5703,7 +5706,7 @@
             <v>349.1</v>
           </cell>
           <cell r="BL224">
-            <v>224.6</v>
+            <v>251.5</v>
           </cell>
         </row>
         <row r="225">
@@ -5953,7 +5956,7 @@
             <v>128.09</v>
           </cell>
           <cell r="BL229">
-            <v>466.05</v>
+            <v>572.65</v>
           </cell>
         </row>
         <row r="230">
@@ -6103,7 +6106,7 @@
             <v>347.7</v>
           </cell>
           <cell r="BL232">
-            <v>193.03</v>
+            <v>234.83</v>
           </cell>
         </row>
         <row r="233">
@@ -6703,7 +6706,7 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>436.87</v>
+            <v>482.17</v>
           </cell>
         </row>
         <row r="247">
@@ -6753,7 +6756,7 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>304.58999999999997</v>
+            <v>347.79</v>
           </cell>
         </row>
         <row r="248">
@@ -6803,7 +6806,7 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>563.29999999999995</v>
+            <v>593.75</v>
           </cell>
         </row>
         <row r="249">
@@ -7053,7 +7056,7 @@
             <v>1212.5</v>
           </cell>
           <cell r="BL253">
-            <v>129.5</v>
+            <v>299.39999999999998</v>
           </cell>
         </row>
         <row r="254">
@@ -7103,7 +7106,7 @@
             <v>1217.27</v>
           </cell>
           <cell r="BL254">
-            <v>199.18</v>
+            <v>213.08</v>
           </cell>
         </row>
         <row r="255">
@@ -7253,7 +7256,7 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>470.95</v>
+            <v>482.65</v>
           </cell>
         </row>
         <row r="258">
@@ -7303,7 +7306,7 @@
             <v>282.8</v>
           </cell>
           <cell r="BL258">
-            <v>313.75</v>
+            <v>576.54999999999995</v>
           </cell>
         </row>
         <row r="259">
@@ -8803,7 +8806,7 @@
             <v>10911.5</v>
           </cell>
           <cell r="BL292">
-            <v>7867.21</v>
+            <v>24876.79</v>
           </cell>
         </row>
         <row r="293">
@@ -8953,7 +8956,7 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>4716.7</v>
+            <v>5779.94</v>
           </cell>
         </row>
         <row r="296">
@@ -9003,7 +9006,7 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>5330.29</v>
+            <v>9705.77</v>
           </cell>
         </row>
         <row r="297">
@@ -9053,7 +9056,7 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>8063.34</v>
+            <v>9755.67</v>
           </cell>
         </row>
         <row r="298">
@@ -9103,7 +9106,7 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>10665.79</v>
+            <v>15322.7</v>
           </cell>
         </row>
         <row r="299">
@@ -9153,7 +9156,7 @@
             <v>819.93</v>
           </cell>
           <cell r="BL299">
-            <v>649.42999999999995</v>
+            <v>1161.1600000000001</v>
           </cell>
         </row>
         <row r="300">
@@ -9253,7 +9256,7 @@
             <v>1498.34</v>
           </cell>
           <cell r="BL301">
-            <v>1403.55</v>
+            <v>5223.99</v>
           </cell>
         </row>
         <row r="302">
@@ -9303,7 +9306,7 @@
             <v>2807.35</v>
           </cell>
           <cell r="BL302">
-            <v>1867.65</v>
+            <v>3277.5</v>
           </cell>
         </row>
         <row r="303">
@@ -9353,7 +9356,7 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>80514.02</v>
+            <v>109524.39</v>
           </cell>
         </row>
         <row r="304">
@@ -9403,7 +9406,7 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>6680.78</v>
+            <v>9043.35</v>
           </cell>
         </row>
         <row r="305">
@@ -9453,7 +9456,7 @@
             <v>3782.99</v>
           </cell>
           <cell r="BL305">
-            <v>728.05</v>
+            <v>783.75</v>
           </cell>
         </row>
         <row r="306">
@@ -9503,7 +9506,7 @@
             <v>2317.5500000000002</v>
           </cell>
           <cell r="BL306">
-            <v>290</v>
+            <v>433</v>
           </cell>
         </row>
         <row r="307">
@@ -9553,7 +9556,7 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>3988.82</v>
+            <v>5353.31</v>
           </cell>
         </row>
         <row r="308">
@@ -9603,7 +9606,7 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>16613.75</v>
+            <v>29217.46</v>
           </cell>
         </row>
         <row r="309">
@@ -9953,7 +9956,7 @@
             <v>5408.2</v>
           </cell>
           <cell r="BL317">
-            <v>1786.26</v>
+            <v>6246.19</v>
           </cell>
         </row>
         <row r="318">
@@ -10103,7 +10106,7 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>5449.8</v>
+            <v>6642.2</v>
           </cell>
         </row>
         <row r="321">
@@ -10153,7 +10156,7 @@
             <v>2748.05</v>
           </cell>
           <cell r="BL321">
-            <v>3777.22</v>
+            <v>4725.95</v>
           </cell>
         </row>
         <row r="322">
@@ -10203,7 +10206,7 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>2263.23</v>
+            <v>3883.83</v>
           </cell>
         </row>
         <row r="323">
@@ -10253,7 +10256,7 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>9542.5</v>
+            <v>12189.58</v>
           </cell>
         </row>
         <row r="324">
@@ -10303,7 +10306,7 @@
             <v>630.75</v>
           </cell>
           <cell r="BL324">
-            <v>306.55</v>
+            <v>401.36</v>
           </cell>
         </row>
         <row r="325">
@@ -10403,7 +10406,7 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>2485.46</v>
+            <v>3183.25</v>
           </cell>
         </row>
         <row r="327">
@@ -10453,7 +10456,7 @@
             <v>3384.9</v>
           </cell>
           <cell r="BL327">
-            <v>581.79999999999995</v>
+            <v>933.45</v>
           </cell>
         </row>
         <row r="328">
@@ -10503,7 +10506,7 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>21101.45</v>
+            <v>32367.51</v>
           </cell>
         </row>
         <row r="329">
@@ -10553,7 +10556,7 @@
             <v>4790.9799999999996</v>
           </cell>
           <cell r="BL329">
-            <v>4777.58</v>
+            <v>5632.88</v>
           </cell>
         </row>
         <row r="330">
@@ -10603,7 +10606,7 @@
             <v>2022.35</v>
           </cell>
           <cell r="BL330">
-            <v>1928.74</v>
+            <v>2400.84</v>
           </cell>
         </row>
         <row r="331">
@@ -10703,7 +10706,7 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>2746.48</v>
+            <v>3953.57</v>
           </cell>
         </row>
         <row r="333">
@@ -10753,7 +10756,7 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>7410.16</v>
+            <v>9696.7800000000007</v>
           </cell>
         </row>
         <row r="334">
@@ -11103,7 +11106,7 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>2730.14</v>
+            <v>4491.96</v>
           </cell>
         </row>
         <row r="343">
@@ -11253,7 +11256,7 @@
             <v>1706.35</v>
           </cell>
           <cell r="BL345">
-            <v>3425.04</v>
+            <v>4092.26</v>
           </cell>
         </row>
         <row r="346">
@@ -11303,7 +11306,7 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>2342.2600000000002</v>
+            <v>3180.69</v>
           </cell>
         </row>
         <row r="347">
@@ -11353,7 +11356,7 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>9462.0300000000007</v>
+            <v>10828.19</v>
           </cell>
         </row>
         <row r="348">
@@ -11403,7 +11406,7 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>8491.7800000000007</v>
+            <v>10434.879999999999</v>
           </cell>
         </row>
         <row r="349">
@@ -11453,7 +11456,7 @@
             <v>1478.26</v>
           </cell>
           <cell r="BL349">
-            <v>557.72</v>
+            <v>716.95</v>
           </cell>
         </row>
         <row r="350">
@@ -11553,7 +11556,7 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>740.1</v>
+            <v>1438.9</v>
           </cell>
         </row>
         <row r="352">
@@ -11653,7 +11656,7 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>19624.55</v>
+            <v>26068.95</v>
           </cell>
         </row>
         <row r="354">
@@ -11703,7 +11706,7 @@
             <v>6679.21</v>
           </cell>
           <cell r="BL354">
-            <v>5071.66</v>
+            <v>5420.08</v>
           </cell>
         </row>
         <row r="355">
@@ -11753,7 +11756,7 @@
             <v>3019.73</v>
           </cell>
           <cell r="BL355">
-            <v>1557.26</v>
+            <v>1691.66</v>
           </cell>
         </row>
         <row r="356">
@@ -11853,7 +11856,7 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>2570.84</v>
+            <v>4220.72</v>
           </cell>
         </row>
         <row r="358">
@@ -11903,7 +11906,7 @@
             <v>18146.46</v>
           </cell>
           <cell r="BL358">
-            <v>13052.18</v>
+            <v>22736.11</v>
           </cell>
         </row>
         <row r="359">
@@ -12901,7 +12904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A45DA6-73B0-4E2B-A1BA-FBFE1A2F5414}">
-  <dimension ref="A1:BK292"/>
+  <dimension ref="A1:BK299"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -13059,7 +13062,7 @@
         <v>109</v>
       </c>
       <c r="P4">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -13247,7 +13250,7 @@
         <v>108</v>
       </c>
       <c r="P5">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -13435,7 +13438,7 @@
         <v>277</v>
       </c>
       <c r="P6">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -13623,7 +13626,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -13811,7 +13814,7 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -13999,7 +14002,7 @@
         <v>78</v>
       </c>
       <c r="P9">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -14375,7 +14378,7 @@
         <v>892</v>
       </c>
       <c r="P11">
-        <v>547</v>
+        <v>751</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -14563,7 +14566,7 @@
         <v>425</v>
       </c>
       <c r="P12">
-        <v>390</v>
+        <v>561</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -14751,7 +14754,7 @@
         <v>775</v>
       </c>
       <c r="P13">
-        <v>420</v>
+        <v>588</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -15445,7 +15448,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1047.4000000000001</v>
+        <v>1041.4000000000001</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -15522,7 +15525,7 @@
         <v>523.79</v>
       </c>
       <c r="P23">
-        <v>173.1</v>
+        <v>444.05</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -15599,7 +15602,7 @@
         <v>599.47</v>
       </c>
       <c r="P24">
-        <v>537.89</v>
+        <v>545.91</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -15676,7 +15679,7 @@
         <v>963.68</v>
       </c>
       <c r="P25">
-        <v>421.07</v>
+        <v>580.96</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -15753,7 +15756,7 @@
         <v>51.99</v>
       </c>
       <c r="P26">
-        <v>41.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -15907,7 +15910,7 @@
         <v>213.94</v>
       </c>
       <c r="P28">
-        <v>86</v>
+        <v>95.9</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -16061,7 +16064,7 @@
         <v>1664.01</v>
       </c>
       <c r="P30">
-        <v>217</v>
+        <v>4848</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -16138,7 +16141,7 @@
         <v>1644.31</v>
       </c>
       <c r="P31">
-        <v>2027.17</v>
+        <v>2100.16</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -16215,7 +16218,7 @@
         <v>251.68</v>
       </c>
       <c r="P32">
-        <v>517.14</v>
+        <v>530.04</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -16369,7 +16372,7 @@
         <v>508.18</v>
       </c>
       <c r="P34">
-        <v>66.7</v>
+        <v>86.4</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -16446,7 +16449,7 @@
         <v>548.19000000000005</v>
       </c>
       <c r="P35">
-        <v>114.6</v>
+        <v>758.05</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -17370,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>163</v>
+        <v>959.3</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -17447,7 +17450,7 @@
         <v>423.9</v>
       </c>
       <c r="P48">
-        <v>579.05999999999995</v>
+        <v>619.61</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -17524,7 +17527,7 @@
         <v>6771.6</v>
       </c>
       <c r="P49">
-        <v>907.53</v>
+        <v>991.28</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -17601,7 +17604,7 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>441.39</v>
+        <v>505.85</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -17678,7 +17681,7 @@
         <v>392.52</v>
       </c>
       <c r="P51">
-        <v>49.3</v>
+        <v>65.3</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -17832,7 +17835,7 @@
         <v>475.55</v>
       </c>
       <c r="P53">
-        <v>29.94</v>
+        <v>74.64</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -17986,7 +17989,7 @@
         <v>6968.14</v>
       </c>
       <c r="P55">
-        <v>731.48</v>
+        <v>743.18</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -18063,7 +18066,7 @@
         <v>351.6</v>
       </c>
       <c r="P56">
-        <v>936.84</v>
+        <v>1244.1199999999999</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -18140,7 +18143,7 @@
         <v>275.2</v>
       </c>
       <c r="P57">
-        <v>281.3</v>
+        <v>334.8</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -18294,7 +18297,7 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>492.81</v>
+        <v>667.68</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -18371,7 +18374,7 @@
         <v>87.73</v>
       </c>
       <c r="P60">
-        <v>245.3</v>
+        <v>266.25</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -19064,7 +19067,7 @@
         <v>1528.85</v>
       </c>
       <c r="P69">
-        <v>1238.8</v>
+        <v>2994.32</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -19295,7 +19298,7 @@
         <v>806.7</v>
       </c>
       <c r="P72">
-        <v>579.29999999999995</v>
+        <v>699.1</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -19372,7 +19375,7 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>331.3</v>
+        <v>946.13</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -19449,7 +19452,7 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>850.52</v>
+        <v>1296.3599999999999</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -19526,7 +19529,7 @@
         <v>5782.77</v>
       </c>
       <c r="P75">
-        <v>882.29</v>
+        <v>1352.67</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -19603,7 +19606,7 @@
         <v>360.6</v>
       </c>
       <c r="P76">
-        <v>117.8</v>
+        <v>163.25</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -19757,7 +19760,7 @@
         <v>276.93</v>
       </c>
       <c r="P78">
-        <v>150.47999999999999</v>
+        <v>209.83</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -19911,7 +19914,7 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>2479.83</v>
+        <v>4804.8999999999996</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -19988,7 +19991,7 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>664.76</v>
+        <v>2210.5100000000002</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -20065,7 +20068,7 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>552.47</v>
+        <v>603.72</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -20219,7 +20222,7 @@
         <v>2160.71</v>
       </c>
       <c r="P84">
-        <v>1177.83</v>
+        <v>2207.09</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -20296,7 +20299,7 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>2421.7399999999998</v>
+        <v>3423.97</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -21374,7 +21377,7 @@
         <v>32.49</v>
       </c>
       <c r="P99">
-        <v>0.01</v>
+        <v>78.959999999999994</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -21682,7 +21685,7 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -21913,7 +21916,7 @@
         <v>64.069999999999993</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -23222,7 +23225,7 @@
         <v>203.03</v>
       </c>
       <c r="P123">
-        <v>17.89</v>
+        <v>21.49</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -23299,7 +23302,7 @@
         <v>540.03</v>
       </c>
       <c r="P124">
-        <v>207.8</v>
+        <v>215.71</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -23376,7 +23379,7 @@
         <v>788.08</v>
       </c>
       <c r="P125">
-        <v>241.87</v>
+        <v>253.37</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -23453,7 +23456,7 @@
         <v>349.1</v>
       </c>
       <c r="P126">
-        <v>224.6</v>
+        <v>251.5</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -23838,7 +23841,7 @@
         <v>128.09</v>
       </c>
       <c r="P131">
-        <v>466.05</v>
+        <v>572.65</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -24069,7 +24072,7 @@
         <v>347.7</v>
       </c>
       <c r="P134">
-        <v>193.03</v>
+        <v>234.83</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -25147,7 +25150,7 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>436.87</v>
+        <v>482.17</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -25224,7 +25227,7 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>304.58999999999997</v>
+        <v>347.79</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -25301,7 +25304,7 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>563.29999999999995</v>
+        <v>593.75</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -25686,7 +25689,7 @@
         <v>1212.5</v>
       </c>
       <c r="P155">
-        <v>129.5</v>
+        <v>299.39999999999998</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25763,7 +25766,7 @@
         <v>1217.27</v>
       </c>
       <c r="P156">
-        <v>199.18</v>
+        <v>213.08</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25994,7 +25997,7 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>470.95</v>
+        <v>482.65</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26071,7 +26074,7 @@
         <v>282.8</v>
       </c>
       <c r="P160">
-        <v>313.75</v>
+        <v>576.54999999999995</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -28689,7 +28692,7 @@
         <v>10911.5</v>
       </c>
       <c r="P194">
-        <v>7867.21</v>
+        <v>24876.79</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -28920,7 +28923,7 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>4716.7</v>
+        <v>5779.94</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -28997,7 +29000,7 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>5330.29</v>
+        <v>9705.77</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -29074,7 +29077,7 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>8063.34</v>
+        <v>9755.67</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -29151,7 +29154,7 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>10665.79</v>
+        <v>15322.7</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -29228,7 +29231,7 @@
         <v>819.93</v>
       </c>
       <c r="P201">
-        <v>649.42999999999995</v>
+        <v>1161.1600000000001</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -29382,7 +29385,7 @@
         <v>1498.34</v>
       </c>
       <c r="P203">
-        <v>1403.55</v>
+        <v>5223.99</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -29459,7 +29462,7 @@
         <v>2807.35</v>
       </c>
       <c r="P204">
-        <v>1867.65</v>
+        <v>3277.5</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -29536,7 +29539,7 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>80514.02</v>
+        <v>109524.39</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -29613,7 +29616,7 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>6680.78</v>
+        <v>9043.35</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -29690,7 +29693,7 @@
         <v>3782.99</v>
       </c>
       <c r="P207">
-        <v>728.05</v>
+        <v>783.75</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -29767,7 +29770,7 @@
         <v>2317.5500000000002</v>
       </c>
       <c r="P208">
-        <v>290</v>
+        <v>433</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -29844,7 +29847,7 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>3988.82</v>
+        <v>5353.31</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -29921,7 +29924,7 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>16613.75</v>
+        <v>29217.46</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -30614,7 +30617,7 @@
         <v>5408.2</v>
       </c>
       <c r="P219">
-        <v>1786.26</v>
+        <v>6246.19</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -30845,7 +30848,7 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>5449.8</v>
+        <v>6642.2</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -30922,7 +30925,7 @@
         <v>2748.05</v>
       </c>
       <c r="P223">
-        <v>3777.22</v>
+        <v>4725.95</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -30999,7 +31002,7 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>2263.23</v>
+        <v>3883.83</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -31076,7 +31079,7 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>9542.5</v>
+        <v>12189.58</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -31153,7 +31156,7 @@
         <v>630.75</v>
       </c>
       <c r="P226">
-        <v>306.55</v>
+        <v>401.36</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -31307,7 +31310,7 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>2485.46</v>
+        <v>3183.25</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -31384,7 +31387,7 @@
         <v>3384.9</v>
       </c>
       <c r="P229">
-        <v>581.79999999999995</v>
+        <v>933.45</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -31461,7 +31464,7 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>21101.45</v>
+        <v>32367.51</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -31538,7 +31541,7 @@
         <v>4790.9799999999996</v>
       </c>
       <c r="P231">
-        <v>4777.58</v>
+        <v>5632.88</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -31615,7 +31618,7 @@
         <v>2022.35</v>
       </c>
       <c r="P232">
-        <v>1928.74</v>
+        <v>2400.84</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -31769,7 +31772,7 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>2746.48</v>
+        <v>3953.57</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -31846,7 +31849,7 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>7410.16</v>
+        <v>9696.7800000000007</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -32539,7 +32542,7 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>2730.14</v>
+        <v>4491.96</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -32770,7 +32773,7 @@
         <v>1706.35</v>
       </c>
       <c r="P247">
-        <v>3425.04</v>
+        <v>4092.26</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -32847,7 +32850,7 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>2342.2600000000002</v>
+        <v>3180.69</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -32924,7 +32927,7 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>9462.0300000000007</v>
+        <v>10828.19</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -33001,7 +33004,7 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>8491.7800000000007</v>
+        <v>10434.879999999999</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -33078,7 +33081,7 @@
         <v>1478.26</v>
       </c>
       <c r="P251">
-        <v>557.72</v>
+        <v>716.95</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -33232,7 +33235,7 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>740.1</v>
+        <v>1438.9</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -33386,7 +33389,7 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>19624.55</v>
+        <v>26068.95</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -33463,7 +33466,7 @@
         <v>6679.21</v>
       </c>
       <c r="P256">
-        <v>5071.66</v>
+        <v>5420.08</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -33540,7 +33543,7 @@
         <v>3019.73</v>
       </c>
       <c r="P257">
-        <v>1557.26</v>
+        <v>1691.66</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -33694,7 +33697,7 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>2570.84</v>
+        <v>4220.72</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -33771,7 +33774,7 @@
         <v>18146.46</v>
       </c>
       <c r="P260">
-        <v>13052.18</v>
+        <v>22736.11</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -35957,7 +35960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A289" t="str">
         <v xml:space="preserve">VENDEDOR </v>
       </c>
@@ -36034,7 +36037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A290" t="str">
         <v xml:space="preserve">VENDEDOR </v>
       </c>
@@ -36111,7 +36114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A291" t="str">
         <v xml:space="preserve">VENDEDOR </v>
       </c>
@@ -36188,7 +36191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>0</v>
       </c>
@@ -36262,6 +36265,163 @@
         <v>0</v>
       </c>
       <c r="Y292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299">
+        <f t="shared" ref="C299:AN299" si="0">SUM(C17:C292)</f>
+        <v>642279.78</v>
+      </c>
+      <c r="D299">
+        <f t="shared" si="0"/>
+        <v>619860.11</v>
+      </c>
+      <c r="E299">
+        <f t="shared" si="0"/>
+        <v>618508.72</v>
+      </c>
+      <c r="F299">
+        <f t="shared" si="0"/>
+        <v>667531.78999999992</v>
+      </c>
+      <c r="G299">
+        <f t="shared" si="0"/>
+        <v>686623.00000000023</v>
+      </c>
+      <c r="H299">
+        <f t="shared" si="0"/>
+        <v>536152.02000000025</v>
+      </c>
+      <c r="I299">
+        <f t="shared" si="0"/>
+        <v>691743.53</v>
+      </c>
+      <c r="J299">
+        <f t="shared" si="0"/>
+        <v>573251.49</v>
+      </c>
+      <c r="K299">
+        <f t="shared" si="0"/>
+        <v>648519.03000000014</v>
+      </c>
+      <c r="L299">
+        <f t="shared" si="0"/>
+        <v>663917.68999999971</v>
+      </c>
+      <c r="M299">
+        <f t="shared" si="0"/>
+        <v>594261.41</v>
+      </c>
+      <c r="N299">
+        <f t="shared" si="0"/>
+        <v>545469.44999999995</v>
+      </c>
+      <c r="O299">
+        <f t="shared" si="0"/>
+        <v>505083.35</v>
+      </c>
+      <c r="P299">
+        <f t="shared" si="0"/>
+        <v>472249.95000000019</v>
+      </c>
+      <c r="Q299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM299">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN299">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D37CA-6BA6-4568-ACB2-341A1391D80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF81AC-D83C-473E-9D16-24BDC42C949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -251,6 +251,9 @@
           <cell r="BL93">
             <v>67</v>
           </cell>
+          <cell r="BM93">
+            <v>28</v>
+          </cell>
         </row>
         <row r="94">
           <cell r="AY94">
@@ -295,6 +298,9 @@
           <cell r="BL94">
             <v>91</v>
           </cell>
+          <cell r="BM94">
+            <v>48</v>
+          </cell>
         </row>
         <row r="95">
           <cell r="AY95">
@@ -339,6 +345,9 @@
           <cell r="BL95">
             <v>185</v>
           </cell>
+          <cell r="BM95">
+            <v>95</v>
+          </cell>
         </row>
         <row r="96">
           <cell r="AY96">
@@ -383,6 +392,9 @@
           <cell r="BL96">
             <v>6</v>
           </cell>
+          <cell r="BM96">
+            <v>1</v>
+          </cell>
         </row>
         <row r="97">
           <cell r="AY97">
@@ -427,6 +439,9 @@
           <cell r="BL97">
             <v>36</v>
           </cell>
+          <cell r="BM97">
+            <v>15</v>
+          </cell>
         </row>
         <row r="98">
           <cell r="AY98">
@@ -471,6 +486,9 @@
           <cell r="BL98">
             <v>70</v>
           </cell>
+          <cell r="BM98">
+            <v>39</v>
+          </cell>
         </row>
         <row r="99">
           <cell r="AY99">
@@ -515,6 +533,9 @@
           <cell r="BL99">
             <v>1</v>
           </cell>
+          <cell r="BM99">
+            <v>1</v>
+          </cell>
         </row>
         <row r="100">
           <cell r="AY100">
@@ -559,6 +580,9 @@
           <cell r="BL100">
             <v>751</v>
           </cell>
+          <cell r="BM100">
+            <v>328</v>
+          </cell>
         </row>
         <row r="101">
           <cell r="AY101">
@@ -603,6 +627,9 @@
           <cell r="BL101">
             <v>561</v>
           </cell>
+          <cell r="BM101">
+            <v>283</v>
+          </cell>
         </row>
         <row r="102">
           <cell r="AY102">
@@ -647,6 +674,9 @@
           <cell r="BL102">
             <v>588</v>
           </cell>
+          <cell r="BM102">
+            <v>2</v>
+          </cell>
         </row>
         <row r="103">
           <cell r="BA103">
@@ -708,6 +738,9 @@
           <cell r="BL116">
             <v>0</v>
           </cell>
+          <cell r="BM116">
+            <v>0</v>
+          </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
@@ -756,7 +789,10 @@
             <v>0</v>
           </cell>
           <cell r="BL117">
-            <v>1010</v>
+            <v>1058</v>
+          </cell>
+          <cell r="BM117">
+            <v>0</v>
           </cell>
         </row>
         <row r="118">
@@ -808,6 +844,9 @@
           <cell r="BL118">
             <v>0</v>
           </cell>
+          <cell r="BM118">
+            <v>0</v>
+          </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
@@ -858,6 +897,9 @@
           <cell r="BL119">
             <v>0</v>
           </cell>
+          <cell r="BM119">
+            <v>0</v>
+          </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
@@ -906,7 +948,10 @@
             <v>0</v>
           </cell>
           <cell r="BL120">
-            <v>1041.4000000000001</v>
+            <v>1009.2</v>
+          </cell>
+          <cell r="BM120">
+            <v>0</v>
           </cell>
         </row>
         <row r="121">
@@ -956,7 +1001,10 @@
             <v>523.79</v>
           </cell>
           <cell r="BL121">
-            <v>444.05</v>
+            <v>441.75</v>
+          </cell>
+          <cell r="BM121">
+            <v>179.3</v>
           </cell>
         </row>
         <row r="122">
@@ -1008,6 +1056,9 @@
           <cell r="BL122">
             <v>545.91</v>
           </cell>
+          <cell r="BM122">
+            <v>174.4</v>
+          </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
@@ -1056,7 +1107,10 @@
             <v>963.68</v>
           </cell>
           <cell r="BL123">
-            <v>580.96</v>
+            <v>573.30999999999995</v>
+          </cell>
+          <cell r="BM123">
+            <v>284.18</v>
           </cell>
         </row>
         <row r="124">
@@ -1106,7 +1160,10 @@
             <v>51.99</v>
           </cell>
           <cell r="BL124">
-            <v>37.4</v>
+            <v>39.4</v>
+          </cell>
+          <cell r="BM124">
+            <v>46.6</v>
           </cell>
         </row>
         <row r="125">
@@ -1158,6 +1215,9 @@
           <cell r="BL125">
             <v>0</v>
           </cell>
+          <cell r="BM125">
+            <v>0</v>
+          </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
@@ -1208,6 +1268,9 @@
           <cell r="BL126">
             <v>95.9</v>
           </cell>
+          <cell r="BM126">
+            <v>0</v>
+          </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
@@ -1258,6 +1321,9 @@
           <cell r="BL127">
             <v>404.9</v>
           </cell>
+          <cell r="BM127">
+            <v>601.91999999999996</v>
+          </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
@@ -1308,6 +1374,9 @@
           <cell r="BL128">
             <v>4848</v>
           </cell>
+          <cell r="BM128">
+            <v>47.9</v>
+          </cell>
         </row>
         <row r="129">
           <cell r="A129" t="str">
@@ -1358,6 +1427,9 @@
           <cell r="BL129">
             <v>2100.16</v>
           </cell>
+          <cell r="BM129">
+            <v>786.72</v>
+          </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
@@ -1408,6 +1480,9 @@
           <cell r="BL130">
             <v>530.04</v>
           </cell>
+          <cell r="BM130">
+            <v>654.87</v>
+          </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
@@ -1458,6 +1533,9 @@
           <cell r="BL131">
             <v>569.79999999999995</v>
           </cell>
+          <cell r="BM131">
+            <v>1051.9100000000001</v>
+          </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
@@ -1506,7 +1584,10 @@
             <v>508.18</v>
           </cell>
           <cell r="BL132">
-            <v>86.4</v>
+            <v>86.7</v>
+          </cell>
+          <cell r="BM132">
+            <v>233.3</v>
           </cell>
         </row>
         <row r="133">
@@ -1558,6 +1639,9 @@
           <cell r="BL133">
             <v>758.05</v>
           </cell>
+          <cell r="BM133">
+            <v>329</v>
+          </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
@@ -1608,6 +1692,9 @@
           <cell r="BL134">
             <v>0</v>
           </cell>
+          <cell r="BM134">
+            <v>0</v>
+          </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
@@ -1658,6 +1745,9 @@
           <cell r="BL135">
             <v>0</v>
           </cell>
+          <cell r="BM135">
+            <v>0</v>
+          </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
@@ -1708,6 +1798,9 @@
           <cell r="BL136">
             <v>0</v>
           </cell>
+          <cell r="BM136">
+            <v>0</v>
+          </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
@@ -1758,6 +1851,9 @@
           <cell r="BL137">
             <v>0</v>
           </cell>
+          <cell r="BM137">
+            <v>0</v>
+          </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
@@ -1808,6 +1904,9 @@
           <cell r="BL138">
             <v>0</v>
           </cell>
+          <cell r="BM138">
+            <v>0</v>
+          </cell>
         </row>
         <row r="141">
           <cell r="A141" t="str">
@@ -1858,6 +1957,9 @@
           <cell r="BL141">
             <v>0</v>
           </cell>
+          <cell r="BM141">
+            <v>0</v>
+          </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
@@ -1908,6 +2010,9 @@
           <cell r="BL142">
             <v>292.04000000000002</v>
           </cell>
+          <cell r="BM142">
+            <v>63.88</v>
+          </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
@@ -1958,6 +2063,9 @@
           <cell r="BL143">
             <v>0</v>
           </cell>
+          <cell r="BM143">
+            <v>0</v>
+          </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
@@ -2008,6 +2116,9 @@
           <cell r="BL144">
             <v>0</v>
           </cell>
+          <cell r="BM144">
+            <v>0</v>
+          </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
@@ -2056,7 +2167,10 @@
             <v>0</v>
           </cell>
           <cell r="BL145">
-            <v>959.3</v>
+            <v>962.3</v>
+          </cell>
+          <cell r="BM145">
+            <v>392.7</v>
           </cell>
         </row>
         <row r="146">
@@ -2108,6 +2222,9 @@
           <cell r="BL146">
             <v>619.61</v>
           </cell>
+          <cell r="BM146">
+            <v>770.64</v>
+          </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
@@ -2158,6 +2275,9 @@
           <cell r="BL147">
             <v>991.28</v>
           </cell>
+          <cell r="BM147">
+            <v>452.97</v>
+          </cell>
         </row>
         <row r="148">
           <cell r="A148" t="str">
@@ -2206,7 +2326,10 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>505.85</v>
+            <v>491.91</v>
+          </cell>
+          <cell r="BM148">
+            <v>1068.73</v>
           </cell>
         </row>
         <row r="149">
@@ -2258,6 +2381,9 @@
           <cell r="BL149">
             <v>65.3</v>
           </cell>
+          <cell r="BM149">
+            <v>0</v>
+          </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
@@ -2308,6 +2434,9 @@
           <cell r="BL150">
             <v>0</v>
           </cell>
+          <cell r="BM150">
+            <v>0</v>
+          </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
@@ -2358,6 +2487,9 @@
           <cell r="BL151">
             <v>74.64</v>
           </cell>
+          <cell r="BM151">
+            <v>14</v>
+          </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
@@ -2408,6 +2540,9 @@
           <cell r="BL152">
             <v>0</v>
           </cell>
+          <cell r="BM152">
+            <v>0</v>
+          </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
@@ -2458,6 +2593,9 @@
           <cell r="BL153">
             <v>743.18</v>
           </cell>
+          <cell r="BM153">
+            <v>1084.5</v>
+          </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
@@ -2508,6 +2646,9 @@
           <cell r="BL154">
             <v>1244.1199999999999</v>
           </cell>
+          <cell r="BM154">
+            <v>59.9</v>
+          </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
@@ -2556,7 +2697,10 @@
             <v>275.2</v>
           </cell>
           <cell r="BL155">
-            <v>334.8</v>
+            <v>321.42</v>
+          </cell>
+          <cell r="BM155">
+            <v>681.73</v>
           </cell>
         </row>
         <row r="156">
@@ -2608,6 +2752,9 @@
           <cell r="BL156">
             <v>0</v>
           </cell>
+          <cell r="BM156">
+            <v>0</v>
+          </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
@@ -2656,7 +2803,10 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>667.68</v>
+            <v>652.88</v>
+          </cell>
+          <cell r="BM157">
+            <v>117.95</v>
           </cell>
         </row>
         <row r="158">
@@ -2706,7 +2856,10 @@
             <v>87.73</v>
           </cell>
           <cell r="BL158">
-            <v>266.25</v>
+            <v>261.3</v>
+          </cell>
+          <cell r="BM158">
+            <v>671.53</v>
           </cell>
         </row>
         <row r="159">
@@ -2758,6 +2911,9 @@
           <cell r="BL159">
             <v>0</v>
           </cell>
+          <cell r="BM159">
+            <v>0</v>
+          </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
@@ -2808,6 +2964,9 @@
           <cell r="BL160">
             <v>0</v>
           </cell>
+          <cell r="BM160">
+            <v>0</v>
+          </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
@@ -2858,6 +3017,9 @@
           <cell r="BL161">
             <v>0</v>
           </cell>
+          <cell r="BM161">
+            <v>0</v>
+          </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
@@ -2908,6 +3070,9 @@
           <cell r="BL162">
             <v>0</v>
           </cell>
+          <cell r="BM162">
+            <v>0</v>
+          </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
@@ -2958,6 +3123,9 @@
           <cell r="BL163">
             <v>0</v>
           </cell>
+          <cell r="BM163">
+            <v>0</v>
+          </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
@@ -3008,6 +3176,9 @@
           <cell r="BL166">
             <v>0</v>
           </cell>
+          <cell r="BM166">
+            <v>0</v>
+          </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
@@ -3058,6 +3229,9 @@
           <cell r="BL167">
             <v>2994.32</v>
           </cell>
+          <cell r="BM167">
+            <v>3.47</v>
+          </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
@@ -3108,6 +3282,9 @@
           <cell r="BL168">
             <v>0</v>
           </cell>
+          <cell r="BM168">
+            <v>0</v>
+          </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
@@ -3158,6 +3335,9 @@
           <cell r="BL169">
             <v>0</v>
           </cell>
+          <cell r="BM169">
+            <v>0</v>
+          </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
@@ -3208,6 +3388,9 @@
           <cell r="BL170">
             <v>699.1</v>
           </cell>
+          <cell r="BM170">
+            <v>178.7</v>
+          </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
@@ -3256,7 +3439,10 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>946.13</v>
+            <v>939.09</v>
+          </cell>
+          <cell r="BM171">
+            <v>291.19</v>
           </cell>
         </row>
         <row r="172">
@@ -3306,7 +3492,10 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>1296.3599999999999</v>
+            <v>1279.22</v>
+          </cell>
+          <cell r="BM172">
+            <v>1372.46</v>
           </cell>
         </row>
         <row r="173">
@@ -3356,7 +3545,10 @@
             <v>5782.77</v>
           </cell>
           <cell r="BL173">
-            <v>1352.67</v>
+            <v>1332.67</v>
+          </cell>
+          <cell r="BM173">
+            <v>964.27</v>
           </cell>
         </row>
         <row r="174">
@@ -3406,7 +3598,10 @@
             <v>360.6</v>
           </cell>
           <cell r="BL174">
-            <v>163.25</v>
+            <v>158.19999999999999</v>
+          </cell>
+          <cell r="BM174">
+            <v>379.57</v>
           </cell>
         </row>
         <row r="175">
@@ -3458,6 +3653,9 @@
           <cell r="BL175">
             <v>0</v>
           </cell>
+          <cell r="BM175">
+            <v>0</v>
+          </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
@@ -3508,6 +3706,9 @@
           <cell r="BL176">
             <v>209.83</v>
           </cell>
+          <cell r="BM176">
+            <v>25.8</v>
+          </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
@@ -3556,7 +3757,10 @@
             <v>159.9</v>
           </cell>
           <cell r="BL177">
-            <v>959.8</v>
+            <v>955.8</v>
+          </cell>
+          <cell r="BM177">
+            <v>0</v>
           </cell>
         </row>
         <row r="178">
@@ -3606,7 +3810,10 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>4804.8999999999996</v>
+            <v>4758.8500000000004</v>
+          </cell>
+          <cell r="BM178">
+            <v>4504.1099999999997</v>
           </cell>
         </row>
         <row r="179">
@@ -3656,7 +3863,10 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>2210.5100000000002</v>
+            <v>2196.5100000000002</v>
+          </cell>
+          <cell r="BM179">
+            <v>420.69</v>
           </cell>
         </row>
         <row r="180">
@@ -3706,7 +3916,10 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>603.72</v>
+            <v>602.27</v>
+          </cell>
+          <cell r="BM180">
+            <v>296.5</v>
           </cell>
         </row>
         <row r="181">
@@ -3758,6 +3971,9 @@
           <cell r="BL181">
             <v>0</v>
           </cell>
+          <cell r="BM181">
+            <v>-71.5</v>
+          </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
@@ -3806,7 +4022,10 @@
             <v>2160.71</v>
           </cell>
           <cell r="BL182">
-            <v>2207.09</v>
+            <v>2194.29</v>
+          </cell>
+          <cell r="BM182">
+            <v>646.1</v>
           </cell>
         </row>
         <row r="183">
@@ -3856,7 +4075,10 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>3423.97</v>
+            <v>3388.07</v>
+          </cell>
+          <cell r="BM183">
+            <v>1846.53</v>
           </cell>
         </row>
         <row r="184">
@@ -3908,6 +4130,9 @@
           <cell r="BL184">
             <v>0</v>
           </cell>
+          <cell r="BM184">
+            <v>0</v>
+          </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
@@ -3958,6 +4183,9 @@
           <cell r="BL185">
             <v>0</v>
           </cell>
+          <cell r="BM185">
+            <v>0</v>
+          </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
@@ -4008,6 +4236,9 @@
           <cell r="BL186">
             <v>0</v>
           </cell>
+          <cell r="BM186">
+            <v>0</v>
+          </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
@@ -4058,6 +4289,9 @@
           <cell r="BL187">
             <v>0</v>
           </cell>
+          <cell r="BM187">
+            <v>0</v>
+          </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
@@ -4108,6 +4342,9 @@
           <cell r="BL188">
             <v>0</v>
           </cell>
+          <cell r="BM188">
+            <v>0</v>
+          </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
@@ -4158,6 +4395,9 @@
           <cell r="BL191">
             <v>0</v>
           </cell>
+          <cell r="BM191">
+            <v>0</v>
+          </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
@@ -4208,6 +4448,9 @@
           <cell r="BL192">
             <v>0</v>
           </cell>
+          <cell r="BM192">
+            <v>0</v>
+          </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
@@ -4258,6 +4501,9 @@
           <cell r="BL193">
             <v>0</v>
           </cell>
+          <cell r="BM193">
+            <v>0</v>
+          </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
@@ -4308,6 +4554,9 @@
           <cell r="BL194">
             <v>0</v>
           </cell>
+          <cell r="BM194">
+            <v>0</v>
+          </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
@@ -4358,6 +4607,9 @@
           <cell r="BL195">
             <v>444.48</v>
           </cell>
+          <cell r="BM195">
+            <v>0</v>
+          </cell>
         </row>
         <row r="196">
           <cell r="A196" t="str">
@@ -4406,7 +4658,10 @@
             <v>90.22</v>
           </cell>
           <cell r="BL196">
-            <v>37.799999999999997</v>
+            <v>34.020000000000003</v>
+          </cell>
+          <cell r="BM196">
+            <v>0</v>
           </cell>
         </row>
         <row r="197">
@@ -4458,6 +4713,9 @@
           <cell r="BL197">
             <v>78.959999999999994</v>
           </cell>
+          <cell r="BM197">
+            <v>0.01</v>
+          </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
@@ -4506,7 +4764,10 @@
             <v>-4.82</v>
           </cell>
           <cell r="BL198">
-            <v>9.5</v>
+            <v>8.5399999999999991</v>
+          </cell>
+          <cell r="BM198">
+            <v>0</v>
           </cell>
         </row>
         <row r="199">
@@ -4558,6 +4819,9 @@
           <cell r="BL199">
             <v>0</v>
           </cell>
+          <cell r="BM199">
+            <v>0</v>
+          </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
@@ -4608,6 +4872,9 @@
           <cell r="BL200">
             <v>0</v>
           </cell>
+          <cell r="BM200">
+            <v>0</v>
+          </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
@@ -4658,6 +4925,9 @@
           <cell r="BL201">
             <v>5.56</v>
           </cell>
+          <cell r="BM201">
+            <v>0</v>
+          </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
@@ -4708,6 +4978,9 @@
           <cell r="BL202">
             <v>0</v>
           </cell>
+          <cell r="BM202">
+            <v>0</v>
+          </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
@@ -4758,6 +5031,9 @@
           <cell r="BL203">
             <v>0</v>
           </cell>
+          <cell r="BM203">
+            <v>0</v>
+          </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
@@ -4808,6 +5084,9 @@
           <cell r="BL204">
             <v>4.96</v>
           </cell>
+          <cell r="BM204">
+            <v>0</v>
+          </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
@@ -4858,6 +5137,9 @@
           <cell r="BL205">
             <v>0</v>
           </cell>
+          <cell r="BM205">
+            <v>0</v>
+          </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
@@ -4908,6 +5190,9 @@
           <cell r="BL206">
             <v>0</v>
           </cell>
+          <cell r="BM206">
+            <v>0</v>
+          </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
@@ -4958,6 +5243,9 @@
           <cell r="BL207">
             <v>115.09</v>
           </cell>
+          <cell r="BM207">
+            <v>0</v>
+          </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
@@ -5008,6 +5296,9 @@
           <cell r="BL208">
             <v>0</v>
           </cell>
+          <cell r="BM208">
+            <v>0</v>
+          </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
@@ -5058,6 +5349,9 @@
           <cell r="BL209">
             <v>0</v>
           </cell>
+          <cell r="BM209">
+            <v>0</v>
+          </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
@@ -5108,6 +5402,9 @@
           <cell r="BL210">
             <v>0</v>
           </cell>
+          <cell r="BM210">
+            <v>0</v>
+          </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
@@ -5158,6 +5455,9 @@
           <cell r="BL211">
             <v>0</v>
           </cell>
+          <cell r="BM211">
+            <v>0</v>
+          </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
@@ -5208,6 +5508,9 @@
           <cell r="BL212">
             <v>0</v>
           </cell>
+          <cell r="BM212">
+            <v>0</v>
+          </cell>
         </row>
         <row r="213">
           <cell r="A213" t="str">
@@ -5258,6 +5561,9 @@
           <cell r="BL213">
             <v>0</v>
           </cell>
+          <cell r="BM213">
+            <v>0</v>
+          </cell>
         </row>
         <row r="216">
           <cell r="A216" t="str">
@@ -5308,6 +5614,9 @@
           <cell r="BL216">
             <v>0</v>
           </cell>
+          <cell r="BM216">
+            <v>0</v>
+          </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
@@ -5358,6 +5667,9 @@
           <cell r="BL217">
             <v>0</v>
           </cell>
+          <cell r="BM217">
+            <v>0</v>
+          </cell>
         </row>
         <row r="218">
           <cell r="A218" t="str">
@@ -5408,6 +5720,9 @@
           <cell r="BL218">
             <v>0</v>
           </cell>
+          <cell r="BM218">
+            <v>0</v>
+          </cell>
         </row>
         <row r="219">
           <cell r="A219" t="str">
@@ -5458,6 +5773,9 @@
           <cell r="BL219">
             <v>0</v>
           </cell>
+          <cell r="BM219">
+            <v>0</v>
+          </cell>
         </row>
         <row r="220">
           <cell r="A220" t="str">
@@ -5508,6 +5826,9 @@
           <cell r="BL220">
             <v>0</v>
           </cell>
+          <cell r="BM220">
+            <v>95</v>
+          </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
@@ -5558,6 +5879,9 @@
           <cell r="BL221">
             <v>21.49</v>
           </cell>
+          <cell r="BM221">
+            <v>144.78</v>
+          </cell>
         </row>
         <row r="222">
           <cell r="A222" t="str">
@@ -5608,6 +5932,9 @@
           <cell r="BL222">
             <v>215.71</v>
           </cell>
+          <cell r="BM222">
+            <v>229.29</v>
+          </cell>
         </row>
         <row r="223">
           <cell r="A223" t="str">
@@ -5656,7 +5983,10 @@
             <v>788.08</v>
           </cell>
           <cell r="BL223">
-            <v>253.37</v>
+            <v>251.25</v>
+          </cell>
+          <cell r="BM223">
+            <v>95.3</v>
           </cell>
         </row>
         <row r="224">
@@ -5706,7 +6036,10 @@
             <v>349.1</v>
           </cell>
           <cell r="BL224">
-            <v>251.5</v>
+            <v>249.5</v>
+          </cell>
+          <cell r="BM224">
+            <v>-20.85</v>
           </cell>
         </row>
         <row r="225">
@@ -5758,6 +6091,9 @@
           <cell r="BL225">
             <v>0</v>
           </cell>
+          <cell r="BM225">
+            <v>0</v>
+          </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
@@ -5808,6 +6144,9 @@
           <cell r="BL226">
             <v>24</v>
           </cell>
+          <cell r="BM226">
+            <v>0</v>
+          </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
@@ -5858,6 +6197,9 @@
           <cell r="BL227">
             <v>0</v>
           </cell>
+          <cell r="BM227">
+            <v>219</v>
+          </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
@@ -5908,6 +6250,9 @@
           <cell r="BL228">
             <v>345.6</v>
           </cell>
+          <cell r="BM228">
+            <v>206</v>
+          </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
@@ -5956,7 +6301,10 @@
             <v>128.09</v>
           </cell>
           <cell r="BL229">
-            <v>572.65</v>
+            <v>576.95000000000005</v>
+          </cell>
+          <cell r="BM229">
+            <v>-27.8</v>
           </cell>
         </row>
         <row r="230">
@@ -6008,6 +6356,9 @@
           <cell r="BL230">
             <v>0</v>
           </cell>
+          <cell r="BM230">
+            <v>201.33</v>
+          </cell>
         </row>
         <row r="231">
           <cell r="A231" t="str">
@@ -6058,6 +6409,9 @@
           <cell r="BL231">
             <v>0</v>
           </cell>
+          <cell r="BM231">
+            <v>0</v>
+          </cell>
         </row>
         <row r="232">
           <cell r="A232" t="str">
@@ -6108,6 +6462,9 @@
           <cell r="BL232">
             <v>234.83</v>
           </cell>
+          <cell r="BM232">
+            <v>67.599999999999994</v>
+          </cell>
         </row>
         <row r="233">
           <cell r="A233" t="str">
@@ -6158,6 +6515,9 @@
           <cell r="BL233">
             <v>1925.14</v>
           </cell>
+          <cell r="BM233">
+            <v>15.28</v>
+          </cell>
         </row>
         <row r="234">
           <cell r="A234" t="str">
@@ -6208,6 +6568,9 @@
           <cell r="BL234">
             <v>0</v>
           </cell>
+          <cell r="BM234">
+            <v>0</v>
+          </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
@@ -6258,6 +6621,9 @@
           <cell r="BL235">
             <v>0</v>
           </cell>
+          <cell r="BM235">
+            <v>0</v>
+          </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
@@ -6308,6 +6674,9 @@
           <cell r="BL236">
             <v>0</v>
           </cell>
+          <cell r="BM236">
+            <v>0</v>
+          </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
@@ -6358,6 +6727,9 @@
           <cell r="BL237">
             <v>0</v>
           </cell>
+          <cell r="BM237">
+            <v>0</v>
+          </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
@@ -6408,6 +6780,9 @@
           <cell r="BL238">
             <v>0</v>
           </cell>
+          <cell r="BM238">
+            <v>0</v>
+          </cell>
         </row>
         <row r="241">
           <cell r="A241" t="str">
@@ -6458,6 +6833,9 @@
           <cell r="BL241">
             <v>0</v>
           </cell>
+          <cell r="BM241">
+            <v>0</v>
+          </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
@@ -6508,6 +6886,9 @@
           <cell r="BL242">
             <v>78.8</v>
           </cell>
+          <cell r="BM242">
+            <v>0</v>
+          </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
@@ -6558,6 +6939,9 @@
           <cell r="BL243">
             <v>0</v>
           </cell>
+          <cell r="BM243">
+            <v>0</v>
+          </cell>
         </row>
         <row r="244">
           <cell r="A244" t="str">
@@ -6608,6 +6992,9 @@
           <cell r="BL244">
             <v>0</v>
           </cell>
+          <cell r="BM244">
+            <v>0</v>
+          </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
@@ -6656,7 +7043,10 @@
             <v>5.3</v>
           </cell>
           <cell r="BL245">
-            <v>115.99</v>
+            <v>105.99</v>
+          </cell>
+          <cell r="BM245">
+            <v>0</v>
           </cell>
         </row>
         <row r="246">
@@ -6706,7 +7096,10 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>482.17</v>
+            <v>480.72</v>
+          </cell>
+          <cell r="BM246">
+            <v>543.62</v>
           </cell>
         </row>
         <row r="247">
@@ -6756,7 +7149,10 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>347.79</v>
+            <v>346.28</v>
+          </cell>
+          <cell r="BM247">
+            <v>429.01</v>
           </cell>
         </row>
         <row r="248">
@@ -6806,7 +7202,10 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>593.75</v>
+            <v>580.64</v>
+          </cell>
+          <cell r="BM248">
+            <v>595.09</v>
           </cell>
         </row>
         <row r="249">
@@ -6858,6 +7257,9 @@
           <cell r="BL249">
             <v>23.8</v>
           </cell>
+          <cell r="BM249">
+            <v>9.85</v>
+          </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
@@ -6908,6 +7310,9 @@
           <cell r="BL250">
             <v>0</v>
           </cell>
+          <cell r="BM250">
+            <v>0</v>
+          </cell>
         </row>
         <row r="251">
           <cell r="A251" t="str">
@@ -6958,6 +7363,9 @@
           <cell r="BL251">
             <v>55.34</v>
           </cell>
+          <cell r="BM251">
+            <v>13.95</v>
+          </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
@@ -7008,6 +7416,9 @@
           <cell r="BL252">
             <v>0</v>
           </cell>
+          <cell r="BM252">
+            <v>0</v>
+          </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
@@ -7058,6 +7469,9 @@
           <cell r="BL253">
             <v>299.39999999999998</v>
           </cell>
+          <cell r="BM253">
+            <v>237.3</v>
+          </cell>
         </row>
         <row r="254">
           <cell r="A254" t="str">
@@ -7106,7 +7520,10 @@
             <v>1217.27</v>
           </cell>
           <cell r="BL254">
-            <v>213.08</v>
+            <v>204.1</v>
+          </cell>
+          <cell r="BM254">
+            <v>507.3</v>
           </cell>
         </row>
         <row r="255">
@@ -7158,6 +7575,9 @@
           <cell r="BL255">
             <v>57.4</v>
           </cell>
+          <cell r="BM255">
+            <v>222.95</v>
+          </cell>
         </row>
         <row r="256">
           <cell r="A256" t="str">
@@ -7208,6 +7628,9 @@
           <cell r="BL256">
             <v>0</v>
           </cell>
+          <cell r="BM256">
+            <v>0</v>
+          </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
@@ -7256,7 +7679,10 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>482.65</v>
+            <v>479.45</v>
+          </cell>
+          <cell r="BM257">
+            <v>30.95</v>
           </cell>
         </row>
         <row r="258">
@@ -7308,6 +7734,9 @@
           <cell r="BL258">
             <v>576.54999999999995</v>
           </cell>
+          <cell r="BM258">
+            <v>47.7</v>
+          </cell>
         </row>
         <row r="259">
           <cell r="A259" t="str">
@@ -7358,6 +7787,9 @@
           <cell r="BL259">
             <v>0</v>
           </cell>
+          <cell r="BM259">
+            <v>0</v>
+          </cell>
         </row>
         <row r="260">
           <cell r="A260" t="str">
@@ -7408,6 +7840,9 @@
           <cell r="BL260">
             <v>0</v>
           </cell>
+          <cell r="BM260">
+            <v>0</v>
+          </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
@@ -7458,6 +7893,9 @@
           <cell r="BL261">
             <v>0</v>
           </cell>
+          <cell r="BM261">
+            <v>0</v>
+          </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
@@ -7508,6 +7946,9 @@
           <cell r="BL262">
             <v>0</v>
           </cell>
+          <cell r="BM262">
+            <v>0</v>
+          </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
@@ -7558,6 +7999,9 @@
           <cell r="BL263">
             <v>0</v>
           </cell>
+          <cell r="BM263">
+            <v>0</v>
+          </cell>
         </row>
         <row r="266">
           <cell r="A266" t="str">
@@ -7608,6 +8052,9 @@
           <cell r="BL266">
             <v>0</v>
           </cell>
+          <cell r="BM266">
+            <v>0</v>
+          </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
@@ -7658,6 +8105,9 @@
           <cell r="BL267">
             <v>0</v>
           </cell>
+          <cell r="BM267">
+            <v>0</v>
+          </cell>
         </row>
         <row r="268">
           <cell r="A268" t="str">
@@ -7708,6 +8158,9 @@
           <cell r="BL268">
             <v>0</v>
           </cell>
+          <cell r="BM268">
+            <v>0</v>
+          </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
@@ -7758,6 +8211,9 @@
           <cell r="BL269">
             <v>0</v>
           </cell>
+          <cell r="BM269">
+            <v>0</v>
+          </cell>
         </row>
         <row r="270">
           <cell r="A270" t="str">
@@ -7808,6 +8264,9 @@
           <cell r="BL270">
             <v>0</v>
           </cell>
+          <cell r="BM270">
+            <v>0</v>
+          </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
@@ -7858,6 +8317,9 @@
           <cell r="BL271">
             <v>0</v>
           </cell>
+          <cell r="BM271">
+            <v>0</v>
+          </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
@@ -7908,6 +8370,9 @@
           <cell r="BL272">
             <v>0.01</v>
           </cell>
+          <cell r="BM272">
+            <v>0.01</v>
+          </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
@@ -7958,6 +8423,9 @@
           <cell r="BL273">
             <v>0</v>
           </cell>
+          <cell r="BM273">
+            <v>0</v>
+          </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
@@ -8008,6 +8476,9 @@
           <cell r="BL274">
             <v>0</v>
           </cell>
+          <cell r="BM274">
+            <v>0</v>
+          </cell>
         </row>
         <row r="275">
           <cell r="A275" t="str">
@@ -8058,6 +8529,9 @@
           <cell r="BL275">
             <v>0</v>
           </cell>
+          <cell r="BM275">
+            <v>0</v>
+          </cell>
         </row>
         <row r="276">
           <cell r="A276" t="str">
@@ -8108,6 +8582,9 @@
           <cell r="BL276">
             <v>0</v>
           </cell>
+          <cell r="BM276">
+            <v>0</v>
+          </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
@@ -8158,6 +8635,9 @@
           <cell r="BL277">
             <v>0</v>
           </cell>
+          <cell r="BM277">
+            <v>0</v>
+          </cell>
         </row>
         <row r="278">
           <cell r="A278" t="str">
@@ -8208,6 +8688,9 @@
           <cell r="BL278">
             <v>0</v>
           </cell>
+          <cell r="BM278">
+            <v>0</v>
+          </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
@@ -8258,6 +8741,9 @@
           <cell r="BL279">
             <v>0</v>
           </cell>
+          <cell r="BM279">
+            <v>0</v>
+          </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
@@ -8308,6 +8794,9 @@
           <cell r="BL280">
             <v>0</v>
           </cell>
+          <cell r="BM280">
+            <v>0</v>
+          </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
@@ -8358,6 +8847,9 @@
           <cell r="BL281">
             <v>0</v>
           </cell>
+          <cell r="BM281">
+            <v>0</v>
+          </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
@@ -8408,6 +8900,9 @@
           <cell r="BL282">
             <v>0</v>
           </cell>
+          <cell r="BM282">
+            <v>0</v>
+          </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
@@ -8458,6 +8953,9 @@
           <cell r="BL283">
             <v>0</v>
           </cell>
+          <cell r="BM283">
+            <v>0</v>
+          </cell>
         </row>
         <row r="284">
           <cell r="A284" t="str">
@@ -8508,6 +9006,9 @@
           <cell r="BL284">
             <v>0</v>
           </cell>
+          <cell r="BM284">
+            <v>0</v>
+          </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
@@ -8558,6 +9059,9 @@
           <cell r="BL285">
             <v>0</v>
           </cell>
+          <cell r="BM285">
+            <v>0</v>
+          </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
@@ -8608,6 +9112,9 @@
           <cell r="BL286">
             <v>0</v>
           </cell>
+          <cell r="BM286">
+            <v>0</v>
+          </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
@@ -8658,6 +9165,9 @@
           <cell r="BL287">
             <v>0</v>
           </cell>
+          <cell r="BM287">
+            <v>0</v>
+          </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
@@ -8708,6 +9218,9 @@
           <cell r="BL288">
             <v>0</v>
           </cell>
+          <cell r="BM288">
+            <v>0</v>
+          </cell>
         </row>
         <row r="291">
           <cell r="A291" t="str">
@@ -8758,6 +9271,9 @@
           <cell r="BL291">
             <v>0</v>
           </cell>
+          <cell r="BM291">
+            <v>0</v>
+          </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
@@ -8806,7 +9322,10 @@
             <v>10911.5</v>
           </cell>
           <cell r="BL292">
-            <v>24876.79</v>
+            <v>24871.29</v>
+          </cell>
+          <cell r="BM292">
+            <v>8544.1200000000008</v>
           </cell>
         </row>
         <row r="293">
@@ -8858,6 +9377,9 @@
           <cell r="BL293">
             <v>0</v>
           </cell>
+          <cell r="BM293">
+            <v>0</v>
+          </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
@@ -8908,6 +9430,9 @@
           <cell r="BL294">
             <v>0</v>
           </cell>
+          <cell r="BM294">
+            <v>0</v>
+          </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
@@ -8956,7 +9481,10 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>5779.94</v>
+            <v>5789.04</v>
+          </cell>
+          <cell r="BM295">
+            <v>1728.8</v>
           </cell>
         </row>
         <row r="296">
@@ -9006,7 +9534,10 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>9705.77</v>
+            <v>9659.8799999999992</v>
+          </cell>
+          <cell r="BM296">
+            <v>3250.35</v>
           </cell>
         </row>
         <row r="297">
@@ -9056,7 +9587,10 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>9755.67</v>
+            <v>9559.2900000000009</v>
+          </cell>
+          <cell r="BM297">
+            <v>2693.16</v>
           </cell>
         </row>
         <row r="298">
@@ -9106,7 +9640,10 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>15322.7</v>
+            <v>15228.52</v>
+          </cell>
+          <cell r="BM298">
+            <v>4222.55</v>
           </cell>
         </row>
         <row r="299">
@@ -9156,7 +9693,10 @@
             <v>819.93</v>
           </cell>
           <cell r="BL299">
-            <v>1161.1600000000001</v>
+            <v>1144.96</v>
+          </cell>
+          <cell r="BM299">
+            <v>482.15</v>
           </cell>
         </row>
         <row r="300">
@@ -9208,6 +9748,9 @@
           <cell r="BL300">
             <v>0</v>
           </cell>
+          <cell r="BM300">
+            <v>0</v>
+          </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
@@ -9256,7 +9799,10 @@
             <v>1498.34</v>
           </cell>
           <cell r="BL301">
-            <v>5223.99</v>
+            <v>5219.09</v>
+          </cell>
+          <cell r="BM301">
+            <v>228.79</v>
           </cell>
         </row>
         <row r="302">
@@ -9308,6 +9854,9 @@
           <cell r="BL302">
             <v>3277.5</v>
           </cell>
+          <cell r="BM302">
+            <v>399.8</v>
+          </cell>
         </row>
         <row r="303">
           <cell r="A303" t="str">
@@ -9356,7 +9905,10 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>109524.39</v>
+            <v>109105.36</v>
+          </cell>
+          <cell r="BM303">
+            <v>53432.43</v>
           </cell>
         </row>
         <row r="304">
@@ -9406,7 +9958,10 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>9043.35</v>
+            <v>8645.2900000000009</v>
+          </cell>
+          <cell r="BM304">
+            <v>6180.9</v>
           </cell>
         </row>
         <row r="305">
@@ -9456,7 +10011,10 @@
             <v>3782.99</v>
           </cell>
           <cell r="BL305">
-            <v>783.75</v>
+            <v>773.75</v>
+          </cell>
+          <cell r="BM305">
+            <v>1366.85</v>
           </cell>
         </row>
         <row r="306">
@@ -9508,6 +10066,9 @@
           <cell r="BL306">
             <v>433</v>
           </cell>
+          <cell r="BM306">
+            <v>1134.8</v>
+          </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
@@ -9556,7 +10117,10 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>5353.31</v>
+            <v>5292.88</v>
+          </cell>
+          <cell r="BM307">
+            <v>2161.36</v>
           </cell>
         </row>
         <row r="308">
@@ -9606,7 +10170,10 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>29217.46</v>
+            <v>29215.86</v>
+          </cell>
+          <cell r="BM308">
+            <v>11360.36</v>
           </cell>
         </row>
         <row r="309">
@@ -9658,6 +10225,9 @@
           <cell r="BL309">
             <v>0</v>
           </cell>
+          <cell r="BM309">
+            <v>0</v>
+          </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
@@ -9708,6 +10278,9 @@
           <cell r="BL310">
             <v>0</v>
           </cell>
+          <cell r="BM310">
+            <v>7.9</v>
+          </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
@@ -9758,6 +10331,9 @@
           <cell r="BL311">
             <v>0</v>
           </cell>
+          <cell r="BM311">
+            <v>0</v>
+          </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
@@ -9808,6 +10384,9 @@
           <cell r="BL312">
             <v>0</v>
           </cell>
+          <cell r="BM312">
+            <v>0</v>
+          </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
@@ -9858,6 +10437,9 @@
           <cell r="BL313">
             <v>0</v>
           </cell>
+          <cell r="BM313">
+            <v>0</v>
+          </cell>
         </row>
         <row r="316">
           <cell r="A316" t="str">
@@ -9908,6 +10490,9 @@
           <cell r="BL316">
             <v>0</v>
           </cell>
+          <cell r="BM316">
+            <v>0</v>
+          </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
@@ -9958,6 +10543,9 @@
           <cell r="BL317">
             <v>6246.19</v>
           </cell>
+          <cell r="BM317">
+            <v>1482.01</v>
+          </cell>
         </row>
         <row r="318">
           <cell r="A318" t="str">
@@ -10008,6 +10596,9 @@
           <cell r="BL318">
             <v>0</v>
           </cell>
+          <cell r="BM318">
+            <v>0</v>
+          </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
@@ -10058,6 +10649,9 @@
           <cell r="BL319">
             <v>0</v>
           </cell>
+          <cell r="BM319">
+            <v>0</v>
+          </cell>
         </row>
         <row r="320">
           <cell r="A320" t="str">
@@ -10106,7 +10700,10 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>6642.2</v>
+            <v>6632.2</v>
+          </cell>
+          <cell r="BM320">
+            <v>3774.38</v>
           </cell>
         </row>
         <row r="321">
@@ -10156,7 +10753,10 @@
             <v>2748.05</v>
           </cell>
           <cell r="BL321">
-            <v>4725.95</v>
+            <v>4704.99</v>
+          </cell>
+          <cell r="BM321">
+            <v>1352.37</v>
           </cell>
         </row>
         <row r="322">
@@ -10206,7 +10806,10 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>3883.83</v>
+            <v>3870.6</v>
+          </cell>
+          <cell r="BM322">
+            <v>3451.95</v>
           </cell>
         </row>
         <row r="323">
@@ -10256,7 +10859,10 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>12189.58</v>
+            <v>11596.46</v>
+          </cell>
+          <cell r="BM323">
+            <v>1851.63</v>
           </cell>
         </row>
         <row r="324">
@@ -10306,7 +10912,10 @@
             <v>630.75</v>
           </cell>
           <cell r="BL324">
-            <v>401.36</v>
+            <v>398.36</v>
+          </cell>
+          <cell r="BM324">
+            <v>385.95</v>
           </cell>
         </row>
         <row r="325">
@@ -10358,6 +10967,9 @@
           <cell r="BL325">
             <v>0</v>
           </cell>
+          <cell r="BM325">
+            <v>0</v>
+          </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
@@ -10406,7 +11018,10 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>3183.25</v>
+            <v>3172.3</v>
+          </cell>
+          <cell r="BM326">
+            <v>376.7</v>
           </cell>
         </row>
         <row r="327">
@@ -10456,7 +11071,10 @@
             <v>3384.9</v>
           </cell>
           <cell r="BL327">
-            <v>933.45</v>
+            <v>929.45</v>
+          </cell>
+          <cell r="BM327">
+            <v>954.19</v>
           </cell>
         </row>
         <row r="328">
@@ -10506,7 +11124,10 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>32367.51</v>
+            <v>32127.45</v>
+          </cell>
+          <cell r="BM328">
+            <v>13334.11</v>
           </cell>
         </row>
         <row r="329">
@@ -10556,7 +11177,10 @@
             <v>4790.9799999999996</v>
           </cell>
           <cell r="BL329">
-            <v>5632.88</v>
+            <v>5550.91</v>
+          </cell>
+          <cell r="BM329">
+            <v>4141.5600000000004</v>
           </cell>
         </row>
         <row r="330">
@@ -10606,7 +11230,10 @@
             <v>2022.35</v>
           </cell>
           <cell r="BL330">
-            <v>2400.84</v>
+            <v>2377.84</v>
+          </cell>
+          <cell r="BM330">
+            <v>304.72000000000003</v>
           </cell>
         </row>
         <row r="331">
@@ -10658,6 +11285,9 @@
           <cell r="BL331">
             <v>3520.64</v>
           </cell>
+          <cell r="BM331">
+            <v>856.19</v>
+          </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
@@ -10706,7 +11336,10 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>3953.57</v>
+            <v>3929.27</v>
+          </cell>
+          <cell r="BM332">
+            <v>1687.77</v>
           </cell>
         </row>
         <row r="333">
@@ -10756,7 +11389,10 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>9696.7800000000007</v>
+            <v>9688.98</v>
+          </cell>
+          <cell r="BM333">
+            <v>3344.29</v>
           </cell>
         </row>
         <row r="334">
@@ -10808,6 +11444,9 @@
           <cell r="BL334">
             <v>0</v>
           </cell>
+          <cell r="BM334">
+            <v>0</v>
+          </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
@@ -10858,6 +11497,9 @@
           <cell r="BL335">
             <v>0</v>
           </cell>
+          <cell r="BM335">
+            <v>0</v>
+          </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
@@ -10908,6 +11550,9 @@
           <cell r="BL336">
             <v>0</v>
           </cell>
+          <cell r="BM336">
+            <v>0</v>
+          </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
@@ -10958,6 +11603,9 @@
           <cell r="BL337">
             <v>0</v>
           </cell>
+          <cell r="BM337">
+            <v>0</v>
+          </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
@@ -11008,6 +11656,9 @@
           <cell r="BL338">
             <v>0</v>
           </cell>
+          <cell r="BM338">
+            <v>0</v>
+          </cell>
         </row>
         <row r="341">
           <cell r="A341" t="str">
@@ -11058,6 +11709,9 @@
           <cell r="BL341">
             <v>0</v>
           </cell>
+          <cell r="BM341">
+            <v>0</v>
+          </cell>
         </row>
         <row r="342">
           <cell r="A342" t="str">
@@ -11106,7 +11760,10 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>4491.96</v>
+            <v>4398.3599999999997</v>
+          </cell>
+          <cell r="BM342">
+            <v>0</v>
           </cell>
         </row>
         <row r="343">
@@ -11158,6 +11815,9 @@
           <cell r="BL343">
             <v>0</v>
           </cell>
+          <cell r="BM343">
+            <v>0</v>
+          </cell>
         </row>
         <row r="344">
           <cell r="A344" t="str">
@@ -11208,6 +11868,9 @@
           <cell r="BL344">
             <v>0</v>
           </cell>
+          <cell r="BM344">
+            <v>0</v>
+          </cell>
         </row>
         <row r="345">
           <cell r="A345" t="str">
@@ -11256,7 +11919,10 @@
             <v>1706.35</v>
           </cell>
           <cell r="BL345">
-            <v>4092.26</v>
+            <v>4088.06</v>
+          </cell>
+          <cell r="BM345">
+            <v>0</v>
           </cell>
         </row>
         <row r="346">
@@ -11306,7 +11972,10 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>3180.69</v>
+            <v>3164.56</v>
+          </cell>
+          <cell r="BM346">
+            <v>-19.899999999999999</v>
           </cell>
         </row>
         <row r="347">
@@ -11356,7 +12025,10 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>10828.19</v>
+            <v>10864.67</v>
+          </cell>
+          <cell r="BM347">
+            <v>0</v>
           </cell>
         </row>
         <row r="348">
@@ -11406,7 +12078,10 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>10434.879999999999</v>
+            <v>10356.299999999999</v>
+          </cell>
+          <cell r="BM348">
+            <v>85.35</v>
           </cell>
         </row>
         <row r="349">
@@ -11456,7 +12131,10 @@
             <v>1478.26</v>
           </cell>
           <cell r="BL349">
-            <v>716.95</v>
+            <v>698.55</v>
+          </cell>
+          <cell r="BM349">
+            <v>0</v>
           </cell>
         </row>
         <row r="350">
@@ -11508,6 +12186,9 @@
           <cell r="BL350">
             <v>0</v>
           </cell>
+          <cell r="BM350">
+            <v>0</v>
+          </cell>
         </row>
         <row r="351">
           <cell r="A351" t="str">
@@ -11556,7 +12237,10 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>1438.9</v>
+            <v>1435.9</v>
+          </cell>
+          <cell r="BM351">
+            <v>0</v>
           </cell>
         </row>
         <row r="352">
@@ -11606,7 +12290,10 @@
             <v>2460.85</v>
           </cell>
           <cell r="BL352">
-            <v>618.35</v>
+            <v>598.35</v>
+          </cell>
+          <cell r="BM352">
+            <v>0</v>
           </cell>
         </row>
         <row r="353">
@@ -11656,7 +12343,10 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>26068.95</v>
+            <v>25275.11</v>
+          </cell>
+          <cell r="BM353">
+            <v>-135.80000000000001</v>
           </cell>
         </row>
         <row r="354">
@@ -11706,7 +12396,10 @@
             <v>6679.21</v>
           </cell>
           <cell r="BL354">
-            <v>5420.08</v>
+            <v>5383.38</v>
+          </cell>
+          <cell r="BM354">
+            <v>-27.9</v>
           </cell>
         </row>
         <row r="355">
@@ -11756,7 +12449,10 @@
             <v>3019.73</v>
           </cell>
           <cell r="BL355">
-            <v>1691.66</v>
+            <v>1675.86</v>
+          </cell>
+          <cell r="BM355">
+            <v>0</v>
           </cell>
         </row>
         <row r="356">
@@ -11806,7 +12502,10 @@
             <v>291.7</v>
           </cell>
           <cell r="BL356">
-            <v>1517.4</v>
+            <v>1479.4</v>
+          </cell>
+          <cell r="BM356">
+            <v>0</v>
           </cell>
         </row>
         <row r="357">
@@ -11856,7 +12555,10 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>4220.72</v>
+            <v>4228.5600000000004</v>
+          </cell>
+          <cell r="BM357">
+            <v>0</v>
           </cell>
         </row>
         <row r="358">
@@ -11906,7 +12608,10 @@
             <v>18146.46</v>
           </cell>
           <cell r="BL358">
-            <v>22736.11</v>
+            <v>22534.81</v>
+          </cell>
+          <cell r="BM358">
+            <v>0</v>
           </cell>
         </row>
         <row r="359">
@@ -11958,6 +12663,9 @@
           <cell r="BL359">
             <v>0</v>
           </cell>
+          <cell r="BM359">
+            <v>0</v>
+          </cell>
         </row>
         <row r="360">
           <cell r="A360" t="str">
@@ -12008,6 +12716,9 @@
           <cell r="BL360">
             <v>0</v>
           </cell>
+          <cell r="BM360">
+            <v>0</v>
+          </cell>
         </row>
         <row r="361">
           <cell r="A361" t="str">
@@ -12058,6 +12769,9 @@
           <cell r="BL361">
             <v>0</v>
           </cell>
+          <cell r="BM361">
+            <v>0</v>
+          </cell>
         </row>
         <row r="362">
           <cell r="A362" t="str">
@@ -12108,6 +12822,9 @@
           <cell r="BL362">
             <v>0</v>
           </cell>
+          <cell r="BM362">
+            <v>0</v>
+          </cell>
         </row>
         <row r="363">
           <cell r="A363" t="str">
@@ -12156,6 +12873,9 @@
             <v>0</v>
           </cell>
           <cell r="BL363">
+            <v>0</v>
+          </cell>
+          <cell r="BM363">
             <v>0</v>
           </cell>
         </row>
@@ -13065,7 +13785,7 @@
         <v>67</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -13253,7 +13973,7 @@
         <v>91</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -13441,7 +14161,7 @@
         <v>185</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -13629,7 +14349,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -13817,7 +14537,7 @@
         <v>36</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -14005,7 +14725,7 @@
         <v>70</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -14193,7 +14913,7 @@
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -14381,7 +15101,7 @@
         <v>751</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -14569,7 +15289,7 @@
         <v>561</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -14757,7 +15477,7 @@
         <v>588</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -15217,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1010</v>
+        <v>1058</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -15448,7 +16168,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1041.4000000000001</v>
+        <v>1009.2</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -15525,10 +16245,10 @@
         <v>523.79</v>
       </c>
       <c r="P23">
-        <v>444.05</v>
+        <v>441.75</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>179.3</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -15605,7 +16325,7 @@
         <v>545.91</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>174.4</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -15679,10 +16399,10 @@
         <v>963.68</v>
       </c>
       <c r="P25">
-        <v>580.96</v>
+        <v>573.30999999999995</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>284.18</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -15756,10 +16476,10 @@
         <v>51.99</v>
       </c>
       <c r="P26">
-        <v>37.4</v>
+        <v>39.4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -15990,7 +16710,7 @@
         <v>404.9</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>601.91999999999996</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -16067,7 +16787,7 @@
         <v>4848</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>47.9</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -16144,7 +16864,7 @@
         <v>2100.16</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>786.72</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -16221,7 +16941,7 @@
         <v>530.04</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>654.87</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -16298,7 +17018,7 @@
         <v>569.79999999999995</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1051.9100000000001</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -16372,10 +17092,10 @@
         <v>508.18</v>
       </c>
       <c r="P34">
-        <v>86.4</v>
+        <v>86.7</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>233.3</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -16452,7 +17172,7 @@
         <v>758.05</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -17145,7 +17865,7 @@
         <v>292.04000000000002</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>63.88</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -17373,10 +18093,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>959.3</v>
+        <v>962.3</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>392.7</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -17453,7 +18173,7 @@
         <v>619.61</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>770.64</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -17530,7 +18250,7 @@
         <v>991.28</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>452.97</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -17604,10 +18324,10 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>505.85</v>
+        <v>491.91</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1068.73</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -17838,7 +18558,7 @@
         <v>74.64</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -17992,7 +18712,7 @@
         <v>743.18</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>1084.5</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -18069,7 +18789,7 @@
         <v>1244.1199999999999</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>59.9</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -18143,10 +18863,10 @@
         <v>275.2</v>
       </c>
       <c r="P57">
-        <v>334.8</v>
+        <v>321.42</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>681.73</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -18297,10 +19017,10 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>667.68</v>
+        <v>652.88</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>117.95</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -18374,10 +19094,10 @@
         <v>87.73</v>
       </c>
       <c r="P60">
-        <v>266.25</v>
+        <v>261.3</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>671.53</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -19070,7 +19790,7 @@
         <v>2994.32</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -19301,7 +20021,7 @@
         <v>699.1</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>178.7</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -19375,10 +20095,10 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>946.13</v>
+        <v>939.09</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>291.19</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19452,10 +20172,10 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>1296.3599999999999</v>
+        <v>1279.22</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1372.46</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -19529,10 +20249,10 @@
         <v>5782.77</v>
       </c>
       <c r="P75">
-        <v>1352.67</v>
+        <v>1332.67</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>964.27</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -19606,10 +20326,10 @@
         <v>360.6</v>
       </c>
       <c r="P76">
-        <v>163.25</v>
+        <v>158.19999999999999</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>379.57</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -19763,7 +20483,7 @@
         <v>209.83</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -19837,7 +20557,7 @@
         <v>159.9</v>
       </c>
       <c r="P79">
-        <v>959.8</v>
+        <v>955.8</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -19914,10 +20634,10 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>4804.8999999999996</v>
+        <v>4758.8500000000004</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4504.1099999999997</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -19991,10 +20711,10 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>2210.5100000000002</v>
+        <v>2196.5100000000002</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>420.69</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -20068,10 +20788,10 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>603.72</v>
+        <v>602.27</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>296.5</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -20148,7 +20868,7 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>-71.5</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -20222,10 +20942,10 @@
         <v>2160.71</v>
       </c>
       <c r="P84">
-        <v>2207.09</v>
+        <v>2194.29</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>646.1</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -20299,10 +21019,10 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>3423.97</v>
+        <v>3388.07</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1846.53</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -21300,7 +22020,7 @@
         <v>90.22</v>
       </c>
       <c r="P98">
-        <v>37.799999999999997</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -21380,7 +22100,7 @@
         <v>78.959999999999994</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -21454,7 +22174,7 @@
         <v>-4.82</v>
       </c>
       <c r="P100">
-        <v>9.5</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -23151,7 +23871,7 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -23228,7 +23948,7 @@
         <v>21.49</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>144.78</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -23305,7 +24025,7 @@
         <v>215.71</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>229.29</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -23379,10 +24099,10 @@
         <v>788.08</v>
       </c>
       <c r="P125">
-        <v>253.37</v>
+        <v>251.25</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -23456,10 +24176,10 @@
         <v>349.1</v>
       </c>
       <c r="P126">
-        <v>251.5</v>
+        <v>249.5</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>-20.85</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -23690,7 +24410,7 @@
         <v>0</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -23767,7 +24487,7 @@
         <v>345.6</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -23841,10 +24561,10 @@
         <v>128.09</v>
       </c>
       <c r="P131">
-        <v>572.65</v>
+        <v>576.95000000000005</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>-27.8</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -23921,7 +24641,7 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>201.33</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -24075,7 +24795,7 @@
         <v>234.83</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -24152,7 +24872,7 @@
         <v>1925.14</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -25073,7 +25793,7 @@
         <v>5.3</v>
       </c>
       <c r="P147">
-        <v>115.99</v>
+        <v>105.99</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -25150,10 +25870,10 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>482.17</v>
+        <v>480.72</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>543.62</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -25227,10 +25947,10 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>347.79</v>
+        <v>346.28</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>429.01</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -25304,10 +26024,10 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>593.75</v>
+        <v>580.64</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>595.09</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -25384,7 +26104,7 @@
         <v>23.8</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -25538,7 +26258,7 @@
         <v>55.34</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>13.95</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -25692,7 +26412,7 @@
         <v>299.39999999999998</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>237.3</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -25766,10 +26486,10 @@
         <v>1217.27</v>
       </c>
       <c r="P156">
-        <v>213.08</v>
+        <v>204.1</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>507.3</v>
       </c>
       <c r="R156">
         <v>0</v>
@@ -25846,7 +26566,7 @@
         <v>57.4</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>222.95</v>
       </c>
       <c r="R157">
         <v>0</v>
@@ -25997,10 +26717,10 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>482.65</v>
+        <v>479.45</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>30.95</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -26077,7 +26797,7 @@
         <v>576.54999999999995</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>47.7</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -27155,7 +27875,7 @@
         <v>0.01</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -28692,10 +29412,10 @@
         <v>10911.5</v>
       </c>
       <c r="P194">
-        <v>24876.79</v>
+        <v>24871.29</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>8544.1200000000008</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -28923,10 +29643,10 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>5779.94</v>
+        <v>5789.04</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>1728.8</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -29000,10 +29720,10 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>9705.77</v>
+        <v>9659.8799999999992</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>3250.35</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -29077,10 +29797,10 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>9755.67</v>
+        <v>9559.2900000000009</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>2693.16</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -29154,10 +29874,10 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>15322.7</v>
+        <v>15228.52</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4222.55</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -29231,10 +29951,10 @@
         <v>819.93</v>
       </c>
       <c r="P201">
-        <v>1161.1600000000001</v>
+        <v>1144.96</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>482.15</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -29385,10 +30105,10 @@
         <v>1498.34</v>
       </c>
       <c r="P203">
-        <v>5223.99</v>
+        <v>5219.09</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>228.79</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -29465,7 +30185,7 @@
         <v>3277.5</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>399.8</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -29539,10 +30259,10 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>109524.39</v>
+        <v>109105.36</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>53432.43</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -29616,10 +30336,10 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>9043.35</v>
+        <v>8645.2900000000009</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>6180.9</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -29693,10 +30413,10 @@
         <v>3782.99</v>
       </c>
       <c r="P207">
-        <v>783.75</v>
+        <v>773.75</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>1366.85</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -29773,7 +30493,7 @@
         <v>433</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>1134.8</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -29847,10 +30567,10 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>5353.31</v>
+        <v>5292.88</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>2161.36</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -29924,10 +30644,10 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>29217.46</v>
+        <v>29215.86</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>11360.36</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -30081,7 +30801,7 @@
         <v>0</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -30620,7 +31340,7 @@
         <v>6246.19</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>1482.01</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -30848,10 +31568,10 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>6642.2</v>
+        <v>6632.2</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>3774.38</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -30925,10 +31645,10 @@
         <v>2748.05</v>
       </c>
       <c r="P223">
-        <v>4725.95</v>
+        <v>4704.99</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>1352.37</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -31002,10 +31722,10 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>3883.83</v>
+        <v>3870.6</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>3451.95</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -31079,10 +31799,10 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>12189.58</v>
+        <v>11596.46</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>1851.63</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -31156,10 +31876,10 @@
         <v>630.75</v>
       </c>
       <c r="P226">
-        <v>401.36</v>
+        <v>398.36</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>385.95</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -31310,10 +32030,10 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>3183.25</v>
+        <v>3172.3</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>376.7</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -31387,10 +32107,10 @@
         <v>3384.9</v>
       </c>
       <c r="P229">
-        <v>933.45</v>
+        <v>929.45</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>954.19</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -31464,10 +32184,10 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>32367.51</v>
+        <v>32127.45</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>13334.11</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -31541,10 +32261,10 @@
         <v>4790.9799999999996</v>
       </c>
       <c r="P231">
-        <v>5632.88</v>
+        <v>5550.91</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>4141.5600000000004</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -31618,10 +32338,10 @@
         <v>2022.35</v>
       </c>
       <c r="P232">
-        <v>2400.84</v>
+        <v>2377.84</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>304.72000000000003</v>
       </c>
       <c r="R232">
         <v>0</v>
@@ -31698,7 +32418,7 @@
         <v>3520.64</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>856.19</v>
       </c>
       <c r="R233">
         <v>0</v>
@@ -31772,10 +32492,10 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>3953.57</v>
+        <v>3929.27</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>1687.77</v>
       </c>
       <c r="R234">
         <v>0</v>
@@ -31849,10 +32569,10 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>9696.7800000000007</v>
+        <v>9688.98</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>3344.29</v>
       </c>
       <c r="R235">
         <v>0</v>
@@ -32542,7 +33262,7 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>4491.96</v>
+        <v>4398.3599999999997</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -32773,7 +33493,7 @@
         <v>1706.35</v>
       </c>
       <c r="P247">
-        <v>4092.26</v>
+        <v>4088.06</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -32850,10 +33570,10 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>3180.69</v>
+        <v>3164.56</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>-19.899999999999999</v>
       </c>
       <c r="R248">
         <v>0</v>
@@ -32927,7 +33647,7 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>10828.19</v>
+        <v>10864.67</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -33004,10 +33724,10 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>10434.879999999999</v>
+        <v>10356.299999999999</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>85.35</v>
       </c>
       <c r="R250">
         <v>0</v>
@@ -33081,7 +33801,7 @@
         <v>1478.26</v>
       </c>
       <c r="P251">
-        <v>716.95</v>
+        <v>698.55</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -33235,7 +33955,7 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>1438.9</v>
+        <v>1435.9</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -33312,7 +34032,7 @@
         <v>2460.85</v>
       </c>
       <c r="P254">
-        <v>618.35</v>
+        <v>598.35</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -33389,10 +34109,10 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>26068.95</v>
+        <v>25275.11</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>-135.80000000000001</v>
       </c>
       <c r="R255">
         <v>0</v>
@@ -33466,10 +34186,10 @@
         <v>6679.21</v>
       </c>
       <c r="P256">
-        <v>5420.08</v>
+        <v>5383.38</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>-27.9</v>
       </c>
       <c r="R256">
         <v>0</v>
@@ -33543,7 +34263,7 @@
         <v>3019.73</v>
       </c>
       <c r="P257">
-        <v>1691.66</v>
+        <v>1675.86</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -33620,7 +34340,7 @@
         <v>291.7</v>
       </c>
       <c r="P258">
-        <v>1517.4</v>
+        <v>1479.4</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -33697,7 +34417,7 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>4220.72</v>
+        <v>4228.5600000000004</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -33774,7 +34494,7 @@
         <v>18146.46</v>
       </c>
       <c r="P260">
-        <v>22736.11</v>
+        <v>22534.81</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -36326,11 +37046,11 @@
       </c>
       <c r="P299">
         <f t="shared" si="0"/>
-        <v>472249.95000000019</v>
+        <v>468457.1</v>
       </c>
       <c r="Q299">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>158883.08000000007</v>
       </c>
       <c r="R299">
         <f t="shared" si="0"/>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF81AC-D83C-473E-9D16-24BDC42C949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75ADC513-1057-450B-AD13-0E995199DAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -252,7 +252,7 @@
             <v>67</v>
           </cell>
           <cell r="BM93">
-            <v>28</v>
+            <v>41</v>
           </cell>
         </row>
         <row r="94">
@@ -299,7 +299,7 @@
             <v>91</v>
           </cell>
           <cell r="BM94">
-            <v>48</v>
+            <v>54</v>
           </cell>
         </row>
         <row r="95">
@@ -346,7 +346,7 @@
             <v>185</v>
           </cell>
           <cell r="BM95">
-            <v>95</v>
+            <v>132</v>
           </cell>
         </row>
         <row r="96">
@@ -393,7 +393,7 @@
             <v>6</v>
           </cell>
           <cell r="BM96">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="97">
@@ -440,7 +440,7 @@
             <v>36</v>
           </cell>
           <cell r="BM97">
-            <v>15</v>
+            <v>26</v>
           </cell>
         </row>
         <row r="98">
@@ -487,7 +487,7 @@
             <v>70</v>
           </cell>
           <cell r="BM98">
-            <v>39</v>
+            <v>56</v>
           </cell>
         </row>
         <row r="99">
@@ -581,7 +581,7 @@
             <v>751</v>
           </cell>
           <cell r="BM100">
-            <v>328</v>
+            <v>423</v>
           </cell>
         </row>
         <row r="101">
@@ -628,7 +628,7 @@
             <v>561</v>
           </cell>
           <cell r="BM101">
-            <v>283</v>
+            <v>332</v>
           </cell>
         </row>
         <row r="102">
@@ -688,6 +688,9 @@
           <cell r="BK103">
             <v>1</v>
           </cell>
+          <cell r="BM103">
+            <v>2</v>
+          </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
@@ -951,7 +954,7 @@
             <v>1009.2</v>
           </cell>
           <cell r="BM120">
-            <v>0</v>
+            <v>753.02</v>
           </cell>
         </row>
         <row r="121">
@@ -1004,7 +1007,7 @@
             <v>441.75</v>
           </cell>
           <cell r="BM121">
-            <v>179.3</v>
+            <v>189.1</v>
           </cell>
         </row>
         <row r="122">
@@ -1057,7 +1060,7 @@
             <v>545.91</v>
           </cell>
           <cell r="BM122">
-            <v>174.4</v>
+            <v>535.42999999999995</v>
           </cell>
         </row>
         <row r="123">
@@ -1110,7 +1113,7 @@
             <v>573.30999999999995</v>
           </cell>
           <cell r="BM123">
-            <v>284.18</v>
+            <v>416.56</v>
           </cell>
         </row>
         <row r="124">
@@ -1269,7 +1272,7 @@
             <v>95.9</v>
           </cell>
           <cell r="BM126">
-            <v>0</v>
+            <v>21.05</v>
           </cell>
         </row>
         <row r="127">
@@ -1322,7 +1325,7 @@
             <v>404.9</v>
           </cell>
           <cell r="BM127">
-            <v>601.91999999999996</v>
+            <v>861.25</v>
           </cell>
         </row>
         <row r="128">
@@ -1375,7 +1378,7 @@
             <v>4848</v>
           </cell>
           <cell r="BM128">
-            <v>47.9</v>
+            <v>226.9</v>
           </cell>
         </row>
         <row r="129">
@@ -1428,7 +1431,7 @@
             <v>2100.16</v>
           </cell>
           <cell r="BM129">
-            <v>786.72</v>
+            <v>821.72</v>
           </cell>
         </row>
         <row r="130">
@@ -1481,7 +1484,7 @@
             <v>530.04</v>
           </cell>
           <cell r="BM130">
-            <v>654.87</v>
+            <v>862.11</v>
           </cell>
         </row>
         <row r="131">
@@ -1587,7 +1590,7 @@
             <v>86.7</v>
           </cell>
           <cell r="BM132">
-            <v>233.3</v>
+            <v>310.2</v>
           </cell>
         </row>
         <row r="133">
@@ -2011,7 +2014,7 @@
             <v>292.04000000000002</v>
           </cell>
           <cell r="BM142">
-            <v>63.88</v>
+            <v>2032.9</v>
           </cell>
         </row>
         <row r="143">
@@ -2223,7 +2226,7 @@
             <v>619.61</v>
           </cell>
           <cell r="BM146">
-            <v>770.64</v>
+            <v>819.14</v>
           </cell>
         </row>
         <row r="147">
@@ -2276,7 +2279,7 @@
             <v>991.28</v>
           </cell>
           <cell r="BM147">
-            <v>452.97</v>
+            <v>528.05999999999995</v>
           </cell>
         </row>
         <row r="148">
@@ -2329,7 +2332,7 @@
             <v>491.91</v>
           </cell>
           <cell r="BM148">
-            <v>1068.73</v>
+            <v>1026.83</v>
           </cell>
         </row>
         <row r="149">
@@ -2541,7 +2544,7 @@
             <v>0</v>
           </cell>
           <cell r="BM152">
-            <v>0</v>
+            <v>-219.9</v>
           </cell>
         </row>
         <row r="153">
@@ -2594,7 +2597,7 @@
             <v>743.18</v>
           </cell>
           <cell r="BM153">
-            <v>1084.5</v>
+            <v>1541.3</v>
           </cell>
         </row>
         <row r="154">
@@ -2806,7 +2809,7 @@
             <v>652.88</v>
           </cell>
           <cell r="BM157">
-            <v>117.95</v>
+            <v>177.9</v>
           </cell>
         </row>
         <row r="158">
@@ -2859,7 +2862,7 @@
             <v>261.3</v>
           </cell>
           <cell r="BM158">
-            <v>671.53</v>
+            <v>721.33</v>
           </cell>
         </row>
         <row r="159">
@@ -3389,7 +3392,7 @@
             <v>699.1</v>
           </cell>
           <cell r="BM170">
-            <v>178.7</v>
+            <v>1511.5</v>
           </cell>
         </row>
         <row r="171">
@@ -3442,7 +3445,7 @@
             <v>939.09</v>
           </cell>
           <cell r="BM171">
-            <v>291.19</v>
+            <v>445.74</v>
           </cell>
         </row>
         <row r="172">
@@ -3495,7 +3498,7 @@
             <v>1279.22</v>
           </cell>
           <cell r="BM172">
-            <v>1372.46</v>
+            <v>1786.24</v>
           </cell>
         </row>
         <row r="173">
@@ -3548,7 +3551,7 @@
             <v>1332.67</v>
           </cell>
           <cell r="BM173">
-            <v>964.27</v>
+            <v>1023.57</v>
           </cell>
         </row>
         <row r="174">
@@ -3601,7 +3604,7 @@
             <v>158.19999999999999</v>
           </cell>
           <cell r="BM174">
-            <v>379.57</v>
+            <v>419.47</v>
           </cell>
         </row>
         <row r="175">
@@ -3707,7 +3710,7 @@
             <v>209.83</v>
           </cell>
           <cell r="BM176">
-            <v>25.8</v>
+            <v>39.700000000000003</v>
           </cell>
         </row>
         <row r="177">
@@ -3813,7 +3816,7 @@
             <v>4758.8500000000004</v>
           </cell>
           <cell r="BM178">
-            <v>4504.1099999999997</v>
+            <v>7711.31</v>
           </cell>
         </row>
         <row r="179">
@@ -3866,7 +3869,7 @@
             <v>2196.5100000000002</v>
           </cell>
           <cell r="BM179">
-            <v>420.69</v>
+            <v>596.89</v>
           </cell>
         </row>
         <row r="180">
@@ -4025,7 +4028,7 @@
             <v>2194.29</v>
           </cell>
           <cell r="BM182">
-            <v>646.1</v>
+            <v>686.3</v>
           </cell>
         </row>
         <row r="183">
@@ -4078,7 +4081,7 @@
             <v>3388.07</v>
           </cell>
           <cell r="BM183">
-            <v>1846.53</v>
+            <v>2210</v>
           </cell>
         </row>
         <row r="184">
@@ -4714,7 +4717,7 @@
             <v>78.959999999999994</v>
           </cell>
           <cell r="BM197">
-            <v>0.01</v>
+            <v>55.38</v>
           </cell>
         </row>
         <row r="198">
@@ -5880,7 +5883,7 @@
             <v>21.49</v>
           </cell>
           <cell r="BM221">
-            <v>144.78</v>
+            <v>197.48</v>
           </cell>
         </row>
         <row r="222">
@@ -5933,7 +5936,7 @@
             <v>215.71</v>
           </cell>
           <cell r="BM222">
-            <v>229.29</v>
+            <v>278.29000000000002</v>
           </cell>
         </row>
         <row r="223">
@@ -5986,7 +5989,7 @@
             <v>251.25</v>
           </cell>
           <cell r="BM223">
-            <v>95.3</v>
+            <v>1554.74</v>
           </cell>
         </row>
         <row r="224">
@@ -6251,7 +6254,7 @@
             <v>345.6</v>
           </cell>
           <cell r="BM228">
-            <v>206</v>
+            <v>537.96</v>
           </cell>
         </row>
         <row r="229">
@@ -6304,7 +6307,7 @@
             <v>576.95000000000005</v>
           </cell>
           <cell r="BM229">
-            <v>-27.8</v>
+            <v>22.1</v>
           </cell>
         </row>
         <row r="230">
@@ -6463,7 +6466,7 @@
             <v>234.83</v>
           </cell>
           <cell r="BM232">
-            <v>67.599999999999994</v>
+            <v>-31.88</v>
           </cell>
         </row>
         <row r="233">
@@ -6516,7 +6519,7 @@
             <v>1925.14</v>
           </cell>
           <cell r="BM233">
-            <v>15.28</v>
+            <v>1686.55</v>
           </cell>
         </row>
         <row r="234">
@@ -7099,7 +7102,7 @@
             <v>480.72</v>
           </cell>
           <cell r="BM246">
-            <v>543.62</v>
+            <v>675.36</v>
           </cell>
         </row>
         <row r="247">
@@ -7152,7 +7155,7 @@
             <v>346.28</v>
           </cell>
           <cell r="BM247">
-            <v>429.01</v>
+            <v>547.78</v>
           </cell>
         </row>
         <row r="248">
@@ -7205,7 +7208,7 @@
             <v>580.64</v>
           </cell>
           <cell r="BM248">
-            <v>595.09</v>
+            <v>977.98</v>
           </cell>
         </row>
         <row r="249">
@@ -7364,7 +7367,7 @@
             <v>55.34</v>
           </cell>
           <cell r="BM251">
-            <v>13.95</v>
+            <v>19.899999999999999</v>
           </cell>
         </row>
         <row r="252">
@@ -7470,7 +7473,7 @@
             <v>299.39999999999998</v>
           </cell>
           <cell r="BM253">
-            <v>237.3</v>
+            <v>278.5</v>
           </cell>
         </row>
         <row r="254">
@@ -7523,7 +7526,7 @@
             <v>204.1</v>
           </cell>
           <cell r="BM254">
-            <v>507.3</v>
+            <v>1058.43</v>
           </cell>
         </row>
         <row r="255">
@@ -7682,7 +7685,7 @@
             <v>479.45</v>
           </cell>
           <cell r="BM257">
-            <v>30.95</v>
+            <v>47.25</v>
           </cell>
         </row>
         <row r="258">
@@ -7735,7 +7738,7 @@
             <v>576.54999999999995</v>
           </cell>
           <cell r="BM258">
-            <v>47.7</v>
+            <v>59.5</v>
           </cell>
         </row>
         <row r="259">
@@ -9325,7 +9328,7 @@
             <v>24871.29</v>
           </cell>
           <cell r="BM292">
-            <v>8544.1200000000008</v>
+            <v>10679.38</v>
           </cell>
         </row>
         <row r="293">
@@ -9484,7 +9487,7 @@
             <v>5789.04</v>
           </cell>
           <cell r="BM295">
-            <v>1728.8</v>
+            <v>1802.6</v>
           </cell>
         </row>
         <row r="296">
@@ -9537,7 +9540,7 @@
             <v>9659.8799999999992</v>
           </cell>
           <cell r="BM296">
-            <v>3250.35</v>
+            <v>3843.75</v>
           </cell>
         </row>
         <row r="297">
@@ -9590,7 +9593,7 @@
             <v>9559.2900000000009</v>
           </cell>
           <cell r="BM297">
-            <v>2693.16</v>
+            <v>3932.24</v>
           </cell>
         </row>
         <row r="298">
@@ -9643,7 +9646,7 @@
             <v>15228.52</v>
           </cell>
           <cell r="BM298">
-            <v>4222.55</v>
+            <v>11939.54</v>
           </cell>
         </row>
         <row r="299">
@@ -9696,7 +9699,7 @@
             <v>1144.96</v>
           </cell>
           <cell r="BM299">
-            <v>482.15</v>
+            <v>584.35</v>
           </cell>
         </row>
         <row r="300">
@@ -9802,7 +9805,7 @@
             <v>5219.09</v>
           </cell>
           <cell r="BM301">
-            <v>228.79</v>
+            <v>236.46</v>
           </cell>
         </row>
         <row r="302">
@@ -9855,7 +9858,7 @@
             <v>3277.5</v>
           </cell>
           <cell r="BM302">
-            <v>399.8</v>
+            <v>579.70000000000005</v>
           </cell>
         </row>
         <row r="303">
@@ -9908,7 +9911,7 @@
             <v>109105.36</v>
           </cell>
           <cell r="BM303">
-            <v>53432.43</v>
+            <v>65970.149999999994</v>
           </cell>
         </row>
         <row r="304">
@@ -9961,7 +9964,7 @@
             <v>8645.2900000000009</v>
           </cell>
           <cell r="BM304">
-            <v>6180.9</v>
+            <v>7941.62</v>
           </cell>
         </row>
         <row r="305">
@@ -10014,7 +10017,7 @@
             <v>773.75</v>
           </cell>
           <cell r="BM305">
-            <v>1366.85</v>
+            <v>1563.43</v>
           </cell>
         </row>
         <row r="306">
@@ -10067,7 +10070,7 @@
             <v>433</v>
           </cell>
           <cell r="BM306">
-            <v>1134.8</v>
+            <v>1434.7</v>
           </cell>
         </row>
         <row r="307">
@@ -10120,7 +10123,7 @@
             <v>5292.88</v>
           </cell>
           <cell r="BM307">
-            <v>2161.36</v>
+            <v>3277.89</v>
           </cell>
         </row>
         <row r="308">
@@ -10173,7 +10176,7 @@
             <v>29215.86</v>
           </cell>
           <cell r="BM308">
-            <v>11360.36</v>
+            <v>13566.5</v>
           </cell>
         </row>
         <row r="309">
@@ -10544,7 +10547,7 @@
             <v>6246.19</v>
           </cell>
           <cell r="BM317">
-            <v>1482.01</v>
+            <v>3045.13</v>
           </cell>
         </row>
         <row r="318">
@@ -10703,7 +10706,7 @@
             <v>6632.2</v>
           </cell>
           <cell r="BM320">
-            <v>3774.38</v>
+            <v>4016.4</v>
           </cell>
         </row>
         <row r="321">
@@ -10756,7 +10759,7 @@
             <v>4704.99</v>
           </cell>
           <cell r="BM321">
-            <v>1352.37</v>
+            <v>1449.66</v>
           </cell>
         </row>
         <row r="322">
@@ -10809,7 +10812,7 @@
             <v>3870.6</v>
           </cell>
           <cell r="BM322">
-            <v>3451.95</v>
+            <v>3710.98</v>
           </cell>
         </row>
         <row r="323">
@@ -10862,7 +10865,7 @@
             <v>11596.46</v>
           </cell>
           <cell r="BM323">
-            <v>1851.63</v>
+            <v>2148.77</v>
           </cell>
         </row>
         <row r="324">
@@ -10915,7 +10918,7 @@
             <v>398.36</v>
           </cell>
           <cell r="BM324">
-            <v>385.95</v>
+            <v>535.35</v>
           </cell>
         </row>
         <row r="325">
@@ -11021,7 +11024,7 @@
             <v>3172.3</v>
           </cell>
           <cell r="BM326">
-            <v>376.7</v>
+            <v>391.6</v>
           </cell>
         </row>
         <row r="327">
@@ -11074,7 +11077,7 @@
             <v>929.45</v>
           </cell>
           <cell r="BM327">
-            <v>954.19</v>
+            <v>1592.96</v>
           </cell>
         </row>
         <row r="328">
@@ -11127,7 +11130,7 @@
             <v>32127.45</v>
           </cell>
           <cell r="BM328">
-            <v>13334.11</v>
+            <v>16726.759999999998</v>
           </cell>
         </row>
         <row r="329">
@@ -11180,7 +11183,7 @@
             <v>5550.91</v>
           </cell>
           <cell r="BM329">
-            <v>4141.5600000000004</v>
+            <v>4782.37</v>
           </cell>
         </row>
         <row r="330">
@@ -11233,7 +11236,7 @@
             <v>2377.84</v>
           </cell>
           <cell r="BM330">
-            <v>304.72000000000003</v>
+            <v>810.78</v>
           </cell>
         </row>
         <row r="331">
@@ -11286,7 +11289,7 @@
             <v>3520.64</v>
           </cell>
           <cell r="BM331">
-            <v>856.19</v>
+            <v>2591.9899999999998</v>
           </cell>
         </row>
         <row r="332">
@@ -11339,7 +11342,7 @@
             <v>3929.27</v>
           </cell>
           <cell r="BM332">
-            <v>1687.77</v>
+            <v>2040.05</v>
           </cell>
         </row>
         <row r="333">
@@ -11392,7 +11395,7 @@
             <v>9688.98</v>
           </cell>
           <cell r="BM333">
-            <v>3344.29</v>
+            <v>5638.46</v>
           </cell>
         </row>
         <row r="334">
@@ -12889,6 +12892,9 @@
           <cell r="BK366">
             <v>0</v>
           </cell>
+          <cell r="BM366">
+            <v>0</v>
+          </cell>
         </row>
         <row r="367">
           <cell r="A367" t="str">
@@ -12906,6 +12912,9 @@
           <cell r="BK367">
             <v>0</v>
           </cell>
+          <cell r="BM367">
+            <v>0</v>
+          </cell>
         </row>
         <row r="368">
           <cell r="A368" t="str">
@@ -12923,6 +12932,9 @@
           <cell r="BK368">
             <v>0</v>
           </cell>
+          <cell r="BM368">
+            <v>0</v>
+          </cell>
         </row>
         <row r="369">
           <cell r="A369" t="str">
@@ -12940,6 +12952,9 @@
           <cell r="BK369">
             <v>0</v>
           </cell>
+          <cell r="BM369">
+            <v>0</v>
+          </cell>
         </row>
         <row r="370">
           <cell r="A370" t="str">
@@ -12957,6 +12972,9 @@
           <cell r="BK370">
             <v>0</v>
           </cell>
+          <cell r="BM370">
+            <v>0</v>
+          </cell>
         </row>
         <row r="371">
           <cell r="A371" t="str">
@@ -12974,6 +12992,9 @@
           <cell r="BK371">
             <v>0</v>
           </cell>
+          <cell r="BM371">
+            <v>0</v>
+          </cell>
         </row>
         <row r="372">
           <cell r="A372" t="str">
@@ -12991,6 +13012,9 @@
           <cell r="BK372">
             <v>0</v>
           </cell>
+          <cell r="BM372">
+            <v>0</v>
+          </cell>
         </row>
         <row r="373">
           <cell r="A373" t="str">
@@ -13008,6 +13032,9 @@
           <cell r="BK373">
             <v>0</v>
           </cell>
+          <cell r="BM373">
+            <v>0</v>
+          </cell>
         </row>
         <row r="374">
           <cell r="A374" t="str">
@@ -13025,6 +13052,9 @@
           <cell r="BK374">
             <v>0</v>
           </cell>
+          <cell r="BM374">
+            <v>0</v>
+          </cell>
         </row>
         <row r="375">
           <cell r="A375" t="str">
@@ -13042,6 +13072,9 @@
           <cell r="BK375">
             <v>0</v>
           </cell>
+          <cell r="BM375">
+            <v>0</v>
+          </cell>
         </row>
         <row r="376">
           <cell r="A376" t="str">
@@ -13059,6 +13092,9 @@
           <cell r="BK376">
             <v>0</v>
           </cell>
+          <cell r="BM376">
+            <v>0</v>
+          </cell>
         </row>
         <row r="377">
           <cell r="A377" t="str">
@@ -13076,6 +13112,9 @@
           <cell r="BK377">
             <v>0</v>
           </cell>
+          <cell r="BM377">
+            <v>0</v>
+          </cell>
         </row>
         <row r="378">
           <cell r="A378" t="str">
@@ -13093,6 +13132,9 @@
           <cell r="BK378">
             <v>0</v>
           </cell>
+          <cell r="BM378">
+            <v>0</v>
+          </cell>
         </row>
         <row r="379">
           <cell r="A379" t="str">
@@ -13110,6 +13152,9 @@
           <cell r="BK379">
             <v>0</v>
           </cell>
+          <cell r="BM379">
+            <v>0</v>
+          </cell>
         </row>
         <row r="380">
           <cell r="A380" t="str">
@@ -13127,6 +13172,9 @@
           <cell r="BK380">
             <v>0</v>
           </cell>
+          <cell r="BM380">
+            <v>0</v>
+          </cell>
         </row>
         <row r="381">
           <cell r="A381" t="str">
@@ -13144,6 +13192,9 @@
           <cell r="BK381">
             <v>0</v>
           </cell>
+          <cell r="BM381">
+            <v>0</v>
+          </cell>
         </row>
         <row r="382">
           <cell r="A382" t="str">
@@ -13161,6 +13212,9 @@
           <cell r="BK382">
             <v>3.7</v>
           </cell>
+          <cell r="BM382">
+            <v>78.8</v>
+          </cell>
         </row>
         <row r="383">
           <cell r="A383" t="str">
@@ -13178,6 +13232,9 @@
           <cell r="BK383">
             <v>0</v>
           </cell>
+          <cell r="BM383">
+            <v>0</v>
+          </cell>
         </row>
         <row r="384">
           <cell r="A384" t="str">
@@ -13195,6 +13252,9 @@
           <cell r="BK384">
             <v>0</v>
           </cell>
+          <cell r="BM384">
+            <v>0</v>
+          </cell>
         </row>
         <row r="385">
           <cell r="A385" t="str">
@@ -13212,6 +13272,9 @@
           <cell r="BK385">
             <v>0</v>
           </cell>
+          <cell r="BM385">
+            <v>0</v>
+          </cell>
         </row>
         <row r="386">
           <cell r="A386" t="str">
@@ -13229,6 +13292,9 @@
           <cell r="BK386">
             <v>0</v>
           </cell>
+          <cell r="BM386">
+            <v>0</v>
+          </cell>
         </row>
         <row r="387">
           <cell r="A387" t="str">
@@ -13246,6 +13312,9 @@
           <cell r="BK387">
             <v>0</v>
           </cell>
+          <cell r="BM387">
+            <v>0</v>
+          </cell>
         </row>
         <row r="388">
           <cell r="A388" t="str">
@@ -13261,6 +13330,9 @@
             <v>0</v>
           </cell>
           <cell r="BK388">
+            <v>0</v>
+          </cell>
+          <cell r="BM388">
             <v>0</v>
           </cell>
         </row>
@@ -13785,7 +13857,7 @@
         <v>67</v>
       </c>
       <c r="Q4">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -13973,7 +14045,7 @@
         <v>91</v>
       </c>
       <c r="Q5">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -14161,7 +14233,7 @@
         <v>185</v>
       </c>
       <c r="Q6">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -14349,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -14537,7 +14609,7 @@
         <v>36</v>
       </c>
       <c r="Q8">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -14725,7 +14797,7 @@
         <v>70</v>
       </c>
       <c r="Q9">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -15101,7 +15173,7 @@
         <v>751</v>
       </c>
       <c r="Q11">
-        <v>328</v>
+        <v>423</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -15289,7 +15361,7 @@
         <v>561</v>
       </c>
       <c r="Q12">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -15665,7 +15737,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -16171,7 +16243,7 @@
         <v>1009.2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>753.02</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -16248,7 +16320,7 @@
         <v>441.75</v>
       </c>
       <c r="Q23">
-        <v>179.3</v>
+        <v>189.1</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -16325,7 +16397,7 @@
         <v>545.91</v>
       </c>
       <c r="Q24">
-        <v>174.4</v>
+        <v>535.42999999999995</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -16402,7 +16474,7 @@
         <v>573.30999999999995</v>
       </c>
       <c r="Q25">
-        <v>284.18</v>
+        <v>416.56</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -16633,7 +16705,7 @@
         <v>95.9</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -16710,7 +16782,7 @@
         <v>404.9</v>
       </c>
       <c r="Q29">
-        <v>601.91999999999996</v>
+        <v>861.25</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -16787,7 +16859,7 @@
         <v>4848</v>
       </c>
       <c r="Q30">
-        <v>47.9</v>
+        <v>226.9</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -16864,7 +16936,7 @@
         <v>2100.16</v>
       </c>
       <c r="Q31">
-        <v>786.72</v>
+        <v>821.72</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -16941,7 +17013,7 @@
         <v>530.04</v>
       </c>
       <c r="Q32">
-        <v>654.87</v>
+        <v>862.11</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -17095,7 +17167,7 @@
         <v>86.7</v>
       </c>
       <c r="Q34">
-        <v>233.3</v>
+        <v>310.2</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -17865,7 +17937,7 @@
         <v>292.04000000000002</v>
       </c>
       <c r="Q44">
-        <v>63.88</v>
+        <v>2032.9</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -18173,7 +18245,7 @@
         <v>619.61</v>
       </c>
       <c r="Q48">
-        <v>770.64</v>
+        <v>819.14</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -18250,7 +18322,7 @@
         <v>991.28</v>
       </c>
       <c r="Q49">
-        <v>452.97</v>
+        <v>528.05999999999995</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -18327,7 +18399,7 @@
         <v>491.91</v>
       </c>
       <c r="Q50">
-        <v>1068.73</v>
+        <v>1026.83</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -18635,7 +18707,7 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>-219.9</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -18712,7 +18784,7 @@
         <v>743.18</v>
       </c>
       <c r="Q55">
-        <v>1084.5</v>
+        <v>1541.3</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -19020,7 +19092,7 @@
         <v>652.88</v>
       </c>
       <c r="Q59">
-        <v>117.95</v>
+        <v>177.9</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -19097,7 +19169,7 @@
         <v>261.3</v>
       </c>
       <c r="Q60">
-        <v>671.53</v>
+        <v>721.33</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -20021,7 +20093,7 @@
         <v>699.1</v>
       </c>
       <c r="Q72">
-        <v>178.7</v>
+        <v>1511.5</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -20098,7 +20170,7 @@
         <v>939.09</v>
       </c>
       <c r="Q73">
-        <v>291.19</v>
+        <v>445.74</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -20175,7 +20247,7 @@
         <v>1279.22</v>
       </c>
       <c r="Q74">
-        <v>1372.46</v>
+        <v>1786.24</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -20252,7 +20324,7 @@
         <v>1332.67</v>
       </c>
       <c r="Q75">
-        <v>964.27</v>
+        <v>1023.57</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -20329,7 +20401,7 @@
         <v>158.19999999999999</v>
       </c>
       <c r="Q76">
-        <v>379.57</v>
+        <v>419.47</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20483,7 +20555,7 @@
         <v>209.83</v>
       </c>
       <c r="Q78">
-        <v>25.8</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20637,7 +20709,7 @@
         <v>4758.8500000000004</v>
       </c>
       <c r="Q80">
-        <v>4504.1099999999997</v>
+        <v>7711.31</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -20714,7 +20786,7 @@
         <v>2196.5100000000002</v>
       </c>
       <c r="Q81">
-        <v>420.69</v>
+        <v>596.89</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -20945,7 +21017,7 @@
         <v>2194.29</v>
       </c>
       <c r="Q84">
-        <v>646.1</v>
+        <v>686.3</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -21022,7 +21094,7 @@
         <v>3388.07</v>
       </c>
       <c r="Q85">
-        <v>1846.53</v>
+        <v>2210</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -22100,7 +22172,7 @@
         <v>78.959999999999994</v>
       </c>
       <c r="Q99">
-        <v>0.01</v>
+        <v>55.38</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -23948,7 +24020,7 @@
         <v>21.49</v>
       </c>
       <c r="Q123">
-        <v>144.78</v>
+        <v>197.48</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -24025,7 +24097,7 @@
         <v>215.71</v>
       </c>
       <c r="Q124">
-        <v>229.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -24102,7 +24174,7 @@
         <v>251.25</v>
       </c>
       <c r="Q125">
-        <v>95.3</v>
+        <v>1554.74</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -24487,7 +24559,7 @@
         <v>345.6</v>
       </c>
       <c r="Q130">
-        <v>206</v>
+        <v>537.96</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -24564,7 +24636,7 @@
         <v>576.95000000000005</v>
       </c>
       <c r="Q131">
-        <v>-27.8</v>
+        <v>22.1</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -24795,7 +24867,7 @@
         <v>234.83</v>
       </c>
       <c r="Q134">
-        <v>67.599999999999994</v>
+        <v>-31.88</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -24872,7 +24944,7 @@
         <v>1925.14</v>
       </c>
       <c r="Q135">
-        <v>15.28</v>
+        <v>1686.55</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -25873,7 +25945,7 @@
         <v>480.72</v>
       </c>
       <c r="Q148">
-        <v>543.62</v>
+        <v>675.36</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -25950,7 +26022,7 @@
         <v>346.28</v>
       </c>
       <c r="Q149">
-        <v>429.01</v>
+        <v>547.78</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -26027,7 +26099,7 @@
         <v>580.64</v>
       </c>
       <c r="Q150">
-        <v>595.09</v>
+        <v>977.98</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -26258,7 +26330,7 @@
         <v>55.34</v>
       </c>
       <c r="Q153">
-        <v>13.95</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -26412,7 +26484,7 @@
         <v>299.39999999999998</v>
       </c>
       <c r="Q155">
-        <v>237.3</v>
+        <v>278.5</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -26489,7 +26561,7 @@
         <v>204.1</v>
       </c>
       <c r="Q156">
-        <v>507.3</v>
+        <v>1058.43</v>
       </c>
       <c r="R156">
         <v>0</v>
@@ -26720,7 +26792,7 @@
         <v>479.45</v>
       </c>
       <c r="Q159">
-        <v>30.95</v>
+        <v>47.25</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -26797,7 +26869,7 @@
         <v>576.54999999999995</v>
       </c>
       <c r="Q160">
-        <v>47.7</v>
+        <v>59.5</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -29415,7 +29487,7 @@
         <v>24871.29</v>
       </c>
       <c r="Q194">
-        <v>8544.1200000000008</v>
+        <v>10679.38</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -29646,7 +29718,7 @@
         <v>5789.04</v>
       </c>
       <c r="Q197">
-        <v>1728.8</v>
+        <v>1802.6</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -29723,7 +29795,7 @@
         <v>9659.8799999999992</v>
       </c>
       <c r="Q198">
-        <v>3250.35</v>
+        <v>3843.75</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -29800,7 +29872,7 @@
         <v>9559.2900000000009</v>
       </c>
       <c r="Q199">
-        <v>2693.16</v>
+        <v>3932.24</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -29877,7 +29949,7 @@
         <v>15228.52</v>
       </c>
       <c r="Q200">
-        <v>4222.55</v>
+        <v>11939.54</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -29954,7 +30026,7 @@
         <v>1144.96</v>
       </c>
       <c r="Q201">
-        <v>482.15</v>
+        <v>584.35</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -30108,7 +30180,7 @@
         <v>5219.09</v>
       </c>
       <c r="Q203">
-        <v>228.79</v>
+        <v>236.46</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -30185,7 +30257,7 @@
         <v>3277.5</v>
       </c>
       <c r="Q204">
-        <v>399.8</v>
+        <v>579.70000000000005</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -30262,7 +30334,7 @@
         <v>109105.36</v>
       </c>
       <c r="Q205">
-        <v>53432.43</v>
+        <v>65970.149999999994</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -30339,7 +30411,7 @@
         <v>8645.2900000000009</v>
       </c>
       <c r="Q206">
-        <v>6180.9</v>
+        <v>7941.62</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -30416,7 +30488,7 @@
         <v>773.75</v>
       </c>
       <c r="Q207">
-        <v>1366.85</v>
+        <v>1563.43</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -30493,7 +30565,7 @@
         <v>433</v>
       </c>
       <c r="Q208">
-        <v>1134.8</v>
+        <v>1434.7</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -30570,7 +30642,7 @@
         <v>5292.88</v>
       </c>
       <c r="Q209">
-        <v>2161.36</v>
+        <v>3277.89</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -30647,7 +30719,7 @@
         <v>29215.86</v>
       </c>
       <c r="Q210">
-        <v>11360.36</v>
+        <v>13566.5</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -31340,7 +31412,7 @@
         <v>6246.19</v>
       </c>
       <c r="Q219">
-        <v>1482.01</v>
+        <v>3045.13</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -31571,7 +31643,7 @@
         <v>6632.2</v>
       </c>
       <c r="Q222">
-        <v>3774.38</v>
+        <v>4016.4</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -31648,7 +31720,7 @@
         <v>4704.99</v>
       </c>
       <c r="Q223">
-        <v>1352.37</v>
+        <v>1449.66</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -31725,7 +31797,7 @@
         <v>3870.6</v>
       </c>
       <c r="Q224">
-        <v>3451.95</v>
+        <v>3710.98</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -31802,7 +31874,7 @@
         <v>11596.46</v>
       </c>
       <c r="Q225">
-        <v>1851.63</v>
+        <v>2148.77</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -31879,7 +31951,7 @@
         <v>398.36</v>
       </c>
       <c r="Q226">
-        <v>385.95</v>
+        <v>535.35</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -32033,7 +32105,7 @@
         <v>3172.3</v>
       </c>
       <c r="Q228">
-        <v>376.7</v>
+        <v>391.6</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -32110,7 +32182,7 @@
         <v>929.45</v>
       </c>
       <c r="Q229">
-        <v>954.19</v>
+        <v>1592.96</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -32187,7 +32259,7 @@
         <v>32127.45</v>
       </c>
       <c r="Q230">
-        <v>13334.11</v>
+        <v>16726.759999999998</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -32264,7 +32336,7 @@
         <v>5550.91</v>
       </c>
       <c r="Q231">
-        <v>4141.5600000000004</v>
+        <v>4782.37</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -32341,7 +32413,7 @@
         <v>2377.84</v>
       </c>
       <c r="Q232">
-        <v>304.72000000000003</v>
+        <v>810.78</v>
       </c>
       <c r="R232">
         <v>0</v>
@@ -32418,7 +32490,7 @@
         <v>3520.64</v>
       </c>
       <c r="Q233">
-        <v>856.19</v>
+        <v>2591.9899999999998</v>
       </c>
       <c r="R233">
         <v>0</v>
@@ -32495,7 +32567,7 @@
         <v>3929.27</v>
       </c>
       <c r="Q234">
-        <v>1687.77</v>
+        <v>2040.05</v>
       </c>
       <c r="R234">
         <v>0</v>
@@ -32572,7 +32644,7 @@
         <v>9688.98</v>
       </c>
       <c r="Q235">
-        <v>3344.29</v>
+        <v>5638.46</v>
       </c>
       <c r="R235">
         <v>0</v>
@@ -36345,7 +36417,7 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="R284">
         <v>0</v>
@@ -37050,7 +37122,7 @@
       </c>
       <c r="Q299">
         <f t="shared" si="0"/>
-        <v>158883.08000000007</v>
+        <v>216374.56000000003</v>
       </c>
       <c r="R299">
         <f t="shared" si="0"/>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75ADC513-1057-450B-AD13-0E995199DAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA998F53-291B-4DC6-BA60-9DE6F67C9909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -252,7 +252,7 @@
             <v>67</v>
           </cell>
           <cell r="BM93">
-            <v>41</v>
+            <v>68</v>
           </cell>
         </row>
         <row r="94">
@@ -299,7 +299,7 @@
             <v>91</v>
           </cell>
           <cell r="BM94">
-            <v>54</v>
+            <v>90</v>
           </cell>
         </row>
         <row r="95">
@@ -346,7 +346,7 @@
             <v>185</v>
           </cell>
           <cell r="BM95">
-            <v>132</v>
+            <v>200</v>
           </cell>
         </row>
         <row r="96">
@@ -393,7 +393,7 @@
             <v>6</v>
           </cell>
           <cell r="BM96">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="97">
@@ -440,7 +440,7 @@
             <v>36</v>
           </cell>
           <cell r="BM97">
-            <v>26</v>
+            <v>42</v>
           </cell>
         </row>
         <row r="98">
@@ -487,7 +487,7 @@
             <v>70</v>
           </cell>
           <cell r="BM98">
-            <v>56</v>
+            <v>81</v>
           </cell>
         </row>
         <row r="99">
@@ -581,7 +581,7 @@
             <v>751</v>
           </cell>
           <cell r="BM100">
-            <v>423</v>
+            <v>849</v>
           </cell>
         </row>
         <row r="101">
@@ -628,7 +628,7 @@
             <v>561</v>
           </cell>
           <cell r="BM101">
-            <v>332</v>
+            <v>678</v>
           </cell>
         </row>
         <row r="102">
@@ -675,7 +675,7 @@
             <v>588</v>
           </cell>
           <cell r="BM102">
-            <v>2</v>
+            <v>236</v>
           </cell>
         </row>
         <row r="103">
@@ -1007,7 +1007,7 @@
             <v>441.75</v>
           </cell>
           <cell r="BM121">
-            <v>189.1</v>
+            <v>223.85</v>
           </cell>
         </row>
         <row r="122">
@@ -1060,7 +1060,7 @@
             <v>545.91</v>
           </cell>
           <cell r="BM122">
-            <v>535.42999999999995</v>
+            <v>743.12</v>
           </cell>
         </row>
         <row r="123">
@@ -1113,7 +1113,7 @@
             <v>573.30999999999995</v>
           </cell>
           <cell r="BM123">
-            <v>416.56</v>
+            <v>445.85</v>
           </cell>
         </row>
         <row r="124">
@@ -1166,7 +1166,7 @@
             <v>39.4</v>
           </cell>
           <cell r="BM124">
-            <v>46.6</v>
+            <v>76.3</v>
           </cell>
         </row>
         <row r="125">
@@ -1272,7 +1272,7 @@
             <v>95.9</v>
           </cell>
           <cell r="BM126">
-            <v>21.05</v>
+            <v>1000.25</v>
           </cell>
         </row>
         <row r="127">
@@ -1378,7 +1378,7 @@
             <v>4848</v>
           </cell>
           <cell r="BM128">
-            <v>226.9</v>
+            <v>378.3</v>
           </cell>
         </row>
         <row r="129">
@@ -1431,7 +1431,7 @@
             <v>2100.16</v>
           </cell>
           <cell r="BM129">
-            <v>821.72</v>
+            <v>1455.22</v>
           </cell>
         </row>
         <row r="130">
@@ -1484,7 +1484,7 @@
             <v>530.04</v>
           </cell>
           <cell r="BM130">
-            <v>862.11</v>
+            <v>903.91</v>
           </cell>
         </row>
         <row r="131">
@@ -1590,7 +1590,7 @@
             <v>86.7</v>
           </cell>
           <cell r="BM132">
-            <v>310.2</v>
+            <v>299.55</v>
           </cell>
         </row>
         <row r="133">
@@ -1643,7 +1643,7 @@
             <v>758.05</v>
           </cell>
           <cell r="BM133">
-            <v>329</v>
+            <v>371</v>
           </cell>
         </row>
         <row r="134">
@@ -2014,7 +2014,7 @@
             <v>292.04000000000002</v>
           </cell>
           <cell r="BM142">
-            <v>2032.9</v>
+            <v>3127.4</v>
           </cell>
         </row>
         <row r="143">
@@ -2173,7 +2173,7 @@
             <v>962.3</v>
           </cell>
           <cell r="BM145">
-            <v>392.7</v>
+            <v>419.6</v>
           </cell>
         </row>
         <row r="146">
@@ -2226,7 +2226,7 @@
             <v>619.61</v>
           </cell>
           <cell r="BM146">
-            <v>819.14</v>
+            <v>960.64</v>
           </cell>
         </row>
         <row r="147">
@@ -2279,7 +2279,7 @@
             <v>991.28</v>
           </cell>
           <cell r="BM147">
-            <v>528.05999999999995</v>
+            <v>824.11</v>
           </cell>
         </row>
         <row r="148">
@@ -2332,7 +2332,7 @@
             <v>491.91</v>
           </cell>
           <cell r="BM148">
-            <v>1026.83</v>
+            <v>1548.72</v>
           </cell>
         </row>
         <row r="149">
@@ -2491,7 +2491,7 @@
             <v>74.64</v>
           </cell>
           <cell r="BM151">
-            <v>14</v>
+            <v>112.15</v>
           </cell>
         </row>
         <row r="152">
@@ -2597,7 +2597,7 @@
             <v>743.18</v>
           </cell>
           <cell r="BM153">
-            <v>1541.3</v>
+            <v>6574.25</v>
           </cell>
         </row>
         <row r="154">
@@ -2650,7 +2650,7 @@
             <v>1244.1199999999999</v>
           </cell>
           <cell r="BM154">
-            <v>59.9</v>
+            <v>180.6</v>
           </cell>
         </row>
         <row r="155">
@@ -2809,7 +2809,7 @@
             <v>652.88</v>
           </cell>
           <cell r="BM157">
-            <v>177.9</v>
+            <v>322.99</v>
           </cell>
         </row>
         <row r="158">
@@ -2862,7 +2862,7 @@
             <v>261.3</v>
           </cell>
           <cell r="BM158">
-            <v>721.33</v>
+            <v>809.13</v>
           </cell>
         </row>
         <row r="159">
@@ -3233,7 +3233,7 @@
             <v>2994.32</v>
           </cell>
           <cell r="BM167">
-            <v>3.47</v>
+            <v>1477.89</v>
           </cell>
         </row>
         <row r="168">
@@ -3392,7 +3392,7 @@
             <v>699.1</v>
           </cell>
           <cell r="BM170">
-            <v>1511.5</v>
+            <v>1507.5</v>
           </cell>
         </row>
         <row r="171">
@@ -3445,7 +3445,7 @@
             <v>939.09</v>
           </cell>
           <cell r="BM171">
-            <v>445.74</v>
+            <v>626.61</v>
           </cell>
         </row>
         <row r="172">
@@ -3498,7 +3498,7 @@
             <v>1279.22</v>
           </cell>
           <cell r="BM172">
-            <v>1786.24</v>
+            <v>2189.0700000000002</v>
           </cell>
         </row>
         <row r="173">
@@ -3551,7 +3551,7 @@
             <v>1332.67</v>
           </cell>
           <cell r="BM173">
-            <v>1023.57</v>
+            <v>2194.5300000000002</v>
           </cell>
         </row>
         <row r="174">
@@ -3604,7 +3604,7 @@
             <v>158.19999999999999</v>
           </cell>
           <cell r="BM174">
-            <v>419.47</v>
+            <v>435.32</v>
           </cell>
         </row>
         <row r="175">
@@ -3710,7 +3710,7 @@
             <v>209.83</v>
           </cell>
           <cell r="BM176">
-            <v>39.700000000000003</v>
+            <v>94.6</v>
           </cell>
         </row>
         <row r="177">
@@ -3763,7 +3763,7 @@
             <v>955.8</v>
           </cell>
           <cell r="BM177">
-            <v>0</v>
+            <v>296</v>
           </cell>
         </row>
         <row r="178">
@@ -3816,7 +3816,7 @@
             <v>4758.8500000000004</v>
           </cell>
           <cell r="BM178">
-            <v>7711.31</v>
+            <v>8502.61</v>
           </cell>
         </row>
         <row r="179">
@@ -3869,7 +3869,7 @@
             <v>2196.5100000000002</v>
           </cell>
           <cell r="BM179">
-            <v>596.89</v>
+            <v>980.88</v>
           </cell>
         </row>
         <row r="180">
@@ -3922,7 +3922,7 @@
             <v>602.27</v>
           </cell>
           <cell r="BM180">
-            <v>296.5</v>
+            <v>722</v>
           </cell>
         </row>
         <row r="181">
@@ -3975,7 +3975,7 @@
             <v>0</v>
           </cell>
           <cell r="BM181">
-            <v>-71.5</v>
+            <v>2.0299999999999998</v>
           </cell>
         </row>
         <row r="182">
@@ -4028,7 +4028,7 @@
             <v>2194.29</v>
           </cell>
           <cell r="BM182">
-            <v>686.3</v>
+            <v>1546.27</v>
           </cell>
         </row>
         <row r="183">
@@ -4081,7 +4081,7 @@
             <v>3388.07</v>
           </cell>
           <cell r="BM183">
-            <v>2210</v>
+            <v>3638.36</v>
           </cell>
         </row>
         <row r="184">
@@ -4717,7 +4717,7 @@
             <v>78.959999999999994</v>
           </cell>
           <cell r="BM197">
-            <v>55.38</v>
+            <v>242.74</v>
           </cell>
         </row>
         <row r="198">
@@ -5671,7 +5671,7 @@
             <v>0</v>
           </cell>
           <cell r="BM217">
-            <v>0</v>
+            <v>111.98</v>
           </cell>
         </row>
         <row r="218">
@@ -5830,7 +5830,7 @@
             <v>0</v>
           </cell>
           <cell r="BM220">
-            <v>95</v>
+            <v>350.03</v>
           </cell>
         </row>
         <row r="221">
@@ -5883,7 +5883,7 @@
             <v>21.49</v>
           </cell>
           <cell r="BM221">
-            <v>197.48</v>
+            <v>242.07</v>
           </cell>
         </row>
         <row r="222">
@@ -5936,7 +5936,7 @@
             <v>215.71</v>
           </cell>
           <cell r="BM222">
-            <v>278.29000000000002</v>
+            <v>726.81</v>
           </cell>
         </row>
         <row r="223">
@@ -5989,7 +5989,7 @@
             <v>251.25</v>
           </cell>
           <cell r="BM223">
-            <v>1554.74</v>
+            <v>1601.95</v>
           </cell>
         </row>
         <row r="224">
@@ -6254,7 +6254,7 @@
             <v>345.6</v>
           </cell>
           <cell r="BM228">
-            <v>537.96</v>
+            <v>895.76</v>
           </cell>
         </row>
         <row r="229">
@@ -6307,7 +6307,7 @@
             <v>576.95000000000005</v>
           </cell>
           <cell r="BM229">
-            <v>22.1</v>
+            <v>-689.7</v>
           </cell>
         </row>
         <row r="230">
@@ -6360,7 +6360,7 @@
             <v>0</v>
           </cell>
           <cell r="BM230">
-            <v>201.33</v>
+            <v>264.05</v>
           </cell>
         </row>
         <row r="231">
@@ -6466,7 +6466,7 @@
             <v>234.83</v>
           </cell>
           <cell r="BM232">
-            <v>-31.88</v>
+            <v>-32.08</v>
           </cell>
         </row>
         <row r="233">
@@ -6519,7 +6519,7 @@
             <v>1925.14</v>
           </cell>
           <cell r="BM233">
-            <v>1686.55</v>
+            <v>2126.4299999999998</v>
           </cell>
         </row>
         <row r="234">
@@ -7102,7 +7102,7 @@
             <v>480.72</v>
           </cell>
           <cell r="BM246">
-            <v>675.36</v>
+            <v>760.47</v>
           </cell>
         </row>
         <row r="247">
@@ -7155,7 +7155,7 @@
             <v>346.28</v>
           </cell>
           <cell r="BM247">
-            <v>547.78</v>
+            <v>788.83</v>
           </cell>
         </row>
         <row r="248">
@@ -7208,7 +7208,7 @@
             <v>580.64</v>
           </cell>
           <cell r="BM248">
-            <v>977.98</v>
+            <v>1467.78</v>
           </cell>
         </row>
         <row r="249">
@@ -7367,7 +7367,7 @@
             <v>55.34</v>
           </cell>
           <cell r="BM251">
-            <v>19.899999999999999</v>
+            <v>63.65</v>
           </cell>
         </row>
         <row r="252">
@@ -7473,7 +7473,7 @@
             <v>299.39999999999998</v>
           </cell>
           <cell r="BM253">
-            <v>278.5</v>
+            <v>313.89999999999998</v>
           </cell>
         </row>
         <row r="254">
@@ -7526,7 +7526,7 @@
             <v>204.1</v>
           </cell>
           <cell r="BM254">
-            <v>1058.43</v>
+            <v>1196.1300000000001</v>
           </cell>
         </row>
         <row r="255">
@@ -7685,7 +7685,7 @@
             <v>479.45</v>
           </cell>
           <cell r="BM257">
-            <v>47.25</v>
+            <v>173.35</v>
           </cell>
         </row>
         <row r="258">
@@ -7738,7 +7738,7 @@
             <v>576.54999999999995</v>
           </cell>
           <cell r="BM258">
-            <v>59.5</v>
+            <v>129.4</v>
           </cell>
         </row>
         <row r="259">
@@ -9328,7 +9328,7 @@
             <v>24871.29</v>
           </cell>
           <cell r="BM292">
-            <v>10679.38</v>
+            <v>13513.36</v>
           </cell>
         </row>
         <row r="293">
@@ -9487,7 +9487,7 @@
             <v>5789.04</v>
           </cell>
           <cell r="BM295">
-            <v>1802.6</v>
+            <v>2212.23</v>
           </cell>
         </row>
         <row r="296">
@@ -9540,7 +9540,7 @@
             <v>9659.8799999999992</v>
           </cell>
           <cell r="BM296">
-            <v>3843.75</v>
+            <v>6416.32</v>
           </cell>
         </row>
         <row r="297">
@@ -9593,7 +9593,7 @@
             <v>9559.2900000000009</v>
           </cell>
           <cell r="BM297">
-            <v>3932.24</v>
+            <v>8433.17</v>
           </cell>
         </row>
         <row r="298">
@@ -9646,7 +9646,7 @@
             <v>15228.52</v>
           </cell>
           <cell r="BM298">
-            <v>11939.54</v>
+            <v>23252.57</v>
           </cell>
         </row>
         <row r="299">
@@ -9699,7 +9699,7 @@
             <v>1144.96</v>
           </cell>
           <cell r="BM299">
-            <v>584.35</v>
+            <v>1091</v>
           </cell>
         </row>
         <row r="300">
@@ -9805,7 +9805,7 @@
             <v>5219.09</v>
           </cell>
           <cell r="BM301">
-            <v>236.46</v>
+            <v>1932.62</v>
           </cell>
         </row>
         <row r="302">
@@ -9858,7 +9858,7 @@
             <v>3277.5</v>
           </cell>
           <cell r="BM302">
-            <v>579.70000000000005</v>
+            <v>1065.5</v>
           </cell>
         </row>
         <row r="303">
@@ -9911,7 +9911,7 @@
             <v>109105.36</v>
           </cell>
           <cell r="BM303">
-            <v>65970.149999999994</v>
+            <v>140533.95000000001</v>
           </cell>
         </row>
         <row r="304">
@@ -9964,7 +9964,7 @@
             <v>8645.2900000000009</v>
           </cell>
           <cell r="BM304">
-            <v>7941.62</v>
+            <v>11067.99</v>
           </cell>
         </row>
         <row r="305">
@@ -10017,7 +10017,7 @@
             <v>773.75</v>
           </cell>
           <cell r="BM305">
-            <v>1563.43</v>
+            <v>3159.05</v>
           </cell>
         </row>
         <row r="306">
@@ -10070,7 +10070,7 @@
             <v>433</v>
           </cell>
           <cell r="BM306">
-            <v>1434.7</v>
+            <v>3080.3</v>
           </cell>
         </row>
         <row r="307">
@@ -10123,7 +10123,7 @@
             <v>5292.88</v>
           </cell>
           <cell r="BM307">
-            <v>3277.89</v>
+            <v>6905.03</v>
           </cell>
         </row>
         <row r="308">
@@ -10176,7 +10176,7 @@
             <v>29215.86</v>
           </cell>
           <cell r="BM308">
-            <v>13566.5</v>
+            <v>30412.48</v>
           </cell>
         </row>
         <row r="309">
@@ -10547,7 +10547,7 @@
             <v>6246.19</v>
           </cell>
           <cell r="BM317">
-            <v>3045.13</v>
+            <v>34917.06</v>
           </cell>
         </row>
         <row r="318">
@@ -10706,7 +10706,7 @@
             <v>6632.2</v>
           </cell>
           <cell r="BM320">
-            <v>4016.4</v>
+            <v>4451.8999999999996</v>
           </cell>
         </row>
         <row r="321">
@@ -10759,7 +10759,7 @@
             <v>4704.99</v>
           </cell>
           <cell r="BM321">
-            <v>1449.66</v>
+            <v>3912.19</v>
           </cell>
         </row>
         <row r="322">
@@ -10812,7 +10812,7 @@
             <v>3870.6</v>
           </cell>
           <cell r="BM322">
-            <v>3710.98</v>
+            <v>8120.15</v>
           </cell>
         </row>
         <row r="323">
@@ -10865,7 +10865,7 @@
             <v>11596.46</v>
           </cell>
           <cell r="BM323">
-            <v>2148.77</v>
+            <v>7683.51</v>
           </cell>
         </row>
         <row r="324">
@@ -10918,7 +10918,7 @@
             <v>398.36</v>
           </cell>
           <cell r="BM324">
-            <v>535.35</v>
+            <v>1334.74</v>
           </cell>
         </row>
         <row r="325">
@@ -11024,7 +11024,7 @@
             <v>3172.3</v>
           </cell>
           <cell r="BM326">
-            <v>391.6</v>
+            <v>1381.2</v>
           </cell>
         </row>
         <row r="327">
@@ -11077,7 +11077,7 @@
             <v>929.45</v>
           </cell>
           <cell r="BM327">
-            <v>1592.96</v>
+            <v>2492.86</v>
           </cell>
         </row>
         <row r="328">
@@ -11130,7 +11130,7 @@
             <v>32127.45</v>
           </cell>
           <cell r="BM328">
-            <v>16726.759999999998</v>
+            <v>37277.550000000003</v>
           </cell>
         </row>
         <row r="329">
@@ -11183,7 +11183,7 @@
             <v>5550.91</v>
           </cell>
           <cell r="BM329">
-            <v>4782.37</v>
+            <v>8882.25</v>
           </cell>
         </row>
         <row r="330">
@@ -11236,7 +11236,7 @@
             <v>2377.84</v>
           </cell>
           <cell r="BM330">
-            <v>810.78</v>
+            <v>1782.09</v>
           </cell>
         </row>
         <row r="331">
@@ -11289,7 +11289,7 @@
             <v>3520.64</v>
           </cell>
           <cell r="BM331">
-            <v>2591.9899999999998</v>
+            <v>4342.83</v>
           </cell>
         </row>
         <row r="332">
@@ -11342,7 +11342,7 @@
             <v>3929.27</v>
           </cell>
           <cell r="BM332">
-            <v>2040.05</v>
+            <v>3780.23</v>
           </cell>
         </row>
         <row r="333">
@@ -11395,7 +11395,7 @@
             <v>9688.98</v>
           </cell>
           <cell r="BM333">
-            <v>5638.46</v>
+            <v>11364.53</v>
           </cell>
         </row>
         <row r="334">
@@ -11501,7 +11501,7 @@
             <v>0</v>
           </cell>
           <cell r="BM335">
-            <v>0</v>
+            <v>7.9</v>
           </cell>
         </row>
         <row r="336">
@@ -11766,7 +11766,7 @@
             <v>4398.3599999999997</v>
           </cell>
           <cell r="BM342">
-            <v>0</v>
+            <v>5300.64</v>
           </cell>
         </row>
         <row r="343">
@@ -11925,7 +11925,7 @@
             <v>4088.06</v>
           </cell>
           <cell r="BM345">
-            <v>0</v>
+            <v>95.65</v>
           </cell>
         </row>
         <row r="346">
@@ -11978,7 +11978,7 @@
             <v>3164.56</v>
           </cell>
           <cell r="BM346">
-            <v>-19.899999999999999</v>
+            <v>1639.56</v>
           </cell>
         </row>
         <row r="347">
@@ -12031,7 +12031,7 @@
             <v>10864.67</v>
           </cell>
           <cell r="BM347">
-            <v>0</v>
+            <v>1693.68</v>
           </cell>
         </row>
         <row r="348">
@@ -12084,7 +12084,7 @@
             <v>10356.299999999999</v>
           </cell>
           <cell r="BM348">
-            <v>85.35</v>
+            <v>2136.92</v>
           </cell>
         </row>
         <row r="349">
@@ -12137,7 +12137,7 @@
             <v>698.55</v>
           </cell>
           <cell r="BM349">
-            <v>0</v>
+            <v>210.15</v>
           </cell>
         </row>
         <row r="350">
@@ -12243,7 +12243,7 @@
             <v>1435.9</v>
           </cell>
           <cell r="BM351">
-            <v>0</v>
+            <v>205.25</v>
           </cell>
         </row>
         <row r="352">
@@ -12296,7 +12296,7 @@
             <v>598.35</v>
           </cell>
           <cell r="BM352">
-            <v>0</v>
+            <v>125.9</v>
           </cell>
         </row>
         <row r="353">
@@ -12349,7 +12349,7 @@
             <v>25275.11</v>
           </cell>
           <cell r="BM353">
-            <v>-135.80000000000001</v>
+            <v>15308.58</v>
           </cell>
         </row>
         <row r="354">
@@ -12402,7 +12402,7 @@
             <v>5383.38</v>
           </cell>
           <cell r="BM354">
-            <v>-27.9</v>
+            <v>3839.83</v>
           </cell>
         </row>
         <row r="355">
@@ -12455,7 +12455,7 @@
             <v>1675.86</v>
           </cell>
           <cell r="BM355">
-            <v>0</v>
+            <v>343.2</v>
           </cell>
         </row>
         <row r="356">
@@ -12508,7 +12508,7 @@
             <v>1479.4</v>
           </cell>
           <cell r="BM356">
-            <v>0</v>
+            <v>869.9</v>
           </cell>
         </row>
         <row r="357">
@@ -12561,7 +12561,7 @@
             <v>4228.5600000000004</v>
           </cell>
           <cell r="BM357">
-            <v>0</v>
+            <v>1426.85</v>
           </cell>
         </row>
         <row r="358">
@@ -12614,7 +12614,7 @@
             <v>22534.81</v>
           </cell>
           <cell r="BM358">
-            <v>0</v>
+            <v>3255.6</v>
           </cell>
         </row>
         <row r="359">
@@ -13857,7 +13857,7 @@
         <v>67</v>
       </c>
       <c r="Q4">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>91</v>
       </c>
       <c r="Q5">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -14233,7 +14233,7 @@
         <v>185</v>
       </c>
       <c r="Q6">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -14609,7 +14609,7 @@
         <v>36</v>
       </c>
       <c r="Q8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -14797,7 +14797,7 @@
         <v>70</v>
       </c>
       <c r="Q9">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -15173,7 +15173,7 @@
         <v>751</v>
       </c>
       <c r="Q11">
-        <v>423</v>
+        <v>849</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -15361,7 +15361,7 @@
         <v>561</v>
       </c>
       <c r="Q12">
-        <v>332</v>
+        <v>678</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -15549,7 +15549,7 @@
         <v>588</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>236</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -16320,7 +16320,7 @@
         <v>441.75</v>
       </c>
       <c r="Q23">
-        <v>189.1</v>
+        <v>223.85</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -16397,7 +16397,7 @@
         <v>545.91</v>
       </c>
       <c r="Q24">
-        <v>535.42999999999995</v>
+        <v>743.12</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>573.30999999999995</v>
       </c>
       <c r="Q25">
-        <v>416.56</v>
+        <v>445.85</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>39.4</v>
       </c>
       <c r="Q26">
-        <v>46.6</v>
+        <v>76.3</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -16705,7 +16705,7 @@
         <v>95.9</v>
       </c>
       <c r="Q28">
-        <v>21.05</v>
+        <v>1000.25</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -16859,7 +16859,7 @@
         <v>4848</v>
       </c>
       <c r="Q30">
-        <v>226.9</v>
+        <v>378.3</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -16936,7 +16936,7 @@
         <v>2100.16</v>
       </c>
       <c r="Q31">
-        <v>821.72</v>
+        <v>1455.22</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -17013,7 +17013,7 @@
         <v>530.04</v>
       </c>
       <c r="Q32">
-        <v>862.11</v>
+        <v>903.91</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -17167,7 +17167,7 @@
         <v>86.7</v>
       </c>
       <c r="Q34">
-        <v>310.2</v>
+        <v>299.55</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>758.05</v>
       </c>
       <c r="Q35">
-        <v>329</v>
+        <v>371</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -17937,7 +17937,7 @@
         <v>292.04000000000002</v>
       </c>
       <c r="Q44">
-        <v>2032.9</v>
+        <v>3127.4</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -18168,7 +18168,7 @@
         <v>962.3</v>
       </c>
       <c r="Q47">
-        <v>392.7</v>
+        <v>419.6</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>619.61</v>
       </c>
       <c r="Q48">
-        <v>819.14</v>
+        <v>960.64</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -18322,7 +18322,7 @@
         <v>991.28</v>
       </c>
       <c r="Q49">
-        <v>528.05999999999995</v>
+        <v>824.11</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -18399,7 +18399,7 @@
         <v>491.91</v>
       </c>
       <c r="Q50">
-        <v>1026.83</v>
+        <v>1548.72</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -18630,7 +18630,7 @@
         <v>74.64</v>
       </c>
       <c r="Q53">
-        <v>14</v>
+        <v>112.15</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>743.18</v>
       </c>
       <c r="Q55">
-        <v>1541.3</v>
+        <v>6574.25</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -18861,7 +18861,7 @@
         <v>1244.1199999999999</v>
       </c>
       <c r="Q56">
-        <v>59.9</v>
+        <v>180.6</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -19092,7 +19092,7 @@
         <v>652.88</v>
       </c>
       <c r="Q59">
-        <v>177.9</v>
+        <v>322.99</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -19169,7 +19169,7 @@
         <v>261.3</v>
       </c>
       <c r="Q60">
-        <v>721.33</v>
+        <v>809.13</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -19862,7 +19862,7 @@
         <v>2994.32</v>
       </c>
       <c r="Q69">
-        <v>3.47</v>
+        <v>1477.89</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -20093,7 +20093,7 @@
         <v>699.1</v>
       </c>
       <c r="Q72">
-        <v>1511.5</v>
+        <v>1507.5</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -20170,7 +20170,7 @@
         <v>939.09</v>
       </c>
       <c r="Q73">
-        <v>445.74</v>
+        <v>626.61</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -20247,7 +20247,7 @@
         <v>1279.22</v>
       </c>
       <c r="Q74">
-        <v>1786.24</v>
+        <v>2189.0700000000002</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>1332.67</v>
       </c>
       <c r="Q75">
-        <v>1023.57</v>
+        <v>2194.5300000000002</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -20401,7 +20401,7 @@
         <v>158.19999999999999</v>
       </c>
       <c r="Q76">
-        <v>419.47</v>
+        <v>435.32</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20555,7 +20555,7 @@
         <v>209.83</v>
       </c>
       <c r="Q78">
-        <v>39.700000000000003</v>
+        <v>94.6</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20632,7 +20632,7 @@
         <v>955.8</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20709,7 +20709,7 @@
         <v>4758.8500000000004</v>
       </c>
       <c r="Q80">
-        <v>7711.31</v>
+        <v>8502.61</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -20786,7 +20786,7 @@
         <v>2196.5100000000002</v>
       </c>
       <c r="Q81">
-        <v>596.89</v>
+        <v>980.88</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -20863,7 +20863,7 @@
         <v>602.27</v>
       </c>
       <c r="Q82">
-        <v>296.5</v>
+        <v>722</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -20940,7 +20940,7 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>-71.5</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>2194.29</v>
       </c>
       <c r="Q84">
-        <v>686.3</v>
+        <v>1546.27</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -21094,7 +21094,7 @@
         <v>3388.07</v>
       </c>
       <c r="Q85">
-        <v>2210</v>
+        <v>3638.36</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -22172,7 +22172,7 @@
         <v>78.959999999999994</v>
       </c>
       <c r="Q99">
-        <v>55.38</v>
+        <v>242.74</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>111.98</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -23943,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>95</v>
+        <v>350.03</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -24020,7 +24020,7 @@
         <v>21.49</v>
       </c>
       <c r="Q123">
-        <v>197.48</v>
+        <v>242.07</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -24097,7 +24097,7 @@
         <v>215.71</v>
       </c>
       <c r="Q124">
-        <v>278.29000000000002</v>
+        <v>726.81</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -24174,7 +24174,7 @@
         <v>251.25</v>
       </c>
       <c r="Q125">
-        <v>1554.74</v>
+        <v>1601.95</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -24559,7 +24559,7 @@
         <v>345.6</v>
       </c>
       <c r="Q130">
-        <v>537.96</v>
+        <v>895.76</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -24636,7 +24636,7 @@
         <v>576.95000000000005</v>
       </c>
       <c r="Q131">
-        <v>22.1</v>
+        <v>-689.7</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -24713,7 +24713,7 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>201.33</v>
+        <v>264.05</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -24867,7 +24867,7 @@
         <v>234.83</v>
       </c>
       <c r="Q134">
-        <v>-31.88</v>
+        <v>-32.08</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -24944,7 +24944,7 @@
         <v>1925.14</v>
       </c>
       <c r="Q135">
-        <v>1686.55</v>
+        <v>2126.4299999999998</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -25945,7 +25945,7 @@
         <v>480.72</v>
       </c>
       <c r="Q148">
-        <v>675.36</v>
+        <v>760.47</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -26022,7 +26022,7 @@
         <v>346.28</v>
       </c>
       <c r="Q149">
-        <v>547.78</v>
+        <v>788.83</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -26099,7 +26099,7 @@
         <v>580.64</v>
       </c>
       <c r="Q150">
-        <v>977.98</v>
+        <v>1467.78</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>55.34</v>
       </c>
       <c r="Q153">
-        <v>19.899999999999999</v>
+        <v>63.65</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -26484,7 +26484,7 @@
         <v>299.39999999999998</v>
       </c>
       <c r="Q155">
-        <v>278.5</v>
+        <v>313.89999999999998</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -26561,7 +26561,7 @@
         <v>204.1</v>
       </c>
       <c r="Q156">
-        <v>1058.43</v>
+        <v>1196.1300000000001</v>
       </c>
       <c r="R156">
         <v>0</v>
@@ -26792,7 +26792,7 @@
         <v>479.45</v>
       </c>
       <c r="Q159">
-        <v>47.25</v>
+        <v>173.35</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -26869,7 +26869,7 @@
         <v>576.54999999999995</v>
       </c>
       <c r="Q160">
-        <v>59.5</v>
+        <v>129.4</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -29487,7 +29487,7 @@
         <v>24871.29</v>
       </c>
       <c r="Q194">
-        <v>10679.38</v>
+        <v>13513.36</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -29718,7 +29718,7 @@
         <v>5789.04</v>
       </c>
       <c r="Q197">
-        <v>1802.6</v>
+        <v>2212.23</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -29795,7 +29795,7 @@
         <v>9659.8799999999992</v>
       </c>
       <c r="Q198">
-        <v>3843.75</v>
+        <v>6416.32</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         <v>9559.2900000000009</v>
       </c>
       <c r="Q199">
-        <v>3932.24</v>
+        <v>8433.17</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>15228.52</v>
       </c>
       <c r="Q200">
-        <v>11939.54</v>
+        <v>23252.57</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -30026,7 +30026,7 @@
         <v>1144.96</v>
       </c>
       <c r="Q201">
-        <v>584.35</v>
+        <v>1091</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -30180,7 +30180,7 @@
         <v>5219.09</v>
       </c>
       <c r="Q203">
-        <v>236.46</v>
+        <v>1932.62</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -30257,7 +30257,7 @@
         <v>3277.5</v>
       </c>
       <c r="Q204">
-        <v>579.70000000000005</v>
+        <v>1065.5</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -30334,7 +30334,7 @@
         <v>109105.36</v>
       </c>
       <c r="Q205">
-        <v>65970.149999999994</v>
+        <v>140533.95000000001</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -30411,7 +30411,7 @@
         <v>8645.2900000000009</v>
       </c>
       <c r="Q206">
-        <v>7941.62</v>
+        <v>11067.99</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -30488,7 +30488,7 @@
         <v>773.75</v>
       </c>
       <c r="Q207">
-        <v>1563.43</v>
+        <v>3159.05</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -30565,7 +30565,7 @@
         <v>433</v>
       </c>
       <c r="Q208">
-        <v>1434.7</v>
+        <v>3080.3</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -30642,7 +30642,7 @@
         <v>5292.88</v>
       </c>
       <c r="Q209">
-        <v>3277.89</v>
+        <v>6905.03</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -30719,7 +30719,7 @@
         <v>29215.86</v>
       </c>
       <c r="Q210">
-        <v>13566.5</v>
+        <v>30412.48</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -31412,7 +31412,7 @@
         <v>6246.19</v>
       </c>
       <c r="Q219">
-        <v>3045.13</v>
+        <v>34917.06</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -31643,7 +31643,7 @@
         <v>6632.2</v>
       </c>
       <c r="Q222">
-        <v>4016.4</v>
+        <v>4451.8999999999996</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -31720,7 +31720,7 @@
         <v>4704.99</v>
       </c>
       <c r="Q223">
-        <v>1449.66</v>
+        <v>3912.19</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -31797,7 +31797,7 @@
         <v>3870.6</v>
       </c>
       <c r="Q224">
-        <v>3710.98</v>
+        <v>8120.15</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -31874,7 +31874,7 @@
         <v>11596.46</v>
       </c>
       <c r="Q225">
-        <v>2148.77</v>
+        <v>7683.51</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -31951,7 +31951,7 @@
         <v>398.36</v>
       </c>
       <c r="Q226">
-        <v>535.35</v>
+        <v>1334.74</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -32105,7 +32105,7 @@
         <v>3172.3</v>
       </c>
       <c r="Q228">
-        <v>391.6</v>
+        <v>1381.2</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -32182,7 +32182,7 @@
         <v>929.45</v>
       </c>
       <c r="Q229">
-        <v>1592.96</v>
+        <v>2492.86</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -32259,7 +32259,7 @@
         <v>32127.45</v>
       </c>
       <c r="Q230">
-        <v>16726.759999999998</v>
+        <v>37277.550000000003</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -32336,7 +32336,7 @@
         <v>5550.91</v>
       </c>
       <c r="Q231">
-        <v>4782.37</v>
+        <v>8882.25</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -32413,7 +32413,7 @@
         <v>2377.84</v>
       </c>
       <c r="Q232">
-        <v>810.78</v>
+        <v>1782.09</v>
       </c>
       <c r="R232">
         <v>0</v>
@@ -32490,7 +32490,7 @@
         <v>3520.64</v>
       </c>
       <c r="Q233">
-        <v>2591.9899999999998</v>
+        <v>4342.83</v>
       </c>
       <c r="R233">
         <v>0</v>
@@ -32567,7 +32567,7 @@
         <v>3929.27</v>
       </c>
       <c r="Q234">
-        <v>2040.05</v>
+        <v>3780.23</v>
       </c>
       <c r="R234">
         <v>0</v>
@@ -32644,7 +32644,7 @@
         <v>9688.98</v>
       </c>
       <c r="Q235">
-        <v>5638.46</v>
+        <v>11364.53</v>
       </c>
       <c r="R235">
         <v>0</v>
@@ -32798,7 +32798,7 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R237">
         <v>0</v>
@@ -33337,7 +33337,7 @@
         <v>4398.3599999999997</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>5300.64</v>
       </c>
       <c r="R244">
         <v>0</v>
@@ -33568,7 +33568,7 @@
         <v>4088.06</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>95.65</v>
       </c>
       <c r="R247">
         <v>0</v>
@@ -33645,7 +33645,7 @@
         <v>3164.56</v>
       </c>
       <c r="Q248">
-        <v>-19.899999999999999</v>
+        <v>1639.56</v>
       </c>
       <c r="R248">
         <v>0</v>
@@ -33722,7 +33722,7 @@
         <v>10864.67</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>1693.68</v>
       </c>
       <c r="R249">
         <v>0</v>
@@ -33799,7 +33799,7 @@
         <v>10356.299999999999</v>
       </c>
       <c r="Q250">
-        <v>85.35</v>
+        <v>2136.92</v>
       </c>
       <c r="R250">
         <v>0</v>
@@ -33876,7 +33876,7 @@
         <v>698.55</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>210.15</v>
       </c>
       <c r="R251">
         <v>0</v>
@@ -34030,7 +34030,7 @@
         <v>1435.9</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>205.25</v>
       </c>
       <c r="R253">
         <v>0</v>
@@ -34107,7 +34107,7 @@
         <v>598.35</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>125.9</v>
       </c>
       <c r="R254">
         <v>0</v>
@@ -34184,7 +34184,7 @@
         <v>25275.11</v>
       </c>
       <c r="Q255">
-        <v>-135.80000000000001</v>
+        <v>15308.58</v>
       </c>
       <c r="R255">
         <v>0</v>
@@ -34261,7 +34261,7 @@
         <v>5383.38</v>
       </c>
       <c r="Q256">
-        <v>-27.9</v>
+        <v>3839.83</v>
       </c>
       <c r="R256">
         <v>0</v>
@@ -34338,7 +34338,7 @@
         <v>1675.86</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>343.2</v>
       </c>
       <c r="R257">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>1479.4</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>869.9</v>
       </c>
       <c r="R258">
         <v>0</v>
@@ -34492,7 +34492,7 @@
         <v>4228.5600000000004</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>1426.85</v>
       </c>
       <c r="R259">
         <v>0</v>
@@ -34569,7 +34569,7 @@
         <v>22534.81</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>3255.6</v>
       </c>
       <c r="R260">
         <v>0</v>
@@ -37122,7 +37122,7 @@
       </c>
       <c r="Q299">
         <f t="shared" si="0"/>
-        <v>216374.56000000003</v>
+        <v>480628.10000000015</v>
       </c>
       <c r="R299">
         <f t="shared" si="0"/>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA998F53-291B-4DC6-BA60-9DE6F67C9909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB9A036-7BBF-4FDF-AB95-087E7843BDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -252,7 +252,7 @@
             <v>67</v>
           </cell>
           <cell r="BM93">
-            <v>68</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="94">
@@ -299,7 +299,7 @@
             <v>91</v>
           </cell>
           <cell r="BM94">
-            <v>90</v>
+            <v>98</v>
           </cell>
         </row>
         <row r="95">
@@ -346,7 +346,7 @@
             <v>185</v>
           </cell>
           <cell r="BM95">
-            <v>200</v>
+            <v>229</v>
           </cell>
         </row>
         <row r="96">
@@ -440,7 +440,7 @@
             <v>36</v>
           </cell>
           <cell r="BM97">
-            <v>42</v>
+            <v>45</v>
           </cell>
         </row>
         <row r="98">
@@ -487,7 +487,7 @@
             <v>70</v>
           </cell>
           <cell r="BM98">
-            <v>81</v>
+            <v>89</v>
           </cell>
         </row>
         <row r="99">
@@ -581,7 +581,7 @@
             <v>751</v>
           </cell>
           <cell r="BM100">
-            <v>849</v>
+            <v>931</v>
           </cell>
         </row>
         <row r="101">
@@ -628,7 +628,7 @@
             <v>561</v>
           </cell>
           <cell r="BM101">
-            <v>678</v>
+            <v>773</v>
           </cell>
         </row>
         <row r="102">
@@ -675,7 +675,7 @@
             <v>588</v>
           </cell>
           <cell r="BM102">
-            <v>236</v>
+            <v>307</v>
           </cell>
         </row>
         <row r="103">
@@ -792,10 +792,10 @@
             <v>0</v>
           </cell>
           <cell r="BL117">
-            <v>1058</v>
+            <v>1000.4</v>
           </cell>
           <cell r="BM117">
-            <v>0</v>
+            <v>4.5</v>
           </cell>
         </row>
         <row r="118">
@@ -1004,10 +1004,10 @@
             <v>523.79</v>
           </cell>
           <cell r="BL121">
-            <v>441.75</v>
+            <v>431.35</v>
           </cell>
           <cell r="BM121">
-            <v>223.85</v>
+            <v>262.57</v>
           </cell>
         </row>
         <row r="122">
@@ -1060,7 +1060,7 @@
             <v>545.91</v>
           </cell>
           <cell r="BM122">
-            <v>743.12</v>
+            <v>942.63</v>
           </cell>
         </row>
         <row r="123">
@@ -1113,7 +1113,7 @@
             <v>573.30999999999995</v>
           </cell>
           <cell r="BM123">
-            <v>445.85</v>
+            <v>466.3</v>
           </cell>
         </row>
         <row r="124">
@@ -1166,7 +1166,7 @@
             <v>39.4</v>
           </cell>
           <cell r="BM124">
-            <v>76.3</v>
+            <v>116.2</v>
           </cell>
         </row>
         <row r="125">
@@ -1269,7 +1269,7 @@
             <v>213.94</v>
           </cell>
           <cell r="BL126">
-            <v>95.9</v>
+            <v>95.5</v>
           </cell>
           <cell r="BM126">
             <v>1000.25</v>
@@ -1375,10 +1375,10 @@
             <v>1664.01</v>
           </cell>
           <cell r="BL128">
-            <v>4848</v>
+            <v>4907.5</v>
           </cell>
           <cell r="BM128">
-            <v>378.3</v>
+            <v>401.9</v>
           </cell>
         </row>
         <row r="129">
@@ -1590,7 +1590,7 @@
             <v>86.7</v>
           </cell>
           <cell r="BM132">
-            <v>299.55</v>
+            <v>319.45</v>
           </cell>
         </row>
         <row r="133">
@@ -1643,7 +1643,7 @@
             <v>758.05</v>
           </cell>
           <cell r="BM133">
-            <v>371</v>
+            <v>367</v>
           </cell>
         </row>
         <row r="134">
@@ -2170,7 +2170,7 @@
             <v>0</v>
           </cell>
           <cell r="BL145">
-            <v>962.3</v>
+            <v>956.3</v>
           </cell>
           <cell r="BM145">
             <v>419.6</v>
@@ -2223,10 +2223,10 @@
             <v>423.9</v>
           </cell>
           <cell r="BL146">
-            <v>619.61</v>
+            <v>617.37</v>
           </cell>
           <cell r="BM146">
-            <v>960.64</v>
+            <v>1020.54</v>
           </cell>
         </row>
         <row r="147">
@@ -2276,10 +2276,10 @@
             <v>6771.6</v>
           </cell>
           <cell r="BL147">
-            <v>991.28</v>
+            <v>977.28</v>
           </cell>
           <cell r="BM147">
-            <v>824.11</v>
+            <v>857.01</v>
           </cell>
         </row>
         <row r="148">
@@ -2329,10 +2329,10 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>491.91</v>
+            <v>489.21</v>
           </cell>
           <cell r="BM148">
-            <v>1548.72</v>
+            <v>1548.42</v>
           </cell>
         </row>
         <row r="149">
@@ -2491,7 +2491,7 @@
             <v>74.64</v>
           </cell>
           <cell r="BM151">
-            <v>112.15</v>
+            <v>136.05000000000001</v>
           </cell>
         </row>
         <row r="152">
@@ -2594,7 +2594,7 @@
             <v>6968.14</v>
           </cell>
           <cell r="BL153">
-            <v>743.18</v>
+            <v>742.58</v>
           </cell>
           <cell r="BM153">
             <v>6574.25</v>
@@ -2650,7 +2650,7 @@
             <v>1244.1199999999999</v>
           </cell>
           <cell r="BM154">
-            <v>180.6</v>
+            <v>200.85</v>
           </cell>
         </row>
         <row r="155">
@@ -2700,7 +2700,7 @@
             <v>275.2</v>
           </cell>
           <cell r="BL155">
-            <v>321.42</v>
+            <v>322.92</v>
           </cell>
           <cell r="BM155">
             <v>681.73</v>
@@ -2806,10 +2806,10 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>652.88</v>
+            <v>648.23</v>
           </cell>
           <cell r="BM157">
-            <v>322.99</v>
+            <v>277.56</v>
           </cell>
         </row>
         <row r="158">
@@ -2862,7 +2862,7 @@
             <v>261.3</v>
           </cell>
           <cell r="BM158">
-            <v>809.13</v>
+            <v>820.93</v>
           </cell>
         </row>
         <row r="159">
@@ -3230,10 +3230,10 @@
             <v>1528.85</v>
           </cell>
           <cell r="BL167">
-            <v>2994.32</v>
+            <v>2968.32</v>
           </cell>
           <cell r="BM167">
-            <v>1477.89</v>
+            <v>1483.88</v>
           </cell>
         </row>
         <row r="168">
@@ -3392,7 +3392,7 @@
             <v>699.1</v>
           </cell>
           <cell r="BM170">
-            <v>1507.5</v>
+            <v>2721.3</v>
           </cell>
         </row>
         <row r="171">
@@ -3442,10 +3442,10 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>939.09</v>
+            <v>922.29</v>
           </cell>
           <cell r="BM171">
-            <v>626.61</v>
+            <v>702.81</v>
           </cell>
         </row>
         <row r="172">
@@ -3495,10 +3495,10 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>1279.22</v>
+            <v>1249.54</v>
           </cell>
           <cell r="BM172">
-            <v>2189.0700000000002</v>
+            <v>2628</v>
           </cell>
         </row>
         <row r="173">
@@ -3548,10 +3548,10 @@
             <v>5782.77</v>
           </cell>
           <cell r="BL173">
-            <v>1332.67</v>
+            <v>1297.72</v>
           </cell>
           <cell r="BM173">
-            <v>2194.5300000000002</v>
+            <v>2287.31</v>
           </cell>
         </row>
         <row r="174">
@@ -3604,7 +3604,7 @@
             <v>158.19999999999999</v>
           </cell>
           <cell r="BM174">
-            <v>435.32</v>
+            <v>440.27</v>
           </cell>
         </row>
         <row r="175">
@@ -3710,7 +3710,7 @@
             <v>209.83</v>
           </cell>
           <cell r="BM176">
-            <v>94.6</v>
+            <v>161.9</v>
           </cell>
         </row>
         <row r="177">
@@ -3763,7 +3763,7 @@
             <v>955.8</v>
           </cell>
           <cell r="BM177">
-            <v>296</v>
+            <v>535.85</v>
           </cell>
         </row>
         <row r="178">
@@ -3813,10 +3813,10 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>4758.8500000000004</v>
+            <v>4711.63</v>
           </cell>
           <cell r="BM178">
-            <v>8502.61</v>
+            <v>9459.86</v>
           </cell>
         </row>
         <row r="179">
@@ -3866,10 +3866,10 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>2196.5100000000002</v>
+            <v>2169.31</v>
           </cell>
           <cell r="BM179">
-            <v>980.88</v>
+            <v>980.38</v>
           </cell>
         </row>
         <row r="180">
@@ -3919,7 +3919,7 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>602.27</v>
+            <v>599.77</v>
           </cell>
           <cell r="BM180">
             <v>722</v>
@@ -4025,10 +4025,10 @@
             <v>2160.71</v>
           </cell>
           <cell r="BL182">
-            <v>2194.29</v>
+            <v>2174.7600000000002</v>
           </cell>
           <cell r="BM182">
-            <v>1546.27</v>
+            <v>1603.37</v>
           </cell>
         </row>
         <row r="183">
@@ -4078,10 +4078,10 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>3388.07</v>
+            <v>3386.07</v>
           </cell>
           <cell r="BM183">
-            <v>3638.36</v>
+            <v>5672.19</v>
           </cell>
         </row>
         <row r="184">
@@ -5883,7 +5883,7 @@
             <v>21.49</v>
           </cell>
           <cell r="BM221">
-            <v>242.07</v>
+            <v>265.47000000000003</v>
           </cell>
         </row>
         <row r="222">
@@ -5936,7 +5936,7 @@
             <v>215.71</v>
           </cell>
           <cell r="BM222">
-            <v>726.81</v>
+            <v>738.36</v>
           </cell>
         </row>
         <row r="223">
@@ -5986,10 +5986,10 @@
             <v>788.08</v>
           </cell>
           <cell r="BL223">
-            <v>251.25</v>
+            <v>249.25</v>
           </cell>
           <cell r="BM223">
-            <v>1601.95</v>
+            <v>1605.65</v>
           </cell>
         </row>
         <row r="224">
@@ -6039,7 +6039,7 @@
             <v>349.1</v>
           </cell>
           <cell r="BL224">
-            <v>249.5</v>
+            <v>245.5</v>
           </cell>
           <cell r="BM224">
             <v>-20.85</v>
@@ -6304,7 +6304,7 @@
             <v>128.09</v>
           </cell>
           <cell r="BL229">
-            <v>576.95000000000005</v>
+            <v>576.45000000000005</v>
           </cell>
           <cell r="BM229">
             <v>-689.7</v>
@@ -6887,7 +6887,7 @@
             <v>247.5</v>
           </cell>
           <cell r="BL242">
-            <v>78.8</v>
+            <v>80.8</v>
           </cell>
           <cell r="BM242">
             <v>0</v>
@@ -7099,10 +7099,10 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>480.72</v>
+            <v>480.84</v>
           </cell>
           <cell r="BM246">
-            <v>760.47</v>
+            <v>917.97</v>
           </cell>
         </row>
         <row r="247">
@@ -7152,10 +7152,10 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>346.28</v>
+            <v>346.03</v>
           </cell>
           <cell r="BM247">
-            <v>788.83</v>
+            <v>922.38</v>
           </cell>
         </row>
         <row r="248">
@@ -7205,10 +7205,10 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>580.64</v>
+            <v>579.89</v>
           </cell>
           <cell r="BM248">
-            <v>1467.78</v>
+            <v>1441.04</v>
           </cell>
         </row>
         <row r="249">
@@ -7258,7 +7258,7 @@
             <v>341.25</v>
           </cell>
           <cell r="BL249">
-            <v>23.8</v>
+            <v>21.9</v>
           </cell>
           <cell r="BM249">
             <v>9.85</v>
@@ -7473,7 +7473,7 @@
             <v>299.39999999999998</v>
           </cell>
           <cell r="BM253">
-            <v>313.89999999999998</v>
+            <v>626.65</v>
           </cell>
         </row>
         <row r="254">
@@ -7523,7 +7523,7 @@
             <v>1217.27</v>
           </cell>
           <cell r="BL254">
-            <v>204.1</v>
+            <v>199.5</v>
           </cell>
           <cell r="BM254">
             <v>1196.1300000000001</v>
@@ -7682,10 +7682,10 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>479.45</v>
+            <v>478.45</v>
           </cell>
           <cell r="BM257">
-            <v>173.35</v>
+            <v>193.25</v>
           </cell>
         </row>
         <row r="258">
@@ -7735,7 +7735,7 @@
             <v>282.8</v>
           </cell>
           <cell r="BL258">
-            <v>576.54999999999995</v>
+            <v>570.54999999999995</v>
           </cell>
           <cell r="BM258">
             <v>129.4</v>
@@ -9325,10 +9325,10 @@
             <v>10911.5</v>
           </cell>
           <cell r="BL292">
-            <v>24871.29</v>
+            <v>24138.79</v>
           </cell>
           <cell r="BM292">
-            <v>13513.36</v>
+            <v>14178.59</v>
           </cell>
         </row>
         <row r="293">
@@ -9484,10 +9484,10 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>5789.04</v>
+            <v>5711.04</v>
           </cell>
           <cell r="BM295">
-            <v>2212.23</v>
+            <v>8949.08</v>
           </cell>
         </row>
         <row r="296">
@@ -9537,10 +9537,10 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>9659.8799999999992</v>
+            <v>9333.11</v>
           </cell>
           <cell r="BM296">
-            <v>6416.32</v>
+            <v>7210.03</v>
           </cell>
         </row>
         <row r="297">
@@ -9590,10 +9590,10 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>9559.2900000000009</v>
+            <v>9442.14</v>
           </cell>
           <cell r="BM297">
-            <v>8433.17</v>
+            <v>9124.7999999999993</v>
           </cell>
         </row>
         <row r="298">
@@ -9643,10 +9643,10 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>15228.52</v>
+            <v>15207.07</v>
           </cell>
           <cell r="BM298">
-            <v>23252.57</v>
+            <v>24610.58</v>
           </cell>
         </row>
         <row r="299">
@@ -9696,10 +9696,10 @@
             <v>819.93</v>
           </cell>
           <cell r="BL299">
-            <v>1144.96</v>
+            <v>1139.6099999999999</v>
           </cell>
           <cell r="BM299">
-            <v>1091</v>
+            <v>1207.5999999999999</v>
           </cell>
         </row>
         <row r="300">
@@ -9802,10 +9802,10 @@
             <v>1498.34</v>
           </cell>
           <cell r="BL301">
-            <v>5219.09</v>
+            <v>5217.09</v>
           </cell>
           <cell r="BM301">
-            <v>1932.62</v>
+            <v>2077.17</v>
           </cell>
         </row>
         <row r="302">
@@ -9855,7 +9855,7 @@
             <v>2807.35</v>
           </cell>
           <cell r="BL302">
-            <v>3277.5</v>
+            <v>3033.37</v>
           </cell>
           <cell r="BM302">
             <v>1065.5</v>
@@ -9908,10 +9908,10 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>109105.36</v>
+            <v>106807.48</v>
           </cell>
           <cell r="BM303">
-            <v>140533.95000000001</v>
+            <v>147588.69</v>
           </cell>
         </row>
         <row r="304">
@@ -9961,10 +9961,10 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>8645.2900000000009</v>
+            <v>8614.8700000000008</v>
           </cell>
           <cell r="BM304">
-            <v>11067.99</v>
+            <v>14286.32</v>
           </cell>
         </row>
         <row r="305">
@@ -10014,10 +10014,10 @@
             <v>3782.99</v>
           </cell>
           <cell r="BL305">
-            <v>773.75</v>
+            <v>785.13</v>
           </cell>
           <cell r="BM305">
-            <v>3159.05</v>
+            <v>3428.8</v>
           </cell>
         </row>
         <row r="306">
@@ -10070,7 +10070,7 @@
             <v>433</v>
           </cell>
           <cell r="BM306">
-            <v>3080.3</v>
+            <v>3199.8</v>
           </cell>
         </row>
         <row r="307">
@@ -10120,10 +10120,10 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>5292.88</v>
+            <v>5259.18</v>
           </cell>
           <cell r="BM307">
-            <v>6905.03</v>
+            <v>7557.23</v>
           </cell>
         </row>
         <row r="308">
@@ -10173,10 +10173,10 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>29215.86</v>
+            <v>29048.79</v>
           </cell>
           <cell r="BM308">
-            <v>30412.48</v>
+            <v>33128.39</v>
           </cell>
         </row>
         <row r="309">
@@ -10282,7 +10282,7 @@
             <v>0</v>
           </cell>
           <cell r="BM310">
-            <v>7.9</v>
+            <v>7.5</v>
           </cell>
         </row>
         <row r="311">
@@ -10544,10 +10544,10 @@
             <v>5408.2</v>
           </cell>
           <cell r="BL317">
-            <v>6246.19</v>
+            <v>6215.59</v>
           </cell>
           <cell r="BM317">
-            <v>34917.06</v>
+            <v>35040.86</v>
           </cell>
         </row>
         <row r="318">
@@ -10703,10 +10703,10 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>6632.2</v>
+            <v>6598.1</v>
           </cell>
           <cell r="BM320">
-            <v>4451.8999999999996</v>
+            <v>5147.7</v>
           </cell>
         </row>
         <row r="321">
@@ -10756,10 +10756,10 @@
             <v>2748.05</v>
           </cell>
           <cell r="BL321">
-            <v>4704.99</v>
+            <v>4660.79</v>
           </cell>
           <cell r="BM321">
-            <v>3912.19</v>
+            <v>4324.5200000000004</v>
           </cell>
         </row>
         <row r="322">
@@ -10809,10 +10809,10 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>3870.6</v>
+            <v>3829.06</v>
           </cell>
           <cell r="BM322">
-            <v>8120.15</v>
+            <v>8760.93</v>
           </cell>
         </row>
         <row r="323">
@@ -10862,10 +10862,10 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>11596.46</v>
+            <v>11295.1</v>
           </cell>
           <cell r="BM323">
-            <v>7683.51</v>
+            <v>8340.2199999999993</v>
           </cell>
         </row>
         <row r="324">
@@ -10915,10 +10915,10 @@
             <v>630.75</v>
           </cell>
           <cell r="BL324">
-            <v>398.36</v>
+            <v>399.66</v>
           </cell>
           <cell r="BM324">
-            <v>1334.74</v>
+            <v>1443.59</v>
           </cell>
         </row>
         <row r="325">
@@ -11021,10 +11021,10 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>3172.3</v>
+            <v>3167.3</v>
           </cell>
           <cell r="BM326">
-            <v>1381.2</v>
+            <v>1511.5</v>
           </cell>
         </row>
         <row r="327">
@@ -11074,7 +11074,7 @@
             <v>3384.9</v>
           </cell>
           <cell r="BL327">
-            <v>929.45</v>
+            <v>923.4</v>
           </cell>
           <cell r="BM327">
             <v>2492.86</v>
@@ -11127,10 +11127,10 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>32127.45</v>
+            <v>31452.35</v>
           </cell>
           <cell r="BM328">
-            <v>37277.550000000003</v>
+            <v>41527.599999999999</v>
           </cell>
         </row>
         <row r="329">
@@ -11180,10 +11180,10 @@
             <v>4790.9799999999996</v>
           </cell>
           <cell r="BL329">
-            <v>5550.91</v>
+            <v>5543.11</v>
           </cell>
           <cell r="BM329">
-            <v>8882.25</v>
+            <v>9476.17</v>
           </cell>
         </row>
         <row r="330">
@@ -11233,10 +11233,10 @@
             <v>2022.35</v>
           </cell>
           <cell r="BL330">
-            <v>2377.84</v>
+            <v>2358.44</v>
           </cell>
           <cell r="BM330">
-            <v>1782.09</v>
+            <v>2064.59</v>
           </cell>
         </row>
         <row r="331">
@@ -11286,7 +11286,7 @@
             <v>1507.74</v>
           </cell>
           <cell r="BL331">
-            <v>3520.64</v>
+            <v>3518.04</v>
           </cell>
           <cell r="BM331">
             <v>4342.83</v>
@@ -11339,10 +11339,10 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>3929.27</v>
+            <v>3903.29</v>
           </cell>
           <cell r="BM332">
-            <v>3780.23</v>
+            <v>4283.58</v>
           </cell>
         </row>
         <row r="333">
@@ -11392,10 +11392,10 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>9688.98</v>
+            <v>9683.18</v>
           </cell>
           <cell r="BM333">
-            <v>11364.53</v>
+            <v>11938.2</v>
           </cell>
         </row>
         <row r="334">
@@ -11763,10 +11763,10 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>4398.3599999999997</v>
+            <v>4185.03</v>
           </cell>
           <cell r="BM342">
-            <v>5300.64</v>
+            <v>7223.84</v>
           </cell>
         </row>
         <row r="343">
@@ -11922,10 +11922,10 @@
             <v>1706.35</v>
           </cell>
           <cell r="BL345">
-            <v>4088.06</v>
+            <v>4026.26</v>
           </cell>
           <cell r="BM345">
-            <v>95.65</v>
+            <v>162.44999999999999</v>
           </cell>
         </row>
         <row r="346">
@@ -11975,10 +11975,10 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>3164.56</v>
+            <v>3153.16</v>
           </cell>
           <cell r="BM346">
-            <v>1639.56</v>
+            <v>2023.52</v>
           </cell>
         </row>
         <row r="347">
@@ -12028,10 +12028,10 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>10864.67</v>
+            <v>10828.47</v>
           </cell>
           <cell r="BM347">
-            <v>1693.68</v>
+            <v>2343.33</v>
           </cell>
         </row>
         <row r="348">
@@ -12081,10 +12081,10 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>10356.299999999999</v>
+            <v>10305.14</v>
           </cell>
           <cell r="BM348">
-            <v>2136.92</v>
+            <v>3386.84</v>
           </cell>
         </row>
         <row r="349">
@@ -12240,10 +12240,10 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>1435.9</v>
+            <v>1426.9</v>
           </cell>
           <cell r="BM351">
-            <v>205.25</v>
+            <v>314.25</v>
           </cell>
         </row>
         <row r="352">
@@ -12293,7 +12293,7 @@
             <v>2460.85</v>
           </cell>
           <cell r="BL352">
-            <v>598.35</v>
+            <v>588.35</v>
           </cell>
           <cell r="BM352">
             <v>125.9</v>
@@ -12346,10 +12346,10 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>25275.11</v>
+            <v>24549.61</v>
           </cell>
           <cell r="BM353">
-            <v>15308.58</v>
+            <v>16771.03</v>
           </cell>
         </row>
         <row r="354">
@@ -12399,10 +12399,10 @@
             <v>6679.21</v>
           </cell>
           <cell r="BL354">
-            <v>5383.38</v>
+            <v>5359.38</v>
           </cell>
           <cell r="BM354">
-            <v>3839.83</v>
+            <v>4042.43</v>
           </cell>
         </row>
         <row r="355">
@@ -12452,10 +12452,10 @@
             <v>3019.73</v>
           </cell>
           <cell r="BL355">
-            <v>1675.86</v>
+            <v>1671.86</v>
           </cell>
           <cell r="BM355">
-            <v>343.2</v>
+            <v>438.2</v>
           </cell>
         </row>
         <row r="356">
@@ -12508,7 +12508,7 @@
             <v>1479.4</v>
           </cell>
           <cell r="BM356">
-            <v>869.9</v>
+            <v>1259.8</v>
           </cell>
         </row>
         <row r="357">
@@ -12558,10 +12558,10 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>4228.5600000000004</v>
+            <v>4179.3599999999997</v>
           </cell>
           <cell r="BM357">
-            <v>1426.85</v>
+            <v>1815.35</v>
           </cell>
         </row>
         <row r="358">
@@ -12611,10 +12611,10 @@
             <v>18146.46</v>
           </cell>
           <cell r="BL358">
-            <v>22534.81</v>
+            <v>22340.61</v>
           </cell>
           <cell r="BM358">
-            <v>3255.6</v>
+            <v>5642.79</v>
           </cell>
         </row>
         <row r="359">
@@ -13857,7 +13857,7 @@
         <v>67</v>
       </c>
       <c r="Q4">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>91</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -14233,7 +14233,7 @@
         <v>185</v>
       </c>
       <c r="Q6">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -14609,7 +14609,7 @@
         <v>36</v>
       </c>
       <c r="Q8">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -14797,7 +14797,7 @@
         <v>70</v>
       </c>
       <c r="Q9">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -15173,7 +15173,7 @@
         <v>751</v>
       </c>
       <c r="Q11">
-        <v>849</v>
+        <v>931</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -15361,7 +15361,7 @@
         <v>561</v>
       </c>
       <c r="Q12">
-        <v>678</v>
+        <v>773</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -15549,7 +15549,7 @@
         <v>588</v>
       </c>
       <c r="Q13">
-        <v>236</v>
+        <v>307</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -16009,10 +16009,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1058</v>
+        <v>1000.4</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>523.79</v>
       </c>
       <c r="P23">
-        <v>441.75</v>
+        <v>431.35</v>
       </c>
       <c r="Q23">
-        <v>223.85</v>
+        <v>262.57</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -16397,7 +16397,7 @@
         <v>545.91</v>
       </c>
       <c r="Q24">
-        <v>743.12</v>
+        <v>942.63</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>573.30999999999995</v>
       </c>
       <c r="Q25">
-        <v>445.85</v>
+        <v>466.3</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>39.4</v>
       </c>
       <c r="Q26">
-        <v>76.3</v>
+        <v>116.2</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -16702,7 +16702,7 @@
         <v>213.94</v>
       </c>
       <c r="P28">
-        <v>95.9</v>
+        <v>95.5</v>
       </c>
       <c r="Q28">
         <v>1000.25</v>
@@ -16856,10 +16856,10 @@
         <v>1664.01</v>
       </c>
       <c r="P30">
-        <v>4848</v>
+        <v>4907.5</v>
       </c>
       <c r="Q30">
-        <v>378.3</v>
+        <v>401.9</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -17167,7 +17167,7 @@
         <v>86.7</v>
       </c>
       <c r="Q34">
-        <v>299.55</v>
+        <v>319.45</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>758.05</v>
       </c>
       <c r="Q35">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -18165,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>962.3</v>
+        <v>956.3</v>
       </c>
       <c r="Q47">
         <v>419.6</v>
@@ -18242,10 +18242,10 @@
         <v>423.9</v>
       </c>
       <c r="P48">
-        <v>619.61</v>
+        <v>617.37</v>
       </c>
       <c r="Q48">
-        <v>960.64</v>
+        <v>1020.54</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -18319,10 +18319,10 @@
         <v>6771.6</v>
       </c>
       <c r="P49">
-        <v>991.28</v>
+        <v>977.28</v>
       </c>
       <c r="Q49">
-        <v>824.11</v>
+        <v>857.01</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -18396,10 +18396,10 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>491.91</v>
+        <v>489.21</v>
       </c>
       <c r="Q50">
-        <v>1548.72</v>
+        <v>1548.42</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -18630,7 +18630,7 @@
         <v>74.64</v>
       </c>
       <c r="Q53">
-        <v>112.15</v>
+        <v>136.05000000000001</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -18781,7 +18781,7 @@
         <v>6968.14</v>
       </c>
       <c r="P55">
-        <v>743.18</v>
+        <v>742.58</v>
       </c>
       <c r="Q55">
         <v>6574.25</v>
@@ -18861,7 +18861,7 @@
         <v>1244.1199999999999</v>
       </c>
       <c r="Q56">
-        <v>180.6</v>
+        <v>200.85</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>275.2</v>
       </c>
       <c r="P57">
-        <v>321.42</v>
+        <v>322.92</v>
       </c>
       <c r="Q57">
         <v>681.73</v>
@@ -19089,10 +19089,10 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>652.88</v>
+        <v>648.23</v>
       </c>
       <c r="Q59">
-        <v>322.99</v>
+        <v>277.56</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -19169,7 +19169,7 @@
         <v>261.3</v>
       </c>
       <c r="Q60">
-        <v>809.13</v>
+        <v>820.93</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -19859,10 +19859,10 @@
         <v>1528.85</v>
       </c>
       <c r="P69">
-        <v>2994.32</v>
+        <v>2968.32</v>
       </c>
       <c r="Q69">
-        <v>1477.89</v>
+        <v>1483.88</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -20093,7 +20093,7 @@
         <v>699.1</v>
       </c>
       <c r="Q72">
-        <v>1507.5</v>
+        <v>2721.3</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -20167,10 +20167,10 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>939.09</v>
+        <v>922.29</v>
       </c>
       <c r="Q73">
-        <v>626.61</v>
+        <v>702.81</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -20244,10 +20244,10 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>1279.22</v>
+        <v>1249.54</v>
       </c>
       <c r="Q74">
-        <v>2189.0700000000002</v>
+        <v>2628</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -20321,10 +20321,10 @@
         <v>5782.77</v>
       </c>
       <c r="P75">
-        <v>1332.67</v>
+        <v>1297.72</v>
       </c>
       <c r="Q75">
-        <v>2194.5300000000002</v>
+        <v>2287.31</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -20401,7 +20401,7 @@
         <v>158.19999999999999</v>
       </c>
       <c r="Q76">
-        <v>435.32</v>
+        <v>440.27</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20555,7 +20555,7 @@
         <v>209.83</v>
       </c>
       <c r="Q78">
-        <v>94.6</v>
+        <v>161.9</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20632,7 +20632,7 @@
         <v>955.8</v>
       </c>
       <c r="Q79">
-        <v>296</v>
+        <v>535.85</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20706,10 +20706,10 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>4758.8500000000004</v>
+        <v>4711.63</v>
       </c>
       <c r="Q80">
-        <v>8502.61</v>
+        <v>9459.86</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -20783,10 +20783,10 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>2196.5100000000002</v>
+        <v>2169.31</v>
       </c>
       <c r="Q81">
-        <v>980.88</v>
+        <v>980.38</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -20860,7 +20860,7 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>602.27</v>
+        <v>599.77</v>
       </c>
       <c r="Q82">
         <v>722</v>
@@ -21014,10 +21014,10 @@
         <v>2160.71</v>
       </c>
       <c r="P84">
-        <v>2194.29</v>
+        <v>2174.7600000000002</v>
       </c>
       <c r="Q84">
-        <v>1546.27</v>
+        <v>1603.37</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -21091,10 +21091,10 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>3388.07</v>
+        <v>3386.07</v>
       </c>
       <c r="Q85">
-        <v>3638.36</v>
+        <v>5672.19</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -24020,7 +24020,7 @@
         <v>21.49</v>
       </c>
       <c r="Q123">
-        <v>242.07</v>
+        <v>265.47000000000003</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -24097,7 +24097,7 @@
         <v>215.71</v>
       </c>
       <c r="Q124">
-        <v>726.81</v>
+        <v>738.36</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -24171,10 +24171,10 @@
         <v>788.08</v>
       </c>
       <c r="P125">
-        <v>251.25</v>
+        <v>249.25</v>
       </c>
       <c r="Q125">
-        <v>1601.95</v>
+        <v>1605.65</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -24248,7 +24248,7 @@
         <v>349.1</v>
       </c>
       <c r="P126">
-        <v>249.5</v>
+        <v>245.5</v>
       </c>
       <c r="Q126">
         <v>-20.85</v>
@@ -24633,7 +24633,7 @@
         <v>128.09</v>
       </c>
       <c r="P131">
-        <v>576.95000000000005</v>
+        <v>576.45000000000005</v>
       </c>
       <c r="Q131">
         <v>-689.7</v>
@@ -25634,7 +25634,7 @@
         <v>247.5</v>
       </c>
       <c r="P144">
-        <v>78.8</v>
+        <v>80.8</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -25942,10 +25942,10 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>480.72</v>
+        <v>480.84</v>
       </c>
       <c r="Q148">
-        <v>760.47</v>
+        <v>917.97</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -26019,10 +26019,10 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>346.28</v>
+        <v>346.03</v>
       </c>
       <c r="Q149">
-        <v>788.83</v>
+        <v>922.38</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -26096,10 +26096,10 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>580.64</v>
+        <v>579.89</v>
       </c>
       <c r="Q150">
-        <v>1467.78</v>
+        <v>1441.04</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -26173,7 +26173,7 @@
         <v>341.25</v>
       </c>
       <c r="P151">
-        <v>23.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q151">
         <v>9.85</v>
@@ -26484,7 +26484,7 @@
         <v>299.39999999999998</v>
       </c>
       <c r="Q155">
-        <v>313.89999999999998</v>
+        <v>626.65</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -26558,7 +26558,7 @@
         <v>1217.27</v>
       </c>
       <c r="P156">
-        <v>204.1</v>
+        <v>199.5</v>
       </c>
       <c r="Q156">
         <v>1196.1300000000001</v>
@@ -26789,10 +26789,10 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>479.45</v>
+        <v>478.45</v>
       </c>
       <c r="Q159">
-        <v>173.35</v>
+        <v>193.25</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>282.8</v>
       </c>
       <c r="P160">
-        <v>576.54999999999995</v>
+        <v>570.54999999999995</v>
       </c>
       <c r="Q160">
         <v>129.4</v>
@@ -29484,10 +29484,10 @@
         <v>10911.5</v>
       </c>
       <c r="P194">
-        <v>24871.29</v>
+        <v>24138.79</v>
       </c>
       <c r="Q194">
-        <v>13513.36</v>
+        <v>14178.59</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -29715,10 +29715,10 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>5789.04</v>
+        <v>5711.04</v>
       </c>
       <c r="Q197">
-        <v>2212.23</v>
+        <v>8949.08</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -29792,10 +29792,10 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>9659.8799999999992</v>
+        <v>9333.11</v>
       </c>
       <c r="Q198">
-        <v>6416.32</v>
+        <v>7210.03</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -29869,10 +29869,10 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>9559.2900000000009</v>
+        <v>9442.14</v>
       </c>
       <c r="Q199">
-        <v>8433.17</v>
+        <v>9124.7999999999993</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -29946,10 +29946,10 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>15228.52</v>
+        <v>15207.07</v>
       </c>
       <c r="Q200">
-        <v>23252.57</v>
+        <v>24610.58</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -30023,10 +30023,10 @@
         <v>819.93</v>
       </c>
       <c r="P201">
-        <v>1144.96</v>
+        <v>1139.6099999999999</v>
       </c>
       <c r="Q201">
-        <v>1091</v>
+        <v>1207.5999999999999</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>1498.34</v>
       </c>
       <c r="P203">
-        <v>5219.09</v>
+        <v>5217.09</v>
       </c>
       <c r="Q203">
-        <v>1932.62</v>
+        <v>2077.17</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -30254,7 +30254,7 @@
         <v>2807.35</v>
       </c>
       <c r="P204">
-        <v>3277.5</v>
+        <v>3033.37</v>
       </c>
       <c r="Q204">
         <v>1065.5</v>
@@ -30331,10 +30331,10 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>109105.36</v>
+        <v>106807.48</v>
       </c>
       <c r="Q205">
-        <v>140533.95000000001</v>
+        <v>147588.69</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -30408,10 +30408,10 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>8645.2900000000009</v>
+        <v>8614.8700000000008</v>
       </c>
       <c r="Q206">
-        <v>11067.99</v>
+        <v>14286.32</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -30485,10 +30485,10 @@
         <v>3782.99</v>
       </c>
       <c r="P207">
-        <v>773.75</v>
+        <v>785.13</v>
       </c>
       <c r="Q207">
-        <v>3159.05</v>
+        <v>3428.8</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -30565,7 +30565,7 @@
         <v>433</v>
       </c>
       <c r="Q208">
-        <v>3080.3</v>
+        <v>3199.8</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -30639,10 +30639,10 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>5292.88</v>
+        <v>5259.18</v>
       </c>
       <c r="Q209">
-        <v>6905.03</v>
+        <v>7557.23</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -30716,10 +30716,10 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>29215.86</v>
+        <v>29048.79</v>
       </c>
       <c r="Q210">
-        <v>30412.48</v>
+        <v>33128.39</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -30873,7 +30873,7 @@
         <v>0</v>
       </c>
       <c r="Q212">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -31409,10 +31409,10 @@
         <v>5408.2</v>
       </c>
       <c r="P219">
-        <v>6246.19</v>
+        <v>6215.59</v>
       </c>
       <c r="Q219">
-        <v>34917.06</v>
+        <v>35040.86</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -31640,10 +31640,10 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>6632.2</v>
+        <v>6598.1</v>
       </c>
       <c r="Q222">
-        <v>4451.8999999999996</v>
+        <v>5147.7</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -31717,10 +31717,10 @@
         <v>2748.05</v>
       </c>
       <c r="P223">
-        <v>4704.99</v>
+        <v>4660.79</v>
       </c>
       <c r="Q223">
-        <v>3912.19</v>
+        <v>4324.5200000000004</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -31794,10 +31794,10 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>3870.6</v>
+        <v>3829.06</v>
       </c>
       <c r="Q224">
-        <v>8120.15</v>
+        <v>8760.93</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -31871,10 +31871,10 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>11596.46</v>
+        <v>11295.1</v>
       </c>
       <c r="Q225">
-        <v>7683.51</v>
+        <v>8340.2199999999993</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -31948,10 +31948,10 @@
         <v>630.75</v>
       </c>
       <c r="P226">
-        <v>398.36</v>
+        <v>399.66</v>
       </c>
       <c r="Q226">
-        <v>1334.74</v>
+        <v>1443.59</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -32102,10 +32102,10 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>3172.3</v>
+        <v>3167.3</v>
       </c>
       <c r="Q228">
-        <v>1381.2</v>
+        <v>1511.5</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -32179,7 +32179,7 @@
         <v>3384.9</v>
       </c>
       <c r="P229">
-        <v>929.45</v>
+        <v>923.4</v>
       </c>
       <c r="Q229">
         <v>2492.86</v>
@@ -32256,10 +32256,10 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>32127.45</v>
+        <v>31452.35</v>
       </c>
       <c r="Q230">
-        <v>37277.550000000003</v>
+        <v>41527.599999999999</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -32333,10 +32333,10 @@
         <v>4790.9799999999996</v>
       </c>
       <c r="P231">
-        <v>5550.91</v>
+        <v>5543.11</v>
       </c>
       <c r="Q231">
-        <v>8882.25</v>
+        <v>9476.17</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -32410,10 +32410,10 @@
         <v>2022.35</v>
       </c>
       <c r="P232">
-        <v>2377.84</v>
+        <v>2358.44</v>
       </c>
       <c r="Q232">
-        <v>1782.09</v>
+        <v>2064.59</v>
       </c>
       <c r="R232">
         <v>0</v>
@@ -32487,7 +32487,7 @@
         <v>1507.74</v>
       </c>
       <c r="P233">
-        <v>3520.64</v>
+        <v>3518.04</v>
       </c>
       <c r="Q233">
         <v>4342.83</v>
@@ -32564,10 +32564,10 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>3929.27</v>
+        <v>3903.29</v>
       </c>
       <c r="Q234">
-        <v>3780.23</v>
+        <v>4283.58</v>
       </c>
       <c r="R234">
         <v>0</v>
@@ -32641,10 +32641,10 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>9688.98</v>
+        <v>9683.18</v>
       </c>
       <c r="Q235">
-        <v>11364.53</v>
+        <v>11938.2</v>
       </c>
       <c r="R235">
         <v>0</v>
@@ -33334,10 +33334,10 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>4398.3599999999997</v>
+        <v>4185.03</v>
       </c>
       <c r="Q244">
-        <v>5300.64</v>
+        <v>7223.84</v>
       </c>
       <c r="R244">
         <v>0</v>
@@ -33565,10 +33565,10 @@
         <v>1706.35</v>
       </c>
       <c r="P247">
-        <v>4088.06</v>
+        <v>4026.26</v>
       </c>
       <c r="Q247">
-        <v>95.65</v>
+        <v>162.44999999999999</v>
       </c>
       <c r="R247">
         <v>0</v>
@@ -33642,10 +33642,10 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>3164.56</v>
+        <v>3153.16</v>
       </c>
       <c r="Q248">
-        <v>1639.56</v>
+        <v>2023.52</v>
       </c>
       <c r="R248">
         <v>0</v>
@@ -33719,10 +33719,10 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>10864.67</v>
+        <v>10828.47</v>
       </c>
       <c r="Q249">
-        <v>1693.68</v>
+        <v>2343.33</v>
       </c>
       <c r="R249">
         <v>0</v>
@@ -33796,10 +33796,10 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>10356.299999999999</v>
+        <v>10305.14</v>
       </c>
       <c r="Q250">
-        <v>2136.92</v>
+        <v>3386.84</v>
       </c>
       <c r="R250">
         <v>0</v>
@@ -34027,10 +34027,10 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>1435.9</v>
+        <v>1426.9</v>
       </c>
       <c r="Q253">
-        <v>205.25</v>
+        <v>314.25</v>
       </c>
       <c r="R253">
         <v>0</v>
@@ -34104,7 +34104,7 @@
         <v>2460.85</v>
       </c>
       <c r="P254">
-        <v>598.35</v>
+        <v>588.35</v>
       </c>
       <c r="Q254">
         <v>125.9</v>
@@ -34181,10 +34181,10 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>25275.11</v>
+        <v>24549.61</v>
       </c>
       <c r="Q255">
-        <v>15308.58</v>
+        <v>16771.03</v>
       </c>
       <c r="R255">
         <v>0</v>
@@ -34258,10 +34258,10 @@
         <v>6679.21</v>
       </c>
       <c r="P256">
-        <v>5383.38</v>
+        <v>5359.38</v>
       </c>
       <c r="Q256">
-        <v>3839.83</v>
+        <v>4042.43</v>
       </c>
       <c r="R256">
         <v>0</v>
@@ -34335,10 +34335,10 @@
         <v>3019.73</v>
       </c>
       <c r="P257">
-        <v>1675.86</v>
+        <v>1671.86</v>
       </c>
       <c r="Q257">
-        <v>343.2</v>
+        <v>438.2</v>
       </c>
       <c r="R257">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>1479.4</v>
       </c>
       <c r="Q258">
-        <v>869.9</v>
+        <v>1259.8</v>
       </c>
       <c r="R258">
         <v>0</v>
@@ -34489,10 +34489,10 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>4228.5600000000004</v>
+        <v>4179.3599999999997</v>
       </c>
       <c r="Q259">
-        <v>1426.85</v>
+        <v>1815.35</v>
       </c>
       <c r="R259">
         <v>0</v>
@@ -34566,10 +34566,10 @@
         <v>18146.46</v>
       </c>
       <c r="P260">
-        <v>22534.81</v>
+        <v>22340.61</v>
       </c>
       <c r="Q260">
-        <v>3255.6</v>
+        <v>5642.79</v>
       </c>
       <c r="R260">
         <v>0</v>
@@ -37118,11 +37118,11 @@
       </c>
       <c r="P299">
         <f t="shared" si="0"/>
-        <v>468457.1</v>
+        <v>461561.68999999977</v>
       </c>
       <c r="Q299">
         <f t="shared" si="0"/>
-        <v>480628.10000000015</v>
+        <v>529713.63000000012</v>
       </c>
       <c r="R299">
         <f t="shared" si="0"/>

--- a/vendas.xlsx
+++ b/vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Claudio\Documents\verdent-projects\new-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB9A036-7BBF-4FDF-AB95-087E7843BDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B9978-325C-48B2-875E-B988B6F83BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F2DED76B-5FEA-48D5-9DAC-66F60A430568}"/>
   </bookViews>
@@ -206,8 +206,19 @@
       <sheetName val="ENTRADA PLANILHA "/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>299858.38</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1">
+            <v>44197</v>
+          </cell>
+        </row>
         <row r="93">
           <cell r="AY93">
             <v>90</v>
@@ -252,8 +263,30 @@
             <v>67</v>
           </cell>
           <cell r="BM93">
-            <v>80</v>
-          </cell>
+            <v>83</v>
+          </cell>
+          <cell r="BN93">
+            <v>19</v>
+          </cell>
+          <cell r="BO93"/>
+          <cell r="BP93"/>
+          <cell r="BQ93"/>
+          <cell r="BR93"/>
+          <cell r="BS93"/>
+          <cell r="BT93"/>
+          <cell r="BU93"/>
+          <cell r="BV93"/>
+          <cell r="BW93"/>
+          <cell r="BX93"/>
+          <cell r="BY93"/>
+          <cell r="BZ93"/>
+          <cell r="CA93"/>
+          <cell r="CB93"/>
+          <cell r="CC93"/>
+          <cell r="CD93"/>
+          <cell r="CE93"/>
+          <cell r="CF93"/>
+          <cell r="CG93"/>
         </row>
         <row r="94">
           <cell r="AY94">
@@ -299,8 +332,30 @@
             <v>91</v>
           </cell>
           <cell r="BM94">
-            <v>98</v>
-          </cell>
+            <v>99</v>
+          </cell>
+          <cell r="BN94">
+            <v>44</v>
+          </cell>
+          <cell r="BO94"/>
+          <cell r="BP94"/>
+          <cell r="BQ94"/>
+          <cell r="BR94"/>
+          <cell r="BS94"/>
+          <cell r="BT94"/>
+          <cell r="BU94"/>
+          <cell r="BV94"/>
+          <cell r="BW94"/>
+          <cell r="BX94"/>
+          <cell r="BY94"/>
+          <cell r="BZ94"/>
+          <cell r="CA94"/>
+          <cell r="CB94"/>
+          <cell r="CC94"/>
+          <cell r="CD94"/>
+          <cell r="CE94"/>
+          <cell r="CF94"/>
+          <cell r="CG94"/>
         </row>
         <row r="95">
           <cell r="AY95">
@@ -346,8 +401,30 @@
             <v>185</v>
           </cell>
           <cell r="BM95">
-            <v>229</v>
-          </cell>
+            <v>231</v>
+          </cell>
+          <cell r="BN95">
+            <v>44</v>
+          </cell>
+          <cell r="BO95"/>
+          <cell r="BP95"/>
+          <cell r="BQ95"/>
+          <cell r="BR95"/>
+          <cell r="BS95"/>
+          <cell r="BT95"/>
+          <cell r="BU95"/>
+          <cell r="BV95"/>
+          <cell r="BW95"/>
+          <cell r="BX95"/>
+          <cell r="BY95"/>
+          <cell r="BZ95"/>
+          <cell r="CA95"/>
+          <cell r="CB95"/>
+          <cell r="CC95"/>
+          <cell r="CD95"/>
+          <cell r="CE95"/>
+          <cell r="CF95"/>
+          <cell r="CG95"/>
         </row>
         <row r="96">
           <cell r="AY96">
@@ -395,6 +472,28 @@
           <cell r="BM96">
             <v>3</v>
           </cell>
+          <cell r="BN96">
+            <v>1</v>
+          </cell>
+          <cell r="BO96"/>
+          <cell r="BP96"/>
+          <cell r="BQ96"/>
+          <cell r="BR96"/>
+          <cell r="BS96"/>
+          <cell r="BT96"/>
+          <cell r="BU96"/>
+          <cell r="BV96"/>
+          <cell r="BW96"/>
+          <cell r="BX96"/>
+          <cell r="BY96"/>
+          <cell r="BZ96"/>
+          <cell r="CA96"/>
+          <cell r="CB96"/>
+          <cell r="CC96"/>
+          <cell r="CD96"/>
+          <cell r="CE96"/>
+          <cell r="CF96"/>
+          <cell r="CG96"/>
         </row>
         <row r="97">
           <cell r="AY97">
@@ -442,6 +541,28 @@
           <cell r="BM97">
             <v>45</v>
           </cell>
+          <cell r="BN97">
+            <v>12</v>
+          </cell>
+          <cell r="BO97"/>
+          <cell r="BP97"/>
+          <cell r="BQ97"/>
+          <cell r="BR97"/>
+          <cell r="BS97"/>
+          <cell r="BT97"/>
+          <cell r="BU97"/>
+          <cell r="BV97"/>
+          <cell r="BW97"/>
+          <cell r="BX97"/>
+          <cell r="BY97"/>
+          <cell r="BZ97"/>
+          <cell r="CA97"/>
+          <cell r="CB97"/>
+          <cell r="CC97"/>
+          <cell r="CD97"/>
+          <cell r="CE97"/>
+          <cell r="CF97"/>
+          <cell r="CG97"/>
         </row>
         <row r="98">
           <cell r="AY98">
@@ -489,6 +610,28 @@
           <cell r="BM98">
             <v>89</v>
           </cell>
+          <cell r="BN98">
+            <v>32</v>
+          </cell>
+          <cell r="BO98"/>
+          <cell r="BP98"/>
+          <cell r="BQ98"/>
+          <cell r="BR98"/>
+          <cell r="BS98"/>
+          <cell r="BT98"/>
+          <cell r="BU98"/>
+          <cell r="BV98"/>
+          <cell r="BW98"/>
+          <cell r="BX98"/>
+          <cell r="BY98"/>
+          <cell r="BZ98"/>
+          <cell r="CA98"/>
+          <cell r="CB98"/>
+          <cell r="CC98"/>
+          <cell r="CD98"/>
+          <cell r="CE98"/>
+          <cell r="CF98"/>
+          <cell r="CG98"/>
         </row>
         <row r="99">
           <cell r="AY99">
@@ -536,6 +679,28 @@
           <cell r="BM99">
             <v>1</v>
           </cell>
+          <cell r="BN99">
+            <v>1</v>
+          </cell>
+          <cell r="BO99"/>
+          <cell r="BP99"/>
+          <cell r="BQ99"/>
+          <cell r="BR99"/>
+          <cell r="BS99"/>
+          <cell r="BT99"/>
+          <cell r="BU99"/>
+          <cell r="BV99"/>
+          <cell r="BW99"/>
+          <cell r="BX99"/>
+          <cell r="BY99"/>
+          <cell r="BZ99"/>
+          <cell r="CA99"/>
+          <cell r="CB99"/>
+          <cell r="CC99"/>
+          <cell r="CD99"/>
+          <cell r="CE99"/>
+          <cell r="CF99"/>
+          <cell r="CG99"/>
         </row>
         <row r="100">
           <cell r="AY100">
@@ -581,8 +746,30 @@
             <v>751</v>
           </cell>
           <cell r="BM100">
-            <v>931</v>
-          </cell>
+            <v>967</v>
+          </cell>
+          <cell r="BN100">
+            <v>247</v>
+          </cell>
+          <cell r="BO100"/>
+          <cell r="BP100"/>
+          <cell r="BQ100"/>
+          <cell r="BR100"/>
+          <cell r="BS100"/>
+          <cell r="BT100"/>
+          <cell r="BU100"/>
+          <cell r="BV100"/>
+          <cell r="BW100"/>
+          <cell r="BX100"/>
+          <cell r="BY100"/>
+          <cell r="BZ100"/>
+          <cell r="CA100"/>
+          <cell r="CB100"/>
+          <cell r="CC100"/>
+          <cell r="CD100"/>
+          <cell r="CE100"/>
+          <cell r="CF100"/>
+          <cell r="CG100"/>
         </row>
         <row r="101">
           <cell r="AY101">
@@ -628,8 +815,30 @@
             <v>561</v>
           </cell>
           <cell r="BM101">
-            <v>773</v>
-          </cell>
+            <v>797</v>
+          </cell>
+          <cell r="BN101">
+            <v>120</v>
+          </cell>
+          <cell r="BO101"/>
+          <cell r="BP101"/>
+          <cell r="BQ101"/>
+          <cell r="BR101"/>
+          <cell r="BS101"/>
+          <cell r="BT101"/>
+          <cell r="BU101"/>
+          <cell r="BV101"/>
+          <cell r="BW101"/>
+          <cell r="BX101"/>
+          <cell r="BY101"/>
+          <cell r="BZ101"/>
+          <cell r="CA101"/>
+          <cell r="CB101"/>
+          <cell r="CC101"/>
+          <cell r="CD101"/>
+          <cell r="CE101"/>
+          <cell r="CF101"/>
+          <cell r="CG101"/>
         </row>
         <row r="102">
           <cell r="AY102">
@@ -675,21 +884,57 @@
             <v>588</v>
           </cell>
           <cell r="BM102">
-            <v>307</v>
-          </cell>
+            <v>336</v>
+          </cell>
+          <cell r="BN102">
+            <v>117</v>
+          </cell>
+          <cell r="BO102"/>
+          <cell r="BP102"/>
+          <cell r="BQ102"/>
+          <cell r="BR102"/>
+          <cell r="BS102"/>
+          <cell r="BT102"/>
+          <cell r="BU102"/>
+          <cell r="BV102"/>
+          <cell r="BW102"/>
+          <cell r="BX102"/>
+          <cell r="BY102"/>
+          <cell r="BZ102"/>
+          <cell r="CA102"/>
+          <cell r="CB102"/>
+          <cell r="CC102"/>
+          <cell r="CD102"/>
+          <cell r="CE102"/>
+          <cell r="CF102"/>
+          <cell r="CG102"/>
         </row>
         <row r="103">
+          <cell r="AY103"/>
+          <cell r="AZ103"/>
           <cell r="BA103">
             <v>1</v>
           </cell>
+          <cell r="BB103"/>
           <cell r="BC103">
             <v>1</v>
           </cell>
+          <cell r="BD103"/>
+          <cell r="BE103"/>
+          <cell r="BF103"/>
+          <cell r="BG103"/>
+          <cell r="BH103"/>
+          <cell r="BI103"/>
+          <cell r="BJ103"/>
           <cell r="BK103">
             <v>1</v>
           </cell>
+          <cell r="BL103"/>
           <cell r="BM103">
             <v>2</v>
+          </cell>
+          <cell r="BN103">
+            <v>1</v>
           </cell>
         </row>
         <row r="116">
@@ -744,6 +989,9 @@
           <cell r="BM116">
             <v>0</v>
           </cell>
+          <cell r="BN116">
+            <v>0</v>
+          </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
@@ -797,6 +1045,9 @@
           <cell r="BM117">
             <v>4.5</v>
           </cell>
+          <cell r="BN117">
+            <v>0</v>
+          </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
@@ -850,6 +1101,9 @@
           <cell r="BM118">
             <v>0</v>
           </cell>
+          <cell r="BN118">
+            <v>0</v>
+          </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
@@ -903,6 +1157,9 @@
           <cell r="BM119">
             <v>0</v>
           </cell>
+          <cell r="BN119">
+            <v>0</v>
+          </cell>
         </row>
         <row r="120">
           <cell r="A120" t="str">
@@ -956,6 +1213,9 @@
           <cell r="BM120">
             <v>753.02</v>
           </cell>
+          <cell r="BN120">
+            <v>0</v>
+          </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
@@ -1007,7 +1267,10 @@
             <v>431.35</v>
           </cell>
           <cell r="BM121">
-            <v>262.57</v>
+            <v>259.57</v>
+          </cell>
+          <cell r="BN121">
+            <v>120.77</v>
           </cell>
         </row>
         <row r="122">
@@ -1060,7 +1323,10 @@
             <v>545.91</v>
           </cell>
           <cell r="BM122">
-            <v>942.63</v>
+            <v>942.64</v>
+          </cell>
+          <cell r="BN122">
+            <v>169.2</v>
           </cell>
         </row>
         <row r="123">
@@ -1113,7 +1379,10 @@
             <v>573.30999999999995</v>
           </cell>
           <cell r="BM123">
-            <v>466.3</v>
+            <v>464.84</v>
+          </cell>
+          <cell r="BN123">
+            <v>812.1</v>
           </cell>
         </row>
         <row r="124">
@@ -1168,6 +1437,9 @@
           <cell r="BM124">
             <v>116.2</v>
           </cell>
+          <cell r="BN124">
+            <v>19.899999999999999</v>
+          </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
@@ -1221,6 +1493,9 @@
           <cell r="BM125">
             <v>0</v>
           </cell>
+          <cell r="BN125">
+            <v>0</v>
+          </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
@@ -1274,6 +1549,9 @@
           <cell r="BM126">
             <v>1000.25</v>
           </cell>
+          <cell r="BN126">
+            <v>23.9</v>
+          </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
@@ -1327,6 +1605,9 @@
           <cell r="BM127">
             <v>861.25</v>
           </cell>
+          <cell r="BN127">
+            <v>0</v>
+          </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
@@ -1378,7 +1659,10 @@
             <v>4907.5</v>
           </cell>
           <cell r="BM128">
-            <v>401.9</v>
+            <v>396.4</v>
+          </cell>
+          <cell r="BN128">
+            <v>413.56</v>
           </cell>
         </row>
         <row r="129">
@@ -1431,7 +1715,10 @@
             <v>2100.16</v>
           </cell>
           <cell r="BM129">
-            <v>1455.22</v>
+            <v>1483.12</v>
+          </cell>
+          <cell r="BN129">
+            <v>32</v>
           </cell>
         </row>
         <row r="130">
@@ -1484,7 +1771,10 @@
             <v>530.04</v>
           </cell>
           <cell r="BM130">
-            <v>903.91</v>
+            <v>899.91</v>
+          </cell>
+          <cell r="BN130">
+            <v>112</v>
           </cell>
         </row>
         <row r="131">
@@ -1539,6 +1829,9 @@
           <cell r="BM131">
             <v>1051.9100000000001</v>
           </cell>
+          <cell r="BN131">
+            <v>0</v>
+          </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
@@ -1592,6 +1885,9 @@
           <cell r="BM132">
             <v>319.45</v>
           </cell>
+          <cell r="BN132">
+            <v>98</v>
+          </cell>
         </row>
         <row r="133">
           <cell r="A133" t="str">
@@ -1645,6 +1941,9 @@
           <cell r="BM133">
             <v>367</v>
           </cell>
+          <cell r="BN133">
+            <v>-82.62</v>
+          </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
@@ -1698,6 +1997,9 @@
           <cell r="BM134">
             <v>0</v>
           </cell>
+          <cell r="BN134">
+            <v>0</v>
+          </cell>
         </row>
         <row r="135">
           <cell r="A135" t="str">
@@ -1751,6 +2053,9 @@
           <cell r="BM135">
             <v>0</v>
           </cell>
+          <cell r="BN135">
+            <v>0</v>
+          </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
@@ -1804,6 +2109,9 @@
           <cell r="BM136">
             <v>0</v>
           </cell>
+          <cell r="BN136">
+            <v>0</v>
+          </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
@@ -1857,6 +2165,9 @@
           <cell r="BM137">
             <v>0</v>
           </cell>
+          <cell r="BN137">
+            <v>0</v>
+          </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
@@ -1910,6 +2221,49 @@
           <cell r="BM138">
             <v>0</v>
           </cell>
+          <cell r="BN138">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139"/>
+          <cell r="B139"/>
+          <cell r="AY139"/>
+          <cell r="AZ139"/>
+          <cell r="BA139"/>
+          <cell r="BB139"/>
+          <cell r="BC139"/>
+          <cell r="BD139"/>
+          <cell r="BE139"/>
+          <cell r="BF139"/>
+          <cell r="BG139"/>
+          <cell r="BH139"/>
+          <cell r="BI139"/>
+          <cell r="BJ139"/>
+          <cell r="BK139"/>
+          <cell r="BL139"/>
+          <cell r="BM139"/>
+          <cell r="BN139"/>
+        </row>
+        <row r="140">
+          <cell r="A140"/>
+          <cell r="B140"/>
+          <cell r="AY140"/>
+          <cell r="AZ140"/>
+          <cell r="BA140"/>
+          <cell r="BB140"/>
+          <cell r="BC140"/>
+          <cell r="BD140"/>
+          <cell r="BE140"/>
+          <cell r="BF140"/>
+          <cell r="BG140"/>
+          <cell r="BH140"/>
+          <cell r="BI140"/>
+          <cell r="BJ140"/>
+          <cell r="BK140"/>
+          <cell r="BL140"/>
+          <cell r="BM140"/>
+          <cell r="BN140"/>
         </row>
         <row r="141">
           <cell r="A141" t="str">
@@ -1963,6 +2317,9 @@
           <cell r="BM141">
             <v>0</v>
           </cell>
+          <cell r="BN141">
+            <v>0</v>
+          </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
@@ -2014,7 +2371,10 @@
             <v>292.04000000000002</v>
           </cell>
           <cell r="BM142">
-            <v>3127.4</v>
+            <v>4061.63</v>
+          </cell>
+          <cell r="BN142">
+            <v>0</v>
           </cell>
         </row>
         <row r="143">
@@ -2069,6 +2429,9 @@
           <cell r="BM143">
             <v>0</v>
           </cell>
+          <cell r="BN143">
+            <v>0</v>
+          </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
@@ -2122,6 +2485,9 @@
           <cell r="BM144">
             <v>0</v>
           </cell>
+          <cell r="BN144">
+            <v>0</v>
+          </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
@@ -2175,6 +2541,9 @@
           <cell r="BM145">
             <v>419.6</v>
           </cell>
+          <cell r="BN145">
+            <v>0</v>
+          </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
@@ -2223,10 +2592,13 @@
             <v>423.9</v>
           </cell>
           <cell r="BL146">
-            <v>617.37</v>
+            <v>616.16999999999996</v>
           </cell>
           <cell r="BM146">
-            <v>1020.54</v>
+            <v>1072.21</v>
+          </cell>
+          <cell r="BN146">
+            <v>98.98</v>
           </cell>
         </row>
         <row r="147">
@@ -2276,10 +2648,13 @@
             <v>6771.6</v>
           </cell>
           <cell r="BL147">
-            <v>977.28</v>
+            <v>990.35</v>
           </cell>
           <cell r="BM147">
-            <v>857.01</v>
+            <v>854.72</v>
+          </cell>
+          <cell r="BN147">
+            <v>302.19</v>
           </cell>
         </row>
         <row r="148">
@@ -2329,10 +2704,13 @@
             <v>1756.31</v>
           </cell>
           <cell r="BL148">
-            <v>489.21</v>
+            <v>485.44</v>
           </cell>
           <cell r="BM148">
-            <v>1548.42</v>
+            <v>1628.97</v>
+          </cell>
+          <cell r="BN148">
+            <v>283.10000000000002</v>
           </cell>
         </row>
         <row r="149">
@@ -2387,6 +2765,9 @@
           <cell r="BM149">
             <v>0</v>
           </cell>
+          <cell r="BN149">
+            <v>95.7</v>
+          </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
@@ -2440,6 +2821,9 @@
           <cell r="BM150">
             <v>0</v>
           </cell>
+          <cell r="BN150">
+            <v>0</v>
+          </cell>
         </row>
         <row r="151">
           <cell r="A151" t="str">
@@ -2493,6 +2877,9 @@
           <cell r="BM151">
             <v>136.05000000000001</v>
           </cell>
+          <cell r="BN151">
+            <v>0</v>
+          </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
@@ -2546,6 +2933,9 @@
           <cell r="BM152">
             <v>-219.9</v>
           </cell>
+          <cell r="BN152">
+            <v>0</v>
+          </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
@@ -2594,10 +2984,13 @@
             <v>6968.14</v>
           </cell>
           <cell r="BL153">
-            <v>742.58</v>
+            <v>1046.25</v>
           </cell>
           <cell r="BM153">
-            <v>6574.25</v>
+            <v>10177.1</v>
+          </cell>
+          <cell r="BN153">
+            <v>1998.12</v>
           </cell>
         </row>
         <row r="154">
@@ -2647,10 +3040,13 @@
             <v>351.6</v>
           </cell>
           <cell r="BL154">
-            <v>1244.1199999999999</v>
+            <v>1242.1600000000001</v>
           </cell>
           <cell r="BM154">
             <v>200.85</v>
+          </cell>
+          <cell r="BN154">
+            <v>546.95000000000005</v>
           </cell>
         </row>
         <row r="155">
@@ -2705,6 +3101,9 @@
           <cell r="BM155">
             <v>681.73</v>
           </cell>
+          <cell r="BN155">
+            <v>100.7</v>
+          </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
@@ -2758,6 +3157,9 @@
           <cell r="BM156">
             <v>0</v>
           </cell>
+          <cell r="BN156">
+            <v>0</v>
+          </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
@@ -2806,10 +3208,13 @@
             <v>1453.89</v>
           </cell>
           <cell r="BL157">
-            <v>648.23</v>
+            <v>646.28</v>
           </cell>
           <cell r="BM157">
-            <v>277.56</v>
+            <v>279.95</v>
+          </cell>
+          <cell r="BN157">
+            <v>444.2</v>
           </cell>
         </row>
         <row r="158">
@@ -2862,7 +3267,10 @@
             <v>261.3</v>
           </cell>
           <cell r="BM158">
-            <v>820.93</v>
+            <v>796.53</v>
+          </cell>
+          <cell r="BN158">
+            <v>60.7</v>
           </cell>
         </row>
         <row r="159">
@@ -2917,6 +3325,9 @@
           <cell r="BM159">
             <v>0</v>
           </cell>
+          <cell r="BN159">
+            <v>0</v>
+          </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
@@ -2970,6 +3381,9 @@
           <cell r="BM160">
             <v>0</v>
           </cell>
+          <cell r="BN160">
+            <v>0</v>
+          </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
@@ -3023,6 +3437,9 @@
           <cell r="BM161">
             <v>0</v>
           </cell>
+          <cell r="BN161">
+            <v>0</v>
+          </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
@@ -3076,6 +3493,9 @@
           <cell r="BM162">
             <v>0</v>
           </cell>
+          <cell r="BN162">
+            <v>0</v>
+          </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
@@ -3129,6 +3549,49 @@
           <cell r="BM163">
             <v>0</v>
           </cell>
+          <cell r="BN163">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164"/>
+          <cell r="B164"/>
+          <cell r="AY164"/>
+          <cell r="AZ164"/>
+          <cell r="BA164"/>
+          <cell r="BB164"/>
+          <cell r="BC164"/>
+          <cell r="BD164"/>
+          <cell r="BE164"/>
+          <cell r="BF164"/>
+          <cell r="BG164"/>
+          <cell r="BH164"/>
+          <cell r="BI164"/>
+          <cell r="BJ164"/>
+          <cell r="BK164"/>
+          <cell r="BL164"/>
+          <cell r="BM164"/>
+          <cell r="BN164"/>
+        </row>
+        <row r="165">
+          <cell r="A165"/>
+          <cell r="B165"/>
+          <cell r="AY165"/>
+          <cell r="AZ165"/>
+          <cell r="BA165"/>
+          <cell r="BB165"/>
+          <cell r="BC165"/>
+          <cell r="BD165"/>
+          <cell r="BE165"/>
+          <cell r="BF165"/>
+          <cell r="BG165"/>
+          <cell r="BH165"/>
+          <cell r="BI165"/>
+          <cell r="BJ165"/>
+          <cell r="BK165"/>
+          <cell r="BL165"/>
+          <cell r="BM165"/>
+          <cell r="BN165"/>
         </row>
         <row r="166">
           <cell r="A166" t="str">
@@ -3182,6 +3645,9 @@
           <cell r="BM166">
             <v>0</v>
           </cell>
+          <cell r="BN166">
+            <v>0</v>
+          </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
@@ -3235,6 +3701,9 @@
           <cell r="BM167">
             <v>1483.88</v>
           </cell>
+          <cell r="BN167">
+            <v>155.9</v>
+          </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
@@ -3288,6 +3757,9 @@
           <cell r="BM168">
             <v>0</v>
           </cell>
+          <cell r="BN168">
+            <v>0</v>
+          </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
@@ -3341,6 +3813,9 @@
           <cell r="BM169">
             <v>0</v>
           </cell>
+          <cell r="BN169">
+            <v>0</v>
+          </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
@@ -3394,6 +3869,9 @@
           <cell r="BM170">
             <v>2721.3</v>
           </cell>
+          <cell r="BN170">
+            <v>134.6</v>
+          </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
@@ -3442,10 +3920,13 @@
             <v>2564.08</v>
           </cell>
           <cell r="BL171">
-            <v>922.29</v>
+            <v>917.25</v>
           </cell>
           <cell r="BM171">
-            <v>702.81</v>
+            <v>698.94</v>
+          </cell>
+          <cell r="BN171">
+            <v>176.95</v>
           </cell>
         </row>
         <row r="172">
@@ -3495,10 +3976,13 @@
             <v>3205.26</v>
           </cell>
           <cell r="BL172">
-            <v>1249.54</v>
+            <v>1249.3</v>
           </cell>
           <cell r="BM172">
-            <v>2628</v>
+            <v>2632.26</v>
+          </cell>
+          <cell r="BN172">
+            <v>256.60000000000002</v>
           </cell>
         </row>
         <row r="173">
@@ -3551,7 +4035,10 @@
             <v>1297.72</v>
           </cell>
           <cell r="BM173">
-            <v>2287.31</v>
+            <v>2282.5300000000002</v>
+          </cell>
+          <cell r="BN173">
+            <v>2302.44</v>
           </cell>
         </row>
         <row r="174">
@@ -3604,7 +4091,10 @@
             <v>158.19999999999999</v>
           </cell>
           <cell r="BM174">
-            <v>440.27</v>
+            <v>437.27</v>
+          </cell>
+          <cell r="BN174">
+            <v>24.75</v>
           </cell>
         </row>
         <row r="175">
@@ -3659,6 +4149,9 @@
           <cell r="BM175">
             <v>0</v>
           </cell>
+          <cell r="BN175">
+            <v>0</v>
+          </cell>
         </row>
         <row r="176">
           <cell r="A176" t="str">
@@ -3710,7 +4203,10 @@
             <v>209.83</v>
           </cell>
           <cell r="BM176">
-            <v>161.9</v>
+            <v>160.9</v>
+          </cell>
+          <cell r="BN176">
+            <v>287.7</v>
           </cell>
         </row>
         <row r="177">
@@ -3763,7 +4259,10 @@
             <v>955.8</v>
           </cell>
           <cell r="BM177">
-            <v>535.85</v>
+            <v>979.75</v>
+          </cell>
+          <cell r="BN177">
+            <v>0</v>
           </cell>
         </row>
         <row r="178">
@@ -3813,10 +4312,13 @@
             <v>7670.07</v>
           </cell>
           <cell r="BL178">
-            <v>4711.63</v>
+            <v>4682.13</v>
           </cell>
           <cell r="BM178">
-            <v>9459.86</v>
+            <v>9357.01</v>
+          </cell>
+          <cell r="BN178">
+            <v>974.8</v>
           </cell>
         </row>
         <row r="179">
@@ -3866,10 +4368,13 @@
             <v>3574.39</v>
           </cell>
           <cell r="BL179">
-            <v>2169.31</v>
+            <v>2167.81</v>
           </cell>
           <cell r="BM179">
-            <v>980.38</v>
+            <v>969.48</v>
+          </cell>
+          <cell r="BN179">
+            <v>2070.15</v>
           </cell>
         </row>
         <row r="180">
@@ -3919,10 +4424,13 @@
             <v>799.37</v>
           </cell>
           <cell r="BL180">
-            <v>599.77</v>
+            <v>597.77</v>
           </cell>
           <cell r="BM180">
-            <v>722</v>
+            <v>740.95</v>
+          </cell>
+          <cell r="BN180">
+            <v>210.38</v>
           </cell>
         </row>
         <row r="181">
@@ -3977,6 +4485,9 @@
           <cell r="BM181">
             <v>2.0299999999999998</v>
           </cell>
+          <cell r="BN181">
+            <v>0</v>
+          </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
@@ -4028,7 +4539,10 @@
             <v>2174.7600000000002</v>
           </cell>
           <cell r="BM182">
-            <v>1603.37</v>
+            <v>1623.14</v>
+          </cell>
+          <cell r="BN182">
+            <v>365</v>
           </cell>
         </row>
         <row r="183">
@@ -4078,10 +4592,13 @@
             <v>5356.76</v>
           </cell>
           <cell r="BL183">
-            <v>3386.07</v>
+            <v>3384.07</v>
           </cell>
           <cell r="BM183">
-            <v>5672.19</v>
+            <v>5618.24</v>
+          </cell>
+          <cell r="BN183">
+            <v>236.45</v>
           </cell>
         </row>
         <row r="184">
@@ -4136,6 +4653,9 @@
           <cell r="BM184">
             <v>0</v>
           </cell>
+          <cell r="BN184">
+            <v>0</v>
+          </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
@@ -4189,6 +4709,9 @@
           <cell r="BM185">
             <v>0</v>
           </cell>
+          <cell r="BN185">
+            <v>0</v>
+          </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
@@ -4242,6 +4765,9 @@
           <cell r="BM186">
             <v>0</v>
           </cell>
+          <cell r="BN186">
+            <v>0</v>
+          </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
@@ -4295,6 +4821,9 @@
           <cell r="BM187">
             <v>0</v>
           </cell>
+          <cell r="BN187">
+            <v>0</v>
+          </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
@@ -4348,6 +4877,49 @@
           <cell r="BM188">
             <v>0</v>
           </cell>
+          <cell r="BN188">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189"/>
+          <cell r="B189"/>
+          <cell r="AY189"/>
+          <cell r="AZ189"/>
+          <cell r="BA189"/>
+          <cell r="BB189"/>
+          <cell r="BC189"/>
+          <cell r="BD189"/>
+          <cell r="BE189"/>
+          <cell r="BF189"/>
+          <cell r="BG189"/>
+          <cell r="BH189"/>
+          <cell r="BI189"/>
+          <cell r="BJ189"/>
+          <cell r="BK189"/>
+          <cell r="BL189"/>
+          <cell r="BM189"/>
+          <cell r="BN189"/>
+        </row>
+        <row r="190">
+          <cell r="A190"/>
+          <cell r="B190"/>
+          <cell r="AY190"/>
+          <cell r="AZ190"/>
+          <cell r="BA190"/>
+          <cell r="BB190"/>
+          <cell r="BC190"/>
+          <cell r="BD190"/>
+          <cell r="BE190"/>
+          <cell r="BF190"/>
+          <cell r="BG190"/>
+          <cell r="BH190"/>
+          <cell r="BI190"/>
+          <cell r="BJ190"/>
+          <cell r="BK190"/>
+          <cell r="BL190"/>
+          <cell r="BM190"/>
+          <cell r="BN190"/>
         </row>
         <row r="191">
           <cell r="A191" t="str">
@@ -4401,6 +4973,9 @@
           <cell r="BM191">
             <v>0</v>
           </cell>
+          <cell r="BN191">
+            <v>0</v>
+          </cell>
         </row>
         <row r="192">
           <cell r="A192" t="str">
@@ -4454,6 +5029,9 @@
           <cell r="BM192">
             <v>0</v>
           </cell>
+          <cell r="BN192">
+            <v>0</v>
+          </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
@@ -4507,6 +5085,9 @@
           <cell r="BM193">
             <v>0</v>
           </cell>
+          <cell r="BN193">
+            <v>0</v>
+          </cell>
         </row>
         <row r="194">
           <cell r="A194" t="str">
@@ -4560,6 +5141,9 @@
           <cell r="BM194">
             <v>0</v>
           </cell>
+          <cell r="BN194">
+            <v>0</v>
+          </cell>
         </row>
         <row r="195">
           <cell r="A195" t="str">
@@ -4608,9 +5192,12 @@
             <v>0</v>
           </cell>
           <cell r="BL195">
-            <v>444.48</v>
+            <v>756.7</v>
           </cell>
           <cell r="BM195">
+            <v>0</v>
+          </cell>
+          <cell r="BN195">
             <v>0</v>
           </cell>
         </row>
@@ -4666,6 +5253,9 @@
           <cell r="BM196">
             <v>0</v>
           </cell>
+          <cell r="BN196">
+            <v>0</v>
+          </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
@@ -4717,7 +5307,10 @@
             <v>78.959999999999994</v>
           </cell>
           <cell r="BM197">
-            <v>242.74</v>
+            <v>354.68</v>
+          </cell>
+          <cell r="BN197">
+            <v>0.01</v>
           </cell>
         </row>
         <row r="198">
@@ -4772,6 +5365,9 @@
           <cell r="BM198">
             <v>0</v>
           </cell>
+          <cell r="BN198">
+            <v>0</v>
+          </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
@@ -4825,6 +5421,9 @@
           <cell r="BM199">
             <v>0</v>
           </cell>
+          <cell r="BN199">
+            <v>0</v>
+          </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
@@ -4878,6 +5477,9 @@
           <cell r="BM200">
             <v>0</v>
           </cell>
+          <cell r="BN200">
+            <v>0</v>
+          </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
@@ -4926,9 +5528,12 @@
             <v>0</v>
           </cell>
           <cell r="BL201">
-            <v>5.56</v>
+            <v>9.4</v>
           </cell>
           <cell r="BM201">
+            <v>0</v>
+          </cell>
+          <cell r="BN201">
             <v>0</v>
           </cell>
         </row>
@@ -4984,6 +5589,9 @@
           <cell r="BM202">
             <v>0</v>
           </cell>
+          <cell r="BN202">
+            <v>0</v>
+          </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
@@ -5037,6 +5645,9 @@
           <cell r="BM203">
             <v>0</v>
           </cell>
+          <cell r="BN203">
+            <v>0</v>
+          </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
@@ -5085,9 +5696,12 @@
             <v>64.069999999999993</v>
           </cell>
           <cell r="BL204">
-            <v>4.96</v>
+            <v>9.1999999999999993</v>
           </cell>
           <cell r="BM204">
+            <v>0</v>
+          </cell>
+          <cell r="BN204">
             <v>0</v>
           </cell>
         </row>
@@ -5143,6 +5757,9 @@
           <cell r="BM205">
             <v>0</v>
           </cell>
+          <cell r="BN205">
+            <v>0</v>
+          </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
@@ -5196,6 +5813,9 @@
           <cell r="BM206">
             <v>0</v>
           </cell>
+          <cell r="BN206">
+            <v>0</v>
+          </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
@@ -5244,9 +5864,12 @@
             <v>0</v>
           </cell>
           <cell r="BL207">
-            <v>115.09</v>
+            <v>204.45</v>
           </cell>
           <cell r="BM207">
+            <v>0</v>
+          </cell>
+          <cell r="BN207">
             <v>0</v>
           </cell>
         </row>
@@ -5302,6 +5925,9 @@
           <cell r="BM208">
             <v>0</v>
           </cell>
+          <cell r="BN208">
+            <v>0</v>
+          </cell>
         </row>
         <row r="209">
           <cell r="A209" t="str">
@@ -5355,6 +5981,9 @@
           <cell r="BM209">
             <v>0</v>
           </cell>
+          <cell r="BN209">
+            <v>0</v>
+          </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
@@ -5408,6 +6037,9 @@
           <cell r="BM210">
             <v>0</v>
           </cell>
+          <cell r="BN210">
+            <v>0</v>
+          </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
@@ -5461,6 +6093,9 @@
           <cell r="BM211">
             <v>0</v>
           </cell>
+          <cell r="BN211">
+            <v>0</v>
+          </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
@@ -5514,6 +6149,9 @@
           <cell r="BM212">
             <v>0</v>
           </cell>
+          <cell r="BN212">
+            <v>0</v>
+          </cell>
         </row>
         <row r="213">
           <cell r="A213" t="str">
@@ -5567,6 +6205,49 @@
           <cell r="BM213">
             <v>0</v>
           </cell>
+          <cell r="BN213">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214"/>
+          <cell r="B214"/>
+          <cell r="AY214"/>
+          <cell r="AZ214"/>
+          <cell r="BA214"/>
+          <cell r="BB214"/>
+          <cell r="BC214"/>
+          <cell r="BD214"/>
+          <cell r="BE214"/>
+          <cell r="BF214"/>
+          <cell r="BG214"/>
+          <cell r="BH214"/>
+          <cell r="BI214"/>
+          <cell r="BJ214"/>
+          <cell r="BK214"/>
+          <cell r="BL214"/>
+          <cell r="BM214"/>
+          <cell r="BN214"/>
+        </row>
+        <row r="215">
+          <cell r="A215"/>
+          <cell r="B215"/>
+          <cell r="AY215"/>
+          <cell r="AZ215"/>
+          <cell r="BA215"/>
+          <cell r="BB215"/>
+          <cell r="BC215"/>
+          <cell r="BD215"/>
+          <cell r="BE215"/>
+          <cell r="BF215"/>
+          <cell r="BG215"/>
+          <cell r="BH215"/>
+          <cell r="BI215"/>
+          <cell r="BJ215"/>
+          <cell r="BK215"/>
+          <cell r="BL215"/>
+          <cell r="BM215"/>
+          <cell r="BN215"/>
         </row>
         <row r="216">
           <cell r="A216" t="str">
@@ -5620,6 +6301,9 @@
           <cell r="BM216">
             <v>0</v>
           </cell>
+          <cell r="BN216">
+            <v>0</v>
+          </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
@@ -5671,7 +6355,10 @@
             <v>0</v>
           </cell>
           <cell r="BM217">
-            <v>111.98</v>
+            <v>215.76</v>
+          </cell>
+          <cell r="BN217">
+            <v>3706.4</v>
           </cell>
         </row>
         <row r="218">
@@ -5726,6 +6413,9 @@
           <cell r="BM218">
             <v>0</v>
           </cell>
+          <cell r="BN218">
+            <v>0</v>
+          </cell>
         </row>
         <row r="219">
           <cell r="A219" t="str">
@@ -5779,6 +6469,9 @@
           <cell r="BM219">
             <v>0</v>
           </cell>
+          <cell r="BN219">
+            <v>0</v>
+          </cell>
         </row>
         <row r="220">
           <cell r="A220" t="str">
@@ -5832,6 +6525,9 @@
           <cell r="BM220">
             <v>350.03</v>
           </cell>
+          <cell r="BN220">
+            <v>0</v>
+          </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
@@ -5880,10 +6576,13 @@
             <v>203.03</v>
           </cell>
           <cell r="BL221">
-            <v>21.49</v>
+            <v>32.1</v>
           </cell>
           <cell r="BM221">
-            <v>265.47000000000003</v>
+            <v>299.44</v>
+          </cell>
+          <cell r="BN221">
+            <v>21.73</v>
           </cell>
         </row>
         <row r="222">
@@ -5933,10 +6632,13 @@
             <v>540.03</v>
           </cell>
           <cell r="BL222">
-            <v>215.71</v>
+            <v>251.76</v>
           </cell>
           <cell r="BM222">
-            <v>738.36</v>
+            <v>746.44</v>
+          </cell>
+          <cell r="BN222">
+            <v>50.06</v>
           </cell>
         </row>
         <row r="223">
@@ -5989,7 +6691,10 @@
             <v>249.25</v>
           </cell>
           <cell r="BM223">
-            <v>1605.65</v>
+            <v>1632.36</v>
+          </cell>
+          <cell r="BN223">
+            <v>678.65</v>
           </cell>
         </row>
         <row r="224">
@@ -6044,6 +6749,9 @@
           <cell r="BM224">
             <v>-20.85</v>
           </cell>
+          <cell r="BN224">
+            <v>-9</v>
+          </cell>
         </row>
         <row r="225">
           <cell r="A225" t="str">
@@ -6097,6 +6805,9 @@
           <cell r="BM225">
             <v>0</v>
           </cell>
+          <cell r="BN225">
+            <v>0</v>
+          </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
@@ -6150,6 +6861,9 @@
           <cell r="BM226">
             <v>0</v>
           </cell>
+          <cell r="BN226">
+            <v>0</v>
+          </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
@@ -6203,6 +6917,9 @@
           <cell r="BM227">
             <v>219</v>
           </cell>
+          <cell r="BN227">
+            <v>0</v>
+          </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
@@ -6254,7 +6971,10 @@
             <v>345.6</v>
           </cell>
           <cell r="BM228">
-            <v>895.76</v>
+            <v>894.16</v>
+          </cell>
+          <cell r="BN228">
+            <v>1280</v>
           </cell>
         </row>
         <row r="229">
@@ -6309,6 +7029,9 @@
           <cell r="BM229">
             <v>-689.7</v>
           </cell>
+          <cell r="BN229">
+            <v>0</v>
+          </cell>
         </row>
         <row r="230">
           <cell r="A230" t="str">
@@ -6362,6 +7085,9 @@
           <cell r="BM230">
             <v>264.05</v>
           </cell>
+          <cell r="BN230">
+            <v>22.2</v>
+          </cell>
         </row>
         <row r="231">
           <cell r="A231" t="str">
@@ -6415,6 +7141,9 @@
           <cell r="BM231">
             <v>0</v>
           </cell>
+          <cell r="BN231">
+            <v>0</v>
+          </cell>
         </row>
         <row r="232">
           <cell r="A232" t="str">
@@ -6463,10 +7192,13 @@
             <v>347.7</v>
           </cell>
           <cell r="BL232">
-            <v>234.83</v>
+            <v>250.45</v>
           </cell>
           <cell r="BM232">
-            <v>-32.08</v>
+            <v>-106.6</v>
+          </cell>
+          <cell r="BN232">
+            <v>116.1</v>
           </cell>
         </row>
         <row r="233">
@@ -6519,7 +7251,10 @@
             <v>1925.14</v>
           </cell>
           <cell r="BM233">
-            <v>2126.4299999999998</v>
+            <v>2487.37</v>
+          </cell>
+          <cell r="BN233">
+            <v>89.06</v>
           </cell>
         </row>
         <row r="234">
@@ -6574,6 +7309,9 @@
           <cell r="BM234">
             <v>0</v>
           </cell>
+          <cell r="BN234">
+            <v>0</v>
+          </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
@@ -6627,6 +7365,9 @@
           <cell r="BM235">
             <v>0</v>
           </cell>
+          <cell r="BN235">
+            <v>0</v>
+          </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
@@ -6680,6 +7421,9 @@
           <cell r="BM236">
             <v>0</v>
           </cell>
+          <cell r="BN236">
+            <v>0</v>
+          </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
@@ -6733,6 +7477,9 @@
           <cell r="BM237">
             <v>0</v>
           </cell>
+          <cell r="BN237">
+            <v>0</v>
+          </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
@@ -6786,6 +7533,49 @@
           <cell r="BM238">
             <v>0</v>
           </cell>
+          <cell r="BN238">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="A239"/>
+          <cell r="B239"/>
+          <cell r="AY239"/>
+          <cell r="AZ239"/>
+          <cell r="BA239"/>
+          <cell r="BB239"/>
+          <cell r="BC239"/>
+          <cell r="BD239"/>
+          <cell r="BE239"/>
+          <cell r="BF239"/>
+          <cell r="BG239"/>
+          <cell r="BH239"/>
+          <cell r="BI239"/>
+          <cell r="BJ239"/>
+          <cell r="BK239"/>
+          <cell r="BL239"/>
+          <cell r="BM239"/>
+          <cell r="BN239"/>
+        </row>
+        <row r="240">
+          <cell r="A240"/>
+          <cell r="B240"/>
+          <cell r="AY240"/>
+          <cell r="AZ240"/>
+          <cell r="BA240"/>
+          <cell r="BB240"/>
+          <cell r="BC240"/>
+          <cell r="BD240"/>
+          <cell r="BE240"/>
+          <cell r="BF240"/>
+          <cell r="BG240"/>
+          <cell r="BH240"/>
+          <cell r="BI240"/>
+          <cell r="BJ240"/>
+          <cell r="BK240"/>
+          <cell r="BL240"/>
+          <cell r="BM240"/>
+          <cell r="BN240"/>
         </row>
         <row r="241">
           <cell r="A241" t="str">
@@ -6839,6 +7629,9 @@
           <cell r="BM241">
             <v>0</v>
           </cell>
+          <cell r="BN241">
+            <v>0</v>
+          </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
@@ -6892,6 +7685,9 @@
           <cell r="BM242">
             <v>0</v>
           </cell>
+          <cell r="BN242">
+            <v>0</v>
+          </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
@@ -6945,6 +7741,9 @@
           <cell r="BM243">
             <v>0</v>
           </cell>
+          <cell r="BN243">
+            <v>0</v>
+          </cell>
         </row>
         <row r="244">
           <cell r="A244" t="str">
@@ -6998,6 +7797,9 @@
           <cell r="BM244">
             <v>0</v>
           </cell>
+          <cell r="BN244">
+            <v>0</v>
+          </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
@@ -7051,6 +7853,9 @@
           <cell r="BM245">
             <v>0</v>
           </cell>
+          <cell r="BN245">
+            <v>0</v>
+          </cell>
         </row>
         <row r="246">
           <cell r="A246" t="str">
@@ -7099,10 +7904,13 @@
             <v>449.41</v>
           </cell>
           <cell r="BL246">
-            <v>480.84</v>
+            <v>476.84</v>
           </cell>
           <cell r="BM246">
-            <v>917.97</v>
+            <v>912.57</v>
+          </cell>
+          <cell r="BN246">
+            <v>46.66</v>
           </cell>
         </row>
         <row r="247">
@@ -7152,10 +7960,13 @@
             <v>1131.74</v>
           </cell>
           <cell r="BL247">
-            <v>346.03</v>
+            <v>344.03</v>
           </cell>
           <cell r="BM247">
-            <v>922.38</v>
+            <v>915.93</v>
+          </cell>
+          <cell r="BN247">
+            <v>161.91</v>
           </cell>
         </row>
         <row r="248">
@@ -7205,10 +8016,13 @@
             <v>989.68</v>
           </cell>
           <cell r="BL248">
-            <v>579.89</v>
+            <v>574.16</v>
           </cell>
           <cell r="BM248">
-            <v>1441.04</v>
+            <v>1449.28</v>
+          </cell>
+          <cell r="BN248">
+            <v>215.74</v>
           </cell>
         </row>
         <row r="249">
@@ -7263,6 +8077,9 @@
           <cell r="BM249">
             <v>9.85</v>
           </cell>
+          <cell r="BN249">
+            <v>6.9</v>
+          </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
@@ -7316,6 +8133,9 @@
           <cell r="BM250">
             <v>0</v>
           </cell>
+          <cell r="BN250">
+            <v>0</v>
+          </cell>
         </row>
         <row r="251">
           <cell r="A251" t="str">
@@ -7369,6 +8189,9 @@
           <cell r="BM251">
             <v>63.65</v>
           </cell>
+          <cell r="BN251">
+            <v>10.9</v>
+          </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
@@ -7422,6 +8245,9 @@
           <cell r="BM252">
             <v>0</v>
           </cell>
+          <cell r="BN252">
+            <v>0</v>
+          </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
@@ -7473,7 +8299,10 @@
             <v>299.39999999999998</v>
           </cell>
           <cell r="BM253">
-            <v>626.65</v>
+            <v>593.05999999999995</v>
+          </cell>
+          <cell r="BN253">
+            <v>307.10000000000002</v>
           </cell>
         </row>
         <row r="254">
@@ -7526,7 +8355,10 @@
             <v>199.5</v>
           </cell>
           <cell r="BM254">
-            <v>1196.1300000000001</v>
+            <v>1173.93</v>
+          </cell>
+          <cell r="BN254">
+            <v>24.95</v>
           </cell>
         </row>
         <row r="255">
@@ -7581,6 +8413,9 @@
           <cell r="BM255">
             <v>222.95</v>
           </cell>
+          <cell r="BN255">
+            <v>131.69999999999999</v>
+          </cell>
         </row>
         <row r="256">
           <cell r="A256" t="str">
@@ -7634,6 +8469,9 @@
           <cell r="BM256">
             <v>0</v>
           </cell>
+          <cell r="BN256">
+            <v>0</v>
+          </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
@@ -7682,10 +8520,13 @@
             <v>332.2</v>
           </cell>
           <cell r="BL257">
-            <v>478.45</v>
+            <v>478.25</v>
           </cell>
           <cell r="BM257">
-            <v>193.25</v>
+            <v>187.25</v>
+          </cell>
+          <cell r="BN257">
+            <v>240.6</v>
           </cell>
         </row>
         <row r="258">
@@ -7740,6 +8581,9 @@
           <cell r="BM258">
             <v>129.4</v>
           </cell>
+          <cell r="BN258">
+            <v>146.02000000000001</v>
+          </cell>
         </row>
         <row r="259">
           <cell r="A259" t="str">
@@ -7793,6 +8637,9 @@
           <cell r="BM259">
             <v>0</v>
           </cell>
+          <cell r="BN259">
+            <v>0</v>
+          </cell>
         </row>
         <row r="260">
           <cell r="A260" t="str">
@@ -7846,6 +8693,9 @@
           <cell r="BM260">
             <v>0</v>
           </cell>
+          <cell r="BN260">
+            <v>0</v>
+          </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
@@ -7899,6 +8749,9 @@
           <cell r="BM261">
             <v>0</v>
           </cell>
+          <cell r="BN261">
+            <v>0</v>
+          </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
@@ -7952,6 +8805,9 @@
           <cell r="BM262">
             <v>0</v>
           </cell>
+          <cell r="BN262">
+            <v>0</v>
+          </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
@@ -8005,6 +8861,49 @@
           <cell r="BM263">
             <v>0</v>
           </cell>
+          <cell r="BN263">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264"/>
+          <cell r="B264"/>
+          <cell r="AY264"/>
+          <cell r="AZ264"/>
+          <cell r="BA264"/>
+          <cell r="BB264"/>
+          <cell r="BC264"/>
+          <cell r="BD264"/>
+          <cell r="BE264"/>
+          <cell r="BF264"/>
+          <cell r="BG264"/>
+          <cell r="BH264"/>
+          <cell r="BI264"/>
+          <cell r="BJ264"/>
+          <cell r="BK264"/>
+          <cell r="BL264"/>
+          <cell r="BM264"/>
+          <cell r="BN264"/>
+        </row>
+        <row r="265">
+          <cell r="A265"/>
+          <cell r="B265"/>
+          <cell r="AY265"/>
+          <cell r="AZ265"/>
+          <cell r="BA265"/>
+          <cell r="BB265"/>
+          <cell r="BC265"/>
+          <cell r="BD265"/>
+          <cell r="BE265"/>
+          <cell r="BF265"/>
+          <cell r="BG265"/>
+          <cell r="BH265"/>
+          <cell r="BI265"/>
+          <cell r="BJ265"/>
+          <cell r="BK265"/>
+          <cell r="BL265"/>
+          <cell r="BM265"/>
+          <cell r="BN265"/>
         </row>
         <row r="266">
           <cell r="A266" t="str">
@@ -8058,6 +8957,9 @@
           <cell r="BM266">
             <v>0</v>
           </cell>
+          <cell r="BN266">
+            <v>0</v>
+          </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
@@ -8111,6 +9013,9 @@
           <cell r="BM267">
             <v>0</v>
           </cell>
+          <cell r="BN267">
+            <v>0</v>
+          </cell>
         </row>
         <row r="268">
           <cell r="A268" t="str">
@@ -8164,6 +9069,9 @@
           <cell r="BM268">
             <v>0</v>
           </cell>
+          <cell r="BN268">
+            <v>0</v>
+          </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
@@ -8217,6 +9125,9 @@
           <cell r="BM269">
             <v>0</v>
           </cell>
+          <cell r="BN269">
+            <v>0</v>
+          </cell>
         </row>
         <row r="270">
           <cell r="A270" t="str">
@@ -8270,6 +9181,9 @@
           <cell r="BM270">
             <v>0</v>
           </cell>
+          <cell r="BN270">
+            <v>0</v>
+          </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
@@ -8323,6 +9237,9 @@
           <cell r="BM271">
             <v>0</v>
           </cell>
+          <cell r="BN271">
+            <v>0</v>
+          </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
@@ -8376,6 +9293,9 @@
           <cell r="BM272">
             <v>0.01</v>
           </cell>
+          <cell r="BN272">
+            <v>0.01</v>
+          </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
@@ -8429,6 +9349,9 @@
           <cell r="BM273">
             <v>0</v>
           </cell>
+          <cell r="BN273">
+            <v>0</v>
+          </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
@@ -8482,6 +9405,9 @@
           <cell r="BM274">
             <v>0</v>
           </cell>
+          <cell r="BN274">
+            <v>0</v>
+          </cell>
         </row>
         <row r="275">
           <cell r="A275" t="str">
@@ -8535,6 +9461,9 @@
           <cell r="BM275">
             <v>0</v>
           </cell>
+          <cell r="BN275">
+            <v>0</v>
+          </cell>
         </row>
         <row r="276">
           <cell r="A276" t="str">
@@ -8588,6 +9517,9 @@
           <cell r="BM276">
             <v>0</v>
           </cell>
+          <cell r="BN276">
+            <v>0</v>
+          </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
@@ -8641,6 +9573,9 @@
           <cell r="BM277">
             <v>0</v>
           </cell>
+          <cell r="BN277">
+            <v>0</v>
+          </cell>
         </row>
         <row r="278">
           <cell r="A278" t="str">
@@ -8694,6 +9629,9 @@
           <cell r="BM278">
             <v>0</v>
           </cell>
+          <cell r="BN278">
+            <v>0</v>
+          </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
@@ -8747,6 +9685,9 @@
           <cell r="BM279">
             <v>0</v>
           </cell>
+          <cell r="BN279">
+            <v>0</v>
+          </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
@@ -8800,6 +9741,9 @@
           <cell r="BM280">
             <v>0</v>
           </cell>
+          <cell r="BN280">
+            <v>0</v>
+          </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
@@ -8853,6 +9797,9 @@
           <cell r="BM281">
             <v>0</v>
           </cell>
+          <cell r="BN281">
+            <v>0</v>
+          </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
@@ -8906,6 +9853,9 @@
           <cell r="BM282">
             <v>0</v>
           </cell>
+          <cell r="BN282">
+            <v>0</v>
+          </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
@@ -8959,6 +9909,9 @@
           <cell r="BM283">
             <v>0</v>
           </cell>
+          <cell r="BN283">
+            <v>0</v>
+          </cell>
         </row>
         <row r="284">
           <cell r="A284" t="str">
@@ -9012,6 +9965,9 @@
           <cell r="BM284">
             <v>0</v>
           </cell>
+          <cell r="BN284">
+            <v>0</v>
+          </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
@@ -9065,6 +10021,9 @@
           <cell r="BM285">
             <v>0</v>
           </cell>
+          <cell r="BN285">
+            <v>0</v>
+          </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
@@ -9118,6 +10077,9 @@
           <cell r="BM286">
             <v>0</v>
           </cell>
+          <cell r="BN286">
+            <v>0</v>
+          </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
@@ -9171,6 +10133,9 @@
           <cell r="BM287">
             <v>0</v>
           </cell>
+          <cell r="BN287">
+            <v>0</v>
+          </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
@@ -9224,6 +10189,49 @@
           <cell r="BM288">
             <v>0</v>
           </cell>
+          <cell r="BN288">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="A289"/>
+          <cell r="B289"/>
+          <cell r="AY289"/>
+          <cell r="AZ289"/>
+          <cell r="BA289"/>
+          <cell r="BB289"/>
+          <cell r="BC289"/>
+          <cell r="BD289"/>
+          <cell r="BE289"/>
+          <cell r="BF289"/>
+          <cell r="BG289"/>
+          <cell r="BH289"/>
+          <cell r="BI289"/>
+          <cell r="BJ289"/>
+          <cell r="BK289"/>
+          <cell r="BL289"/>
+          <cell r="BM289"/>
+          <cell r="BN289"/>
+        </row>
+        <row r="290">
+          <cell r="A290"/>
+          <cell r="B290"/>
+          <cell r="AY290"/>
+          <cell r="AZ290"/>
+          <cell r="BA290"/>
+          <cell r="BB290"/>
+          <cell r="BC290"/>
+          <cell r="BD290"/>
+          <cell r="BE290"/>
+          <cell r="BF290"/>
+          <cell r="BG290"/>
+          <cell r="BH290"/>
+          <cell r="BI290"/>
+          <cell r="BJ290"/>
+          <cell r="BK290"/>
+          <cell r="BL290"/>
+          <cell r="BM290"/>
+          <cell r="BN290"/>
         </row>
         <row r="291">
           <cell r="A291" t="str">
@@ -9277,6 +10285,9 @@
           <cell r="BM291">
             <v>0</v>
           </cell>
+          <cell r="BN291">
+            <v>0</v>
+          </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
@@ -9328,7 +10339,10 @@
             <v>24138.79</v>
           </cell>
           <cell r="BM292">
-            <v>14178.59</v>
+            <v>14143.75</v>
+          </cell>
+          <cell r="BN292">
+            <v>381.3</v>
           </cell>
         </row>
         <row r="293">
@@ -9383,6 +10397,9 @@
           <cell r="BM293">
             <v>0</v>
           </cell>
+          <cell r="BN293">
+            <v>0</v>
+          </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
@@ -9436,6 +10453,9 @@
           <cell r="BM294">
             <v>0</v>
           </cell>
+          <cell r="BN294">
+            <v>0</v>
+          </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
@@ -9484,10 +10504,13 @@
             <v>9643.9500000000007</v>
           </cell>
           <cell r="BL295">
-            <v>5711.04</v>
+            <v>5707.04</v>
           </cell>
           <cell r="BM295">
-            <v>8949.08</v>
+            <v>8904.39</v>
+          </cell>
+          <cell r="BN295">
+            <v>0</v>
           </cell>
         </row>
         <row r="296">
@@ -9537,10 +10560,13 @@
             <v>7099.57</v>
           </cell>
           <cell r="BL296">
-            <v>9333.11</v>
+            <v>9340.02</v>
           </cell>
           <cell r="BM296">
-            <v>7210.03</v>
+            <v>7391.75</v>
+          </cell>
+          <cell r="BN296">
+            <v>2025.52</v>
           </cell>
         </row>
         <row r="297">
@@ -9590,10 +10616,13 @@
             <v>10437.030000000001</v>
           </cell>
           <cell r="BL297">
-            <v>9442.14</v>
+            <v>9458.65</v>
           </cell>
           <cell r="BM297">
-            <v>9124.7999999999993</v>
+            <v>9070.18</v>
+          </cell>
+          <cell r="BN297">
+            <v>4117.1000000000004</v>
           </cell>
         </row>
         <row r="298">
@@ -9643,10 +10672,13 @@
             <v>14032.28</v>
           </cell>
           <cell r="BL298">
-            <v>15207.07</v>
+            <v>15201.68</v>
           </cell>
           <cell r="BM298">
-            <v>24610.58</v>
+            <v>24947.91</v>
+          </cell>
+          <cell r="BN298">
+            <v>5378.34</v>
           </cell>
         </row>
         <row r="299">
@@ -9699,7 +10731,10 @@
             <v>1139.6099999999999</v>
           </cell>
           <cell r="BM299">
-            <v>1207.5999999999999</v>
+            <v>1240.83</v>
+          </cell>
+          <cell r="BN299">
+            <v>306.3</v>
           </cell>
         </row>
         <row r="300">
@@ -9754,6 +10789,9 @@
           <cell r="BM300">
             <v>0</v>
           </cell>
+          <cell r="BN300">
+            <v>0</v>
+          </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
@@ -9805,7 +10843,10 @@
             <v>5217.09</v>
           </cell>
           <cell r="BM301">
-            <v>2077.17</v>
+            <v>2115.17</v>
+          </cell>
+          <cell r="BN301">
+            <v>509.28</v>
           </cell>
         </row>
         <row r="302">
@@ -9855,10 +10896,13 @@
             <v>2807.35</v>
           </cell>
           <cell r="BL302">
-            <v>3033.37</v>
+            <v>3028.4</v>
           </cell>
           <cell r="BM302">
             <v>1065.5</v>
+          </cell>
+          <cell r="BN302">
+            <v>1075.7</v>
           </cell>
         </row>
         <row r="303">
@@ -9908,10 +10952,13 @@
             <v>153570.17000000001</v>
           </cell>
           <cell r="BL303">
-            <v>106807.48</v>
+            <v>106816.7</v>
           </cell>
           <cell r="BM303">
-            <v>147588.69</v>
+            <v>161839.26999999999</v>
+          </cell>
+          <cell r="BN303">
+            <v>51094.68</v>
           </cell>
         </row>
         <row r="304">
@@ -9961,10 +11008,13 @@
             <v>11988.76</v>
           </cell>
           <cell r="BL304">
-            <v>8614.8700000000008</v>
+            <v>8603.7199999999993</v>
           </cell>
           <cell r="BM304">
-            <v>14286.32</v>
+            <v>14227.76</v>
+          </cell>
+          <cell r="BN304">
+            <v>1631.13</v>
           </cell>
         </row>
         <row r="305">
@@ -10017,7 +11067,10 @@
             <v>785.13</v>
           </cell>
           <cell r="BM305">
-            <v>3428.8</v>
+            <v>3427.8</v>
+          </cell>
+          <cell r="BN305">
+            <v>1036.5999999999999</v>
           </cell>
         </row>
         <row r="306">
@@ -10072,6 +11125,9 @@
           <cell r="BM306">
             <v>3199.8</v>
           </cell>
+          <cell r="BN306">
+            <v>1120.8599999999999</v>
+          </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
@@ -10120,10 +11176,13 @@
             <v>8450.7999999999993</v>
           </cell>
           <cell r="BL307">
-            <v>5259.18</v>
+            <v>5748.16</v>
           </cell>
           <cell r="BM307">
-            <v>7557.23</v>
+            <v>7827.09</v>
+          </cell>
+          <cell r="BN307">
+            <v>3034.22</v>
           </cell>
         </row>
         <row r="308">
@@ -10173,10 +11232,13 @@
             <v>20216.419999999998</v>
           </cell>
           <cell r="BL308">
-            <v>29048.79</v>
+            <v>29036.69</v>
           </cell>
           <cell r="BM308">
-            <v>33128.39</v>
+            <v>32672.89</v>
+          </cell>
+          <cell r="BN308">
+            <v>4535.0600000000004</v>
           </cell>
         </row>
         <row r="309">
@@ -10231,6 +11293,9 @@
           <cell r="BM309">
             <v>0</v>
           </cell>
+          <cell r="BN309">
+            <v>0</v>
+          </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
@@ -10284,6 +11349,9 @@
           <cell r="BM310">
             <v>7.5</v>
           </cell>
+          <cell r="BN310">
+            <v>0</v>
+          </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
@@ -10337,6 +11405,9 @@
           <cell r="BM311">
             <v>0</v>
           </cell>
+          <cell r="BN311">
+            <v>0</v>
+          </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
@@ -10390,6 +11461,9 @@
           <cell r="BM312">
             <v>0</v>
           </cell>
+          <cell r="BN312">
+            <v>0</v>
+          </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
@@ -10443,6 +11517,49 @@
           <cell r="BM313">
             <v>0</v>
           </cell>
+          <cell r="BN313">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314"/>
+          <cell r="B314"/>
+          <cell r="AY314"/>
+          <cell r="AZ314"/>
+          <cell r="BA314"/>
+          <cell r="BB314"/>
+          <cell r="BC314"/>
+          <cell r="BD314"/>
+          <cell r="BE314"/>
+          <cell r="BF314"/>
+          <cell r="BG314"/>
+          <cell r="BH314"/>
+          <cell r="BI314"/>
+          <cell r="BJ314"/>
+          <cell r="BK314"/>
+          <cell r="BL314"/>
+          <cell r="BM314"/>
+          <cell r="BN314"/>
+        </row>
+        <row r="315">
+          <cell r="A315"/>
+          <cell r="B315"/>
+          <cell r="AY315"/>
+          <cell r="AZ315"/>
+          <cell r="BA315"/>
+          <cell r="BB315"/>
+          <cell r="BC315"/>
+          <cell r="BD315"/>
+          <cell r="BE315"/>
+          <cell r="BF315"/>
+          <cell r="BG315"/>
+          <cell r="BH315"/>
+          <cell r="BI315"/>
+          <cell r="BJ315"/>
+          <cell r="BK315"/>
+          <cell r="BL315"/>
+          <cell r="BM315"/>
+          <cell r="BN315"/>
         </row>
         <row r="316">
           <cell r="A316" t="str">
@@ -10496,6 +11613,9 @@
           <cell r="BM316">
             <v>0</v>
           </cell>
+          <cell r="BN316">
+            <v>0</v>
+          </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
@@ -10547,7 +11667,10 @@
             <v>6215.59</v>
           </cell>
           <cell r="BM317">
-            <v>35040.86</v>
+            <v>35110.46</v>
+          </cell>
+          <cell r="BN317">
+            <v>13911.98</v>
           </cell>
         </row>
         <row r="318">
@@ -10602,6 +11725,9 @@
           <cell r="BM318">
             <v>0</v>
           </cell>
+          <cell r="BN318">
+            <v>0</v>
+          </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
@@ -10655,6 +11781,9 @@
           <cell r="BM319">
             <v>0</v>
           </cell>
+          <cell r="BN319">
+            <v>0</v>
+          </cell>
         </row>
         <row r="320">
           <cell r="A320" t="str">
@@ -10703,10 +11832,13 @@
             <v>2431.15</v>
           </cell>
           <cell r="BL320">
-            <v>6598.1</v>
+            <v>6561.35</v>
           </cell>
           <cell r="BM320">
-            <v>5147.7</v>
+            <v>5271.2</v>
+          </cell>
+          <cell r="BN320">
+            <v>2526.8000000000002</v>
           </cell>
         </row>
         <row r="321">
@@ -10759,7 +11891,10 @@
             <v>4660.79</v>
           </cell>
           <cell r="BM321">
-            <v>4324.5200000000004</v>
+            <v>4412.3500000000004</v>
+          </cell>
+          <cell r="BN321">
+            <v>746.93</v>
           </cell>
         </row>
         <row r="322">
@@ -10809,10 +11944,13 @@
             <v>5884.89</v>
           </cell>
           <cell r="BL322">
-            <v>3829.06</v>
+            <v>3818.71</v>
           </cell>
           <cell r="BM322">
-            <v>8760.93</v>
+            <v>8931.69</v>
+          </cell>
+          <cell r="BN322">
+            <v>1261.69</v>
           </cell>
         </row>
         <row r="323">
@@ -10862,10 +12000,13 @@
             <v>5304.37</v>
           </cell>
           <cell r="BL323">
-            <v>11295.1</v>
+            <v>11294.1</v>
           </cell>
           <cell r="BM323">
-            <v>8340.2199999999993</v>
+            <v>8474.06</v>
+          </cell>
+          <cell r="BN323">
+            <v>1164.8800000000001</v>
           </cell>
         </row>
         <row r="324">
@@ -10918,7 +12059,10 @@
             <v>399.66</v>
           </cell>
           <cell r="BM324">
-            <v>1443.59</v>
+            <v>1440.59</v>
+          </cell>
+          <cell r="BN324">
+            <v>242.3</v>
           </cell>
         </row>
         <row r="325">
@@ -10973,6 +12117,9 @@
           <cell r="BM325">
             <v>0</v>
           </cell>
+          <cell r="BN325">
+            <v>0</v>
+          </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
@@ -11021,10 +12168,13 @@
             <v>2586.27</v>
           </cell>
           <cell r="BL326">
-            <v>3167.3</v>
+            <v>3165.3</v>
           </cell>
           <cell r="BM326">
-            <v>1511.5</v>
+            <v>1611.7</v>
+          </cell>
+          <cell r="BN326">
+            <v>327.8</v>
           </cell>
         </row>
         <row r="327">
@@ -11079,6 +12229,9 @@
           <cell r="BM327">
             <v>2492.86</v>
           </cell>
+          <cell r="BN327">
+            <v>868.6</v>
+          </cell>
         </row>
         <row r="328">
           <cell r="A328" t="str">
@@ -11127,10 +12280,13 @@
             <v>18556.27</v>
           </cell>
           <cell r="BL328">
-            <v>31452.35</v>
+            <v>31472.85</v>
           </cell>
           <cell r="BM328">
-            <v>41527.599999999999</v>
+            <v>41501.870000000003</v>
+          </cell>
+          <cell r="BN328">
+            <v>14689.75</v>
           </cell>
         </row>
         <row r="329">
@@ -11183,7 +12339,10 @@
             <v>5543.11</v>
           </cell>
           <cell r="BM329">
-            <v>9476.17</v>
+            <v>9571.82</v>
+          </cell>
+          <cell r="BN329">
+            <v>1110.22</v>
           </cell>
         </row>
         <row r="330">
@@ -11236,7 +12395,10 @@
             <v>2358.44</v>
           </cell>
           <cell r="BM330">
-            <v>2064.59</v>
+            <v>2105.9899999999998</v>
+          </cell>
+          <cell r="BN330">
+            <v>346.8</v>
           </cell>
         </row>
         <row r="331">
@@ -11291,6 +12453,9 @@
           <cell r="BM331">
             <v>4342.83</v>
           </cell>
+          <cell r="BN331">
+            <v>489.9</v>
+          </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
@@ -11339,10 +12504,13 @@
             <v>2024.05</v>
           </cell>
           <cell r="BL332">
-            <v>3903.29</v>
+            <v>3863.39</v>
           </cell>
           <cell r="BM332">
-            <v>4283.58</v>
+            <v>4788.7299999999996</v>
+          </cell>
+          <cell r="BN332">
+            <v>1423.58</v>
           </cell>
         </row>
         <row r="333">
@@ -11392,10 +12560,13 @@
             <v>10644.94</v>
           </cell>
           <cell r="BL333">
-            <v>9683.18</v>
+            <v>9586.25</v>
           </cell>
           <cell r="BM333">
-            <v>11938.2</v>
+            <v>12439.75</v>
+          </cell>
+          <cell r="BN333">
+            <v>5618.29</v>
           </cell>
         </row>
         <row r="334">
@@ -11450,6 +12621,9 @@
           <cell r="BM334">
             <v>0</v>
           </cell>
+          <cell r="BN334">
+            <v>0</v>
+          </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
@@ -11503,6 +12677,9 @@
           <cell r="BM335">
             <v>7.9</v>
           </cell>
+          <cell r="BN335">
+            <v>0</v>
+          </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
@@ -11556,6 +12733,9 @@
           <cell r="BM336">
             <v>0</v>
           </cell>
+          <cell r="BN336">
+            <v>0</v>
+          </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
@@ -11609,6 +12789,9 @@
           <cell r="BM337">
             <v>0</v>
           </cell>
+          <cell r="BN337">
+            <v>0</v>
+          </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
@@ -11662,6 +12845,49 @@
           <cell r="BM338">
             <v>0</v>
           </cell>
+          <cell r="BN338">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="A339"/>
+          <cell r="B339"/>
+          <cell r="AY339"/>
+          <cell r="AZ339"/>
+          <cell r="BA339"/>
+          <cell r="BB339"/>
+          <cell r="BC339"/>
+          <cell r="BD339"/>
+          <cell r="BE339"/>
+          <cell r="BF339"/>
+          <cell r="BG339"/>
+          <cell r="BH339"/>
+          <cell r="BI339"/>
+          <cell r="BJ339"/>
+          <cell r="BK339"/>
+          <cell r="BL339"/>
+          <cell r="BM339"/>
+          <cell r="BN339"/>
+        </row>
+        <row r="340">
+          <cell r="A340"/>
+          <cell r="B340"/>
+          <cell r="AY340"/>
+          <cell r="AZ340"/>
+          <cell r="BA340"/>
+          <cell r="BB340"/>
+          <cell r="BC340"/>
+          <cell r="BD340"/>
+          <cell r="BE340"/>
+          <cell r="BF340"/>
+          <cell r="BG340"/>
+          <cell r="BH340"/>
+          <cell r="BI340"/>
+          <cell r="BJ340"/>
+          <cell r="BK340"/>
+          <cell r="BL340"/>
+          <cell r="BM340"/>
+          <cell r="BN340"/>
         </row>
         <row r="341">
           <cell r="A341" t="str">
@@ -11715,6 +12941,9 @@
           <cell r="BM341">
             <v>0</v>
           </cell>
+          <cell r="BN341">
+            <v>0</v>
+          </cell>
         </row>
         <row r="342">
           <cell r="A342" t="str">
@@ -11763,10 +12992,13 @@
             <v>3516.16</v>
           </cell>
           <cell r="BL342">
-            <v>4185.03</v>
+            <v>4190.76</v>
           </cell>
           <cell r="BM342">
-            <v>7223.84</v>
+            <v>7216.1</v>
+          </cell>
+          <cell r="BN342">
+            <v>1818.87</v>
           </cell>
         </row>
         <row r="343">
@@ -11821,6 +13053,9 @@
           <cell r="BM343">
             <v>0</v>
           </cell>
+          <cell r="BN343">
+            <v>0</v>
+          </cell>
         </row>
         <row r="344">
           <cell r="A344" t="str">
@@ -11874,6 +13109,9 @@
           <cell r="BM344">
             <v>0</v>
           </cell>
+          <cell r="BN344">
+            <v>0</v>
+          </cell>
         </row>
         <row r="345">
           <cell r="A345" t="str">
@@ -11925,7 +13163,10 @@
             <v>4026.26</v>
           </cell>
           <cell r="BM345">
-            <v>162.44999999999999</v>
+            <v>316.77</v>
+          </cell>
+          <cell r="BN345">
+            <v>170.7</v>
           </cell>
         </row>
         <row r="346">
@@ -11975,10 +13216,13 @@
             <v>4351.96</v>
           </cell>
           <cell r="BL346">
-            <v>3153.16</v>
+            <v>3143.16</v>
           </cell>
           <cell r="BM346">
-            <v>2023.52</v>
+            <v>2066.3200000000002</v>
+          </cell>
+          <cell r="BN346">
+            <v>886.46</v>
           </cell>
         </row>
         <row r="347">
@@ -12028,10 +13272,13 @@
             <v>6772.9</v>
           </cell>
           <cell r="BL347">
-            <v>10828.47</v>
+            <v>10817.69</v>
           </cell>
           <cell r="BM347">
-            <v>2343.33</v>
+            <v>2638.73</v>
+          </cell>
+          <cell r="BN347">
+            <v>1259.94</v>
           </cell>
         </row>
         <row r="348">
@@ -12081,10 +13328,13 @@
             <v>10251.93</v>
           </cell>
           <cell r="BL348">
-            <v>10305.14</v>
+            <v>10301.9</v>
           </cell>
           <cell r="BM348">
-            <v>3386.84</v>
+            <v>3844.17</v>
+          </cell>
+          <cell r="BN348">
+            <v>1835.89</v>
           </cell>
         </row>
         <row r="349">
@@ -12134,10 +13384,13 @@
             <v>1478.26</v>
           </cell>
           <cell r="BL349">
-            <v>698.55</v>
+            <v>697.6</v>
           </cell>
           <cell r="BM349">
             <v>210.15</v>
+          </cell>
+          <cell r="BN349">
+            <v>273.2</v>
           </cell>
         </row>
         <row r="350">
@@ -12192,6 +13445,9 @@
           <cell r="BM350">
             <v>0</v>
           </cell>
+          <cell r="BN350">
+            <v>0</v>
+          </cell>
         </row>
         <row r="351">
           <cell r="A351" t="str">
@@ -12240,10 +13496,13 @@
             <v>3188.47</v>
           </cell>
           <cell r="BL351">
-            <v>1426.9</v>
+            <v>1425.9</v>
           </cell>
           <cell r="BM351">
-            <v>314.25</v>
+            <v>312.61</v>
+          </cell>
+          <cell r="BN351">
+            <v>2405.6999999999998</v>
           </cell>
         </row>
         <row r="352">
@@ -12296,7 +13555,10 @@
             <v>588.35</v>
           </cell>
           <cell r="BM352">
-            <v>125.9</v>
+            <v>115.9</v>
+          </cell>
+          <cell r="BN352">
+            <v>161.9</v>
           </cell>
         </row>
         <row r="353">
@@ -12346,10 +13608,13 @@
             <v>29857.48</v>
           </cell>
           <cell r="BL353">
-            <v>24549.61</v>
+            <v>24550.31</v>
           </cell>
           <cell r="BM353">
-            <v>16771.03</v>
+            <v>16715.03</v>
+          </cell>
+          <cell r="BN353">
+            <v>5321.42</v>
           </cell>
         </row>
         <row r="354">
@@ -12402,7 +13667,10 @@
             <v>5359.38</v>
           </cell>
           <cell r="BM354">
-            <v>4042.43</v>
+            <v>4180.05</v>
+          </cell>
+          <cell r="BN354">
+            <v>3333.23</v>
           </cell>
         </row>
         <row r="355">
@@ -12455,7 +13723,10 @@
             <v>1671.86</v>
           </cell>
           <cell r="BM355">
-            <v>438.2</v>
+            <v>443.1</v>
+          </cell>
+          <cell r="BN355">
+            <v>165.7</v>
           </cell>
         </row>
         <row r="356">
@@ -12510,6 +13781,9 @@
           <cell r="BM356">
             <v>1259.8</v>
           </cell>
+          <cell r="BN356">
+            <v>500</v>
+          </cell>
         </row>
         <row r="357">
           <cell r="A357" t="str">
@@ -12558,10 +13832,13 @@
             <v>4746.4399999999996</v>
           </cell>
           <cell r="BL357">
-            <v>4179.3599999999997</v>
+            <v>4177.3599999999997</v>
           </cell>
           <cell r="BM357">
-            <v>1815.35</v>
+            <v>1892.34</v>
+          </cell>
+          <cell r="BN357">
+            <v>567</v>
           </cell>
         </row>
         <row r="358">
@@ -12614,7 +13891,10 @@
             <v>22340.61</v>
           </cell>
           <cell r="BM358">
-            <v>5642.79</v>
+            <v>5960.89</v>
+          </cell>
+          <cell r="BN358">
+            <v>2778.15</v>
           </cell>
         </row>
         <row r="359">
@@ -12669,6 +13949,9 @@
           <cell r="BM359">
             <v>0</v>
           </cell>
+          <cell r="BN359">
+            <v>0</v>
+          </cell>
         </row>
         <row r="360">
           <cell r="A360" t="str">
@@ -12722,6 +14005,9 @@
           <cell r="BM360">
             <v>0</v>
           </cell>
+          <cell r="BN360">
+            <v>0</v>
+          </cell>
         </row>
         <row r="361">
           <cell r="A361" t="str">
@@ -12775,6 +14061,9 @@
           <cell r="BM361">
             <v>0</v>
           </cell>
+          <cell r="BN361">
+            <v>0</v>
+          </cell>
         </row>
         <row r="362">
           <cell r="A362" t="str">
@@ -12828,6 +14117,9 @@
           <cell r="BM362">
             <v>0</v>
           </cell>
+          <cell r="BN362">
+            <v>0</v>
+          </cell>
         </row>
         <row r="363">
           <cell r="A363" t="str">
@@ -12881,20 +14173,77 @@
           <cell r="BM363">
             <v>0</v>
           </cell>
+          <cell r="BN363">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="364">
+          <cell r="A364"/>
+          <cell r="B364"/>
+          <cell r="AY364"/>
+          <cell r="AZ364"/>
+          <cell r="BA364"/>
+          <cell r="BB364"/>
+          <cell r="BC364"/>
+          <cell r="BD364"/>
+          <cell r="BE364"/>
+          <cell r="BF364"/>
+          <cell r="BG364"/>
+          <cell r="BH364"/>
+          <cell r="BI364"/>
+          <cell r="BJ364"/>
+          <cell r="BK364"/>
+          <cell r="BL364"/>
+          <cell r="BM364"/>
+          <cell r="BN364"/>
+        </row>
+        <row r="365">
+          <cell r="A365"/>
+          <cell r="B365"/>
+          <cell r="AY365"/>
+          <cell r="AZ365"/>
+          <cell r="BA365"/>
+          <cell r="BB365"/>
+          <cell r="BC365"/>
+          <cell r="BD365"/>
+          <cell r="BE365"/>
+          <cell r="BF365"/>
+          <cell r="BG365"/>
+          <cell r="BH365"/>
+          <cell r="BI365"/>
+          <cell r="BJ365"/>
+          <cell r="BK365"/>
+          <cell r="BL365"/>
+          <cell r="BM365"/>
+          <cell r="BN365"/>
         </row>
         <row r="366">
+          <cell r="A366"/>
+          <cell r="B366"/>
+          <cell r="AY366"/>
+          <cell r="AZ366"/>
           <cell r="BA366">
             <v>0</v>
           </cell>
+          <cell r="BB366"/>
           <cell r="BC366">
             <v>0</v>
           </cell>
+          <cell r="BD366"/>
+          <cell r="BE366"/>
+          <cell r="BF366"/>
+          <cell r="BG366"/>
+          <cell r="BH366"/>
+          <cell r="BI366"/>
+          <cell r="BJ366"/>
           <cell r="BK366">
             <v>0</v>
           </cell>
+          <cell r="BL366"/>
           <cell r="BM366">
             <v>0</v>
           </cell>
+          <cell r="BN366"/>
         </row>
         <row r="367">
           <cell r="A367" t="str">
@@ -12903,18 +14252,30 @@
           <cell r="B367" t="str">
             <v>ACABAMENTO  **</v>
           </cell>
+          <cell r="AY367"/>
+          <cell r="AZ367"/>
           <cell r="BA367">
             <v>0</v>
           </cell>
+          <cell r="BB367"/>
           <cell r="BC367">
             <v>0</v>
           </cell>
+          <cell r="BD367"/>
+          <cell r="BE367"/>
+          <cell r="BF367"/>
+          <cell r="BG367"/>
+          <cell r="BH367"/>
+          <cell r="BI367"/>
+          <cell r="BJ367"/>
           <cell r="BK367">
             <v>0</v>
           </cell>
+          <cell r="BL367"/>
           <cell r="BM367">
             <v>0</v>
           </cell>
+          <cell r="BN367"/>
         </row>
         <row r="368">
           <cell r="A368" t="str">
@@ -12923,18 +14284,30 @@
           <cell r="B368" t="str">
             <v>COBERTURA</v>
           </cell>
+          <cell r="AY368"/>
+          <cell r="AZ368"/>
           <cell r="BA368">
             <v>0</v>
           </cell>
+          <cell r="BB368"/>
           <cell r="BC368">
             <v>0</v>
           </cell>
+          <cell r="BD368"/>
+          <cell r="BE368"/>
+          <cell r="BF368"/>
+          <cell r="BG368"/>
+          <cell r="BH368"/>
+          <cell r="BI368"/>
+          <cell r="BJ368"/>
           <cell r="BK368">
             <v>0</v>
           </cell>
+          <cell r="BL368"/>
           <cell r="BM368">
             <v>0</v>
           </cell>
+          <cell r="BN368"/>
         </row>
         <row r="369">
           <cell r="A369" t="str">
@@ -12943,18 +14316,30 @@
           <cell r="B369" t="str">
             <v>ELETRICA     **</v>
           </cell>
+          <cell r="AY369"/>
+          <cell r="AZ369"/>
           <cell r="BA369">
             <v>0</v>
           </cell>
+          <cell r="BB369"/>
           <cell r="BC369">
             <v>0</v>
           </cell>
+          <cell r="BD369"/>
+          <cell r="BE369"/>
+          <cell r="BF369"/>
+          <cell r="BG369"/>
+          <cell r="BH369"/>
+          <cell r="BI369"/>
+          <cell r="BJ369"/>
           <cell r="BK369">
             <v>0</v>
           </cell>
+          <cell r="BL369"/>
           <cell r="BM369">
             <v>0</v>
           </cell>
+          <cell r="BN369"/>
         </row>
         <row r="370">
           <cell r="A370" t="str">
@@ -12963,18 +14348,30 @@
           <cell r="B370" t="str">
             <v>ELETRODOMESTICOS   **</v>
           </cell>
+          <cell r="AY370"/>
+          <cell r="AZ370"/>
           <cell r="BA370">
             <v>0</v>
           </cell>
+          <cell r="BB370"/>
           <cell r="BC370">
             <v>0</v>
           </cell>
+          <cell r="BD370"/>
+          <cell r="BE370"/>
+          <cell r="BF370"/>
+          <cell r="BG370"/>
+          <cell r="BH370"/>
+          <cell r="BI370"/>
+          <cell r="BJ370"/>
           <cell r="BK370">
             <v>0</v>
           </cell>
+          <cell r="BL370"/>
           <cell r="BM370">
             <v>0</v>
           </cell>
+          <cell r="BN370"/>
         </row>
         <row r="371">
           <cell r="A371" t="str">
@@ -12983,18 +14380,27 @@
           <cell r="B371" t="str">
             <v>ESQUADRIAS</v>
           </cell>
+          <cell r="AZ371"/>
           <cell r="BA371">
             <v>0</v>
           </cell>
           <cell r="BC371">
             <v>0</v>
           </cell>
+          <cell r="BD371"/>
+          <cell r="BF371"/>
+          <cell r="BG371"/>
+          <cell r="BH371"/>
+          <cell r="BI371"/>
+          <cell r="BJ371"/>
           <cell r="BK371">
             <v>0</v>
           </cell>
+          <cell r="BL371"/>
           <cell r="BM371">
             <v>0</v>
           </cell>
+          <cell r="BN371"/>
         </row>
         <row r="372">
           <cell r="A372" t="str">
@@ -13009,12 +14415,19 @@
           <cell r="BC372">
             <v>0.01</v>
           </cell>
+          <cell r="BF372"/>
+          <cell r="BG372"/>
+          <cell r="BH372"/>
+          <cell r="BI372"/>
+          <cell r="BJ372"/>
           <cell r="BK372">
             <v>0</v>
           </cell>
+          <cell r="BL372"/>
           <cell r="BM372">
             <v>0</v>
           </cell>
+          <cell r="BN372"/>
         </row>
         <row r="373">
           <cell r="A373" t="str">
@@ -13029,12 +14442,19 @@
           <cell r="BC373">
             <v>0</v>
           </cell>
+          <cell r="BF373"/>
+          <cell r="BG373"/>
+          <cell r="BH373"/>
+          <cell r="BI373"/>
+          <cell r="BJ373"/>
           <cell r="BK373">
             <v>0</v>
           </cell>
+          <cell r="BL373"/>
           <cell r="BM373">
             <v>0</v>
           </cell>
+          <cell r="BN373"/>
         </row>
         <row r="374">
           <cell r="A374" t="str">
@@ -13049,12 +14469,19 @@
           <cell r="BC374">
             <v>0</v>
           </cell>
+          <cell r="BF374"/>
+          <cell r="BG374"/>
+          <cell r="BH374"/>
+          <cell r="BI374"/>
+          <cell r="BJ374"/>
           <cell r="BK374">
             <v>0</v>
           </cell>
+          <cell r="BL374"/>
           <cell r="BM374">
             <v>0</v>
           </cell>
+          <cell r="BN374"/>
         </row>
         <row r="375">
           <cell r="A375" t="str">
@@ -13069,12 +14496,19 @@
           <cell r="BC375">
             <v>0</v>
           </cell>
+          <cell r="BF375"/>
+          <cell r="BG375"/>
+          <cell r="BH375"/>
+          <cell r="BI375"/>
+          <cell r="BJ375"/>
           <cell r="BK375">
             <v>0</v>
           </cell>
+          <cell r="BL375"/>
           <cell r="BM375">
             <v>0</v>
           </cell>
+          <cell r="BN375"/>
         </row>
         <row r="376">
           <cell r="A376" t="str">
@@ -13089,12 +14523,19 @@
           <cell r="BC376">
             <v>0</v>
           </cell>
+          <cell r="BF376"/>
+          <cell r="BG376"/>
+          <cell r="BH376"/>
+          <cell r="BI376"/>
+          <cell r="BJ376"/>
           <cell r="BK376">
             <v>0</v>
           </cell>
+          <cell r="BL376"/>
           <cell r="BM376">
             <v>0</v>
           </cell>
+          <cell r="BN376"/>
         </row>
         <row r="377">
           <cell r="A377" t="str">
@@ -13109,12 +14550,19 @@
           <cell r="BC377">
             <v>0</v>
           </cell>
+          <cell r="BF377"/>
+          <cell r="BG377"/>
+          <cell r="BH377"/>
+          <cell r="BI377"/>
+          <cell r="BJ377"/>
           <cell r="BK377">
             <v>0</v>
           </cell>
+          <cell r="BL377"/>
           <cell r="BM377">
             <v>0</v>
           </cell>
+          <cell r="BN377"/>
         </row>
         <row r="378">
           <cell r="A378" t="str">
@@ -13129,12 +14577,19 @@
           <cell r="BC378">
             <v>0</v>
           </cell>
+          <cell r="BF378"/>
+          <cell r="BG378"/>
+          <cell r="BH378"/>
+          <cell r="BI378"/>
+          <cell r="BJ378"/>
           <cell r="BK378">
             <v>0</v>
           </cell>
+          <cell r="BL378"/>
           <cell r="BM378">
             <v>0</v>
           </cell>
+          <cell r="BN378"/>
         </row>
         <row r="379">
           <cell r="A379" t="str">
@@ -13149,12 +14604,19 @@
           <cell r="BC379">
             <v>0</v>
           </cell>
+          <cell r="BF379"/>
+          <cell r="BG379"/>
+          <cell r="BH379"/>
+          <cell r="BI379"/>
+          <cell r="BJ379"/>
           <cell r="BK379">
             <v>0</v>
           </cell>
+          <cell r="BL379"/>
           <cell r="BM379">
             <v>0</v>
           </cell>
+          <cell r="BN379"/>
         </row>
         <row r="380">
           <cell r="A380" t="str">
@@ -13169,12 +14631,19 @@
           <cell r="BC380">
             <v>0</v>
           </cell>
+          <cell r="BF380"/>
+          <cell r="BG380"/>
+          <cell r="BH380"/>
+          <cell r="BI380"/>
+          <cell r="BJ380"/>
           <cell r="BK380">
             <v>0</v>
           </cell>
+          <cell r="BL380"/>
           <cell r="BM380">
             <v>0</v>
           </cell>
+          <cell r="BN380"/>
         </row>
         <row r="381">
           <cell r="A381" t="str">
@@ -13189,12 +14658,19 @@
           <cell r="BC381">
             <v>0</v>
           </cell>
+          <cell r="BF381"/>
+          <cell r="BG381"/>
+          <cell r="BH381"/>
+          <cell r="BI381"/>
+          <cell r="BJ381"/>
           <cell r="BK381">
             <v>0</v>
           </cell>
+          <cell r="BL381"/>
           <cell r="BM381">
             <v>0</v>
           </cell>
+          <cell r="BN381"/>
         </row>
         <row r="382">
           <cell r="A382" t="str">
@@ -13209,12 +14685,19 @@
           <cell r="BC382">
             <v>0</v>
           </cell>
+          <cell r="BF382"/>
+          <cell r="BG382"/>
+          <cell r="BH382"/>
+          <cell r="BI382"/>
+          <cell r="BJ382"/>
           <cell r="BK382">
             <v>3.7</v>
           </cell>
+          <cell r="BL382"/>
           <cell r="BM382">
             <v>78.8</v>
           </cell>
+          <cell r="BN382"/>
         </row>
         <row r="383">
           <cell r="A383" t="str">
@@ -13229,12 +14712,19 @@
           <cell r="BC383">
             <v>0</v>
           </cell>
+          <cell r="BF383"/>
+          <cell r="BG383"/>
+          <cell r="BH383"/>
+          <cell r="BI383"/>
+          <cell r="BJ383"/>
           <cell r="BK383">
             <v>0</v>
           </cell>
+          <cell r="BL383"/>
           <cell r="BM383">
             <v>0</v>
           </cell>
+          <cell r="BN383"/>
         </row>
         <row r="384">
           <cell r="A384" t="str">
@@ -13249,12 +14739,19 @@
           <cell r="BC384">
             <v>0</v>
           </cell>
+          <cell r="BF384"/>
+          <cell r="BG384"/>
+          <cell r="BH384"/>
+          <cell r="BI384"/>
+          <cell r="BJ384"/>
           <cell r="BK384">
             <v>0</v>
           </cell>
+          <cell r="BL384"/>
           <cell r="BM384">
             <v>0</v>
           </cell>
+          <cell r="BN384"/>
         </row>
         <row r="385">
           <cell r="A385" t="str">
@@ -13269,12 +14766,19 @@
           <cell r="BC385">
             <v>0</v>
           </cell>
+          <cell r="BF385"/>
+          <cell r="BG385"/>
+          <cell r="BH385"/>
+          <cell r="BI385"/>
+          <cell r="BJ385"/>
           <cell r="BK385">
             <v>0</v>
           </cell>
+          <cell r="BL385"/>
           <cell r="BM385">
             <v>0</v>
           </cell>
+          <cell r="BN385"/>
         </row>
         <row r="386">
           <cell r="A386" t="str">
@@ -13289,12 +14793,19 @@
           <cell r="BC386">
             <v>0</v>
           </cell>
+          <cell r="BF386"/>
+          <cell r="BG386"/>
+          <cell r="BH386"/>
+          <cell r="BI386"/>
+          <cell r="BJ386"/>
           <cell r="BK386">
             <v>0</v>
           </cell>
+          <cell r="BL386"/>
           <cell r="BM386">
             <v>0</v>
           </cell>
+          <cell r="BN386"/>
         </row>
         <row r="387">
           <cell r="A387" t="str">
@@ -13309,12 +14820,19 @@
           <cell r="BC387">
             <v>0</v>
           </cell>
+          <cell r="BF387"/>
+          <cell r="BG387"/>
+          <cell r="BH387"/>
+          <cell r="BI387"/>
+          <cell r="BJ387"/>
           <cell r="BK387">
             <v>0</v>
           </cell>
+          <cell r="BL387"/>
           <cell r="BM387">
             <v>0</v>
           </cell>
+          <cell r="BN387"/>
         </row>
         <row r="388">
           <cell r="A388" t="str">
@@ -13329,12 +14847,19 @@
           <cell r="BC388">
             <v>0</v>
           </cell>
+          <cell r="BF388"/>
+          <cell r="BG388"/>
+          <cell r="BH388"/>
+          <cell r="BI388"/>
+          <cell r="BJ388"/>
           <cell r="BK388">
             <v>0</v>
           </cell>
+          <cell r="BL388"/>
           <cell r="BM388">
             <v>0</v>
           </cell>
+          <cell r="BN388"/>
         </row>
         <row r="389">
           <cell r="A389" t="str">
@@ -13343,13 +14868,49 @@
           <cell r="B389" t="str">
             <v>zPARAFUSOS</v>
           </cell>
+          <cell r="BA389"/>
+          <cell r="BC389"/>
+          <cell r="BF389"/>
+          <cell r="BG389"/>
+          <cell r="BH389"/>
+          <cell r="BI389"/>
+          <cell r="BJ389"/>
+          <cell r="BK389"/>
+          <cell r="BL389"/>
+          <cell r="BM389"/>
+          <cell r="BN389"/>
+        </row>
+        <row r="390">
+          <cell r="BA390"/>
+          <cell r="BC390"/>
+          <cell r="BF390"/>
+          <cell r="BG390"/>
+          <cell r="BH390"/>
+          <cell r="BI390"/>
+          <cell r="BJ390"/>
+          <cell r="BK390"/>
+          <cell r="BL390"/>
+          <cell r="BM390"/>
+          <cell r="BN390"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="AX2">
+            <v>53666.77</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="B1">
+            <v>44197</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
@@ -13857,10 +15418,10 @@
         <v>67</v>
       </c>
       <c r="Q4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -14045,10 +15606,10 @@
         <v>91</v>
       </c>
       <c r="Q5">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -14233,10 +15794,10 @@
         <v>185</v>
       </c>
       <c r="Q6">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -14424,7 +15985,7 @@
         <v>3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -14612,7 +16173,7 @@
         <v>45</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -14800,7 +16361,7 @@
         <v>89</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -14988,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -15173,10 +16734,10 @@
         <v>751</v>
       </c>
       <c r="Q11">
-        <v>931</v>
+        <v>967</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -15361,10 +16922,10 @@
         <v>561</v>
       </c>
       <c r="Q12">
-        <v>773</v>
+        <v>797</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -15549,10 +17110,10 @@
         <v>588</v>
       </c>
       <c r="Q13">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -15740,7 +17301,7 @@
         <v>2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -16320,10 +17881,10 @@
         <v>431.35</v>
       </c>
       <c r="Q23">
-        <v>262.57</v>
+        <v>259.57</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>120.77</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -16397,10 +17958,10 @@
         <v>545.91</v>
       </c>
       <c r="Q24">
-        <v>942.63</v>
+        <v>942.64</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>169.2</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -16474,10 +18035,10 @@
         <v>573.30999999999995</v>
       </c>
       <c r="Q25">
-        <v>466.3</v>
+        <v>464.84</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>812.1</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -16554,7 +18115,7 @@
         <v>116.2</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -16708,7 +18269,7 @@
         <v>1000.25</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -16859,10 +18420,10 @@
         <v>4907.5</v>
       </c>
       <c r="Q30">
-        <v>401.9</v>
+        <v>396.4</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>413.56</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -16936,10 +18497,10 @@
         <v>2100.16</v>
       </c>
       <c r="Q31">
-        <v>1455.22</v>
+        <v>1483.12</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -17013,10 +18574,10 @@
         <v>530.04</v>
       </c>
       <c r="Q32">
-        <v>903.91</v>
+        <v>899.91</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -17170,7 +18731,7 @@
         <v>319.45</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -17247,7 +18808,7 @@
         <v>367</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>-82.62</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -17937,7 +19498,7 @@
         <v>292.04000000000002</v>
       </c>
       <c r="Q44">
-        <v>3127.4</v>
+        <v>4061.63</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -18242,13 +19803,13 @@
         <v>423.9</v>
       </c>
       <c r="P48">
-        <v>617.37</v>
+        <v>616.16999999999996</v>
       </c>
       <c r="Q48">
-        <v>1020.54</v>
+        <v>1072.21</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>98.98</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -18319,13 +19880,13 @@
         <v>6771.6</v>
       </c>
       <c r="P49">
-        <v>977.28</v>
+        <v>990.35</v>
       </c>
       <c r="Q49">
-        <v>857.01</v>
+        <v>854.72</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>302.19</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -18396,13 +19957,13 @@
         <v>1756.31</v>
       </c>
       <c r="P50">
-        <v>489.21</v>
+        <v>485.44</v>
       </c>
       <c r="Q50">
-        <v>1548.42</v>
+        <v>1628.97</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>283.10000000000002</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -18479,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -18781,13 +20342,13 @@
         <v>6968.14</v>
       </c>
       <c r="P55">
-        <v>742.58</v>
+        <v>1046.25</v>
       </c>
       <c r="Q55">
-        <v>6574.25</v>
+        <v>10177.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1998.12</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -18858,13 +20419,13 @@
         <v>351.6</v>
       </c>
       <c r="P56">
-        <v>1244.1199999999999</v>
+        <v>1242.1600000000001</v>
       </c>
       <c r="Q56">
         <v>200.85</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>546.95000000000005</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -18941,7 +20502,7 @@
         <v>681.73</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>100.7</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -19089,13 +20650,13 @@
         <v>1453.89</v>
       </c>
       <c r="P59">
-        <v>648.23</v>
+        <v>646.28</v>
       </c>
       <c r="Q59">
-        <v>277.56</v>
+        <v>279.95</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>444.2</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -19169,10 +20730,10 @@
         <v>261.3</v>
       </c>
       <c r="Q60">
-        <v>820.93</v>
+        <v>796.53</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>60.7</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -19865,7 +21426,7 @@
         <v>1483.88</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>155.9</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -20096,7 +21657,7 @@
         <v>2721.3</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>134.6</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -20167,13 +21728,13 @@
         <v>2564.08</v>
       </c>
       <c r="P73">
-        <v>922.29</v>
+        <v>917.25</v>
       </c>
       <c r="Q73">
-        <v>702.81</v>
+        <v>698.94</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>176.95</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -20244,13 +21805,13 @@
         <v>3205.26</v>
       </c>
       <c r="P74">
-        <v>1249.54</v>
+        <v>1249.3</v>
       </c>
       <c r="Q74">
-        <v>2628</v>
+        <v>2632.26</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>256.60000000000002</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -20324,10 +21885,10 @@
         <v>1297.72</v>
       </c>
       <c r="Q75">
-        <v>2287.31</v>
+        <v>2282.5300000000002</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2302.44</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -20401,10 +21962,10 @@
         <v>158.19999999999999</v>
       </c>
       <c r="Q76">
-        <v>440.27</v>
+        <v>437.27</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>24.75</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -20555,10 +22116,10 @@
         <v>209.83</v>
       </c>
       <c r="Q78">
-        <v>161.9</v>
+        <v>160.9</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>287.7</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -20632,7 +22193,7 @@
         <v>955.8</v>
       </c>
       <c r="Q79">
-        <v>535.85</v>
+        <v>979.75</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20706,13 +22267,13 @@
         <v>7670.07</v>
       </c>
       <c r="P80">
-        <v>4711.63</v>
+        <v>4682.13</v>
       </c>
       <c r="Q80">
-        <v>9459.86</v>
+        <v>9357.01</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>974.8</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -20783,13 +22344,13 @@
         <v>3574.39</v>
       </c>
       <c r="P81">
-        <v>2169.31</v>
+        <v>2167.81</v>
       </c>
       <c r="Q81">
-        <v>980.38</v>
+        <v>969.48</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2070.15</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -20860,13 +22421,13 @@
         <v>799.37</v>
       </c>
       <c r="P82">
-        <v>599.77</v>
+        <v>597.77</v>
       </c>
       <c r="Q82">
-        <v>722</v>
+        <v>740.95</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>210.38</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -21017,10 +22578,10 @@
         <v>2174.7600000000002</v>
       </c>
       <c r="Q84">
-        <v>1603.37</v>
+        <v>1623.14</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -21091,13 +22652,13 @@
         <v>5356.76</v>
       </c>
       <c r="P85">
-        <v>3386.07</v>
+        <v>3384.07</v>
       </c>
       <c r="Q85">
-        <v>5672.19</v>
+        <v>5618.24</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>236.45</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -22015,7 +23576,7 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>444.48</v>
+        <v>756.7</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -22172,10 +23733,10 @@
         <v>78.959999999999994</v>
       </c>
       <c r="Q99">
-        <v>242.74</v>
+        <v>354.68</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -22477,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>5.56</v>
+        <v>9.4</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -22708,7 +24269,7 @@
         <v>64.069999999999993</v>
       </c>
       <c r="P106">
-        <v>4.96</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -22939,7 +24500,7 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>115.09</v>
+        <v>204.45</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -23712,10 +25273,10 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>111.98</v>
+        <v>215.76</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>3706.4</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24017,13 +25578,13 @@
         <v>203.03</v>
       </c>
       <c r="P123">
-        <v>21.49</v>
+        <v>32.1</v>
       </c>
       <c r="Q123">
-        <v>265.47000000000003</v>
+        <v>299.44</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>21.73</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -24094,13 +25655,13 @@
         <v>540.03</v>
       </c>
       <c r="P124">
-        <v>215.71</v>
+        <v>251.76</v>
       </c>
       <c r="Q124">
-        <v>738.36</v>
+        <v>746.44</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>50.06</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -24174,10 +25735,10 @@
         <v>249.25</v>
       </c>
       <c r="Q125">
-        <v>1605.65</v>
+        <v>1632.36</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>678.65</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -24254,7 +25815,7 @@
         <v>-20.85</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -24559,10 +26120,10 @@
         <v>345.6</v>
       </c>
       <c r="Q130">
-        <v>895.76</v>
+        <v>894.16</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -24716,7 +26277,7 @@
         <v>264.05</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -24864,13 +26425,13 @@
         <v>347.7</v>
       </c>
       <c r="P134">
-        <v>234.83</v>
+        <v>250.45</v>
       </c>
       <c r="Q134">
-        <v>-32.08</v>
+        <v>-106.6</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>116.1</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -24944,10 +26505,10 @@
         <v>1925.14</v>
       </c>
       <c r="Q135">
-        <v>2126.4299999999998</v>
+        <v>2487.37</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>89.06</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -25942,13 +27503,13 @@
         <v>449.41</v>
       </c>
       <c r="P148">
-        <v>480.84</v>
+        <v>476.84</v>
       </c>
       <c r="Q148">
-        <v>917.97</v>
+        <v>912.57</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>46.66</v>
       </c>
       <c r="S148">
         <v>0</v>
@@ -26019,13 +27580,13 @@
         <v>1131.74</v>
       </c>
       <c r="P149">
-        <v>346.03</v>
+        <v>344.03</v>
       </c>
       <c r="Q149">
-        <v>922.38</v>
+        <v>915.93</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>161.91</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -26096,13 +27657,13 @@
         <v>989.68</v>
       </c>
       <c r="P150">
-        <v>579.89</v>
+        <v>574.16</v>
       </c>
       <c r="Q150">
-        <v>1441.04</v>
+        <v>1449.28</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>215.74</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -26179,7 +27740,7 @@
         <v>9.85</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -26333,7 +27894,7 @@
         <v>63.65</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="S153">
         <v>0</v>
@@ -26484,10 +28045,10 @@
         <v>299.39999999999998</v>
       </c>
       <c r="Q155">
-        <v>626.65</v>
+        <v>593.05999999999995</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>307.10000000000002</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -26561,10 +28122,10 @@
         <v>199.5</v>
       </c>
       <c r="Q156">
-        <v>1196.1300000000001</v>
+        <v>1173.93</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -26641,7 +28202,7 @@
         <v>222.95</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -26789,13 +28350,13 @@
         <v>332.2</v>
       </c>
       <c r="P159">
-        <v>478.45</v>
+        <v>478.25</v>
       </c>
       <c r="Q159">
-        <v>193.25</v>
+        <v>187.25</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>240.6</v>
       </c>
       <c r="S159">
         <v>0</v>
@@ -26872,7 +28433,7 @@
         <v>129.4</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>146.02000000000001</v>
       </c>
       <c r="S160">
         <v>0</v>
@@ -27950,7 +29511,7 @@
         <v>0.01</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -29487,10 +31048,10 @@
         <v>24138.79</v>
       </c>
       <c r="Q194">
-        <v>14178.59</v>
+        <v>14143.75</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>381.3</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -29715,10 +31276,10 @@
         <v>9643.9500000000007</v>
       </c>
       <c r="P197">
-        <v>5711.04</v>
+        <v>5707.04</v>
       </c>
       <c r="Q197">
-        <v>8949.08</v>
+        <v>8904.39</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -29792,13 +31353,13 @@
         <v>7099.57</v>
       </c>
       <c r="P198">
-        <v>9333.11</v>
+        <v>9340.02</v>
       </c>
       <c r="Q198">
-        <v>7210.03</v>
+        <v>7391.75</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2025.52</v>
       </c>
       <c r="S198">
         <v>0</v>
@@ -29869,13 +31430,13 @@
         <v>10437.030000000001</v>
       </c>
       <c r="P199">
-        <v>9442.14</v>
+        <v>9458.65</v>
       </c>
       <c r="Q199">
-        <v>9124.7999999999993</v>
+        <v>9070.18</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>4117.1000000000004</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -29946,13 +31507,13 @@
         <v>14032.28</v>
       </c>
       <c r="P200">
-        <v>15207.07</v>
+        <v>15201.68</v>
       </c>
       <c r="Q200">
-        <v>24610.58</v>
+        <v>24947.91</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>5378.34</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -30026,10 +31587,10 @@
         <v>1139.6099999999999</v>
       </c>
       <c r="Q201">
-        <v>1207.5999999999999</v>
+        <v>1240.83</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>306.3</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -30180,10 +31741,10 @@
         <v>5217.09</v>
       </c>
       <c r="Q203">
-        <v>2077.17</v>
+        <v>2115.17</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>509.28</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -30254,13 +31815,13 @@
         <v>2807.35</v>
       </c>
       <c r="P204">
-        <v>3033.37</v>
+        <v>3028.4</v>
       </c>
       <c r="Q204">
         <v>1065.5</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>1075.7</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -30331,13 +31892,13 @@
         <v>153570.17000000001</v>
       </c>
       <c r="P205">
-        <v>106807.48</v>
+        <v>106816.7</v>
       </c>
       <c r="Q205">
-        <v>147588.69</v>
+        <v>161839.26999999999</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>51094.68</v>
       </c>
       <c r="S205">
         <v>0</v>
@@ -30408,13 +31969,13 @@
         <v>11988.76</v>
       </c>
       <c r="P206">
-        <v>8614.8700000000008</v>
+        <v>8603.7199999999993</v>
       </c>
       <c r="Q206">
-        <v>14286.32</v>
+        <v>14227.76</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>1631.13</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -30488,10 +32049,10 @@
         <v>785.13</v>
       </c>
       <c r="Q207">
-        <v>3428.8</v>
+        <v>3427.8</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>1036.5999999999999</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -30568,7 +32129,7 @@
         <v>3199.8</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>1120.8599999999999</v>
       </c>
       <c r="S208">
         <v>0</v>
@@ -30639,13 +32200,13 @@
         <v>8450.7999999999993</v>
       </c>
       <c r="P209">
-        <v>5259.18</v>
+        <v>5748.16</v>
       </c>
       <c r="Q209">
-        <v>7557.23</v>
+        <v>7827.09</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>3034.22</v>
       </c>
       <c r="S209">
         <v>0</v>
@@ -30716,13 +32277,13 @@
         <v>20216.419999999998</v>
       </c>
       <c r="P210">
-        <v>29048.79</v>
+        <v>29036.69</v>
       </c>
       <c r="Q210">
-        <v>33128.39</v>
+        <v>32672.89</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>4535.0600000000004</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -31412,10 +32973,10 @@
         <v>6215.59</v>
       </c>
       <c r="Q219">
-        <v>35040.86</v>
+        <v>35110.46</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>13911.98</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -31640,13 +33201,13 @@
         <v>2431.15</v>
       </c>
       <c r="P222">
-        <v>6598.1</v>
+        <v>6561.35</v>
       </c>
       <c r="Q222">
-        <v>5147.7</v>
+        <v>5271.2</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2526.8000000000002</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -31720,10 +33281,10 @@
         <v>4660.79</v>
       </c>
       <c r="Q223">
-        <v>4324.5200000000004</v>
+        <v>4412.3500000000004</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>746.93</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -31794,13 +33355,13 @@
         <v>5884.89</v>
       </c>
       <c r="P224">
-        <v>3829.06</v>
+        <v>3818.71</v>
       </c>
       <c r="Q224">
-        <v>8760.93</v>
+        <v>8931.69</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>1261.69</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -31871,13 +33432,13 @@
         <v>5304.37</v>
       </c>
       <c r="P225">
-        <v>11295.1</v>
+        <v>11294.1</v>
       </c>
       <c r="Q225">
-        <v>8340.2199999999993</v>
+        <v>8474.06</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>1164.8800000000001</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -31951,10 +33512,10 @@
         <v>399.66</v>
       </c>
       <c r="Q226">
-        <v>1443.59</v>
+        <v>1440.59</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>242.3</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -32102,13 +33663,13 @@
         <v>2586.27</v>
       </c>
       <c r="P228">
-        <v>3167.3</v>
+        <v>3165.3</v>
       </c>
       <c r="Q228">
-        <v>1511.5</v>
+        <v>1611.7</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>327.8</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -32185,7 +33746,7 @@
         <v>2492.86</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>868.6</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -32256,13 +33817,13 @@
         <v>18556.27</v>
       </c>
       <c r="P230">
-        <v>31452.35</v>
+        <v>31472.85</v>
       </c>
       <c r="Q230">
-        <v>41527.599999999999</v>
+        <v>41501.870000000003</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>14689.75</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -32336,10 +33897,10 @@
         <v>5543.11</v>
       </c>
       <c r="Q231">
-        <v>9476.17</v>
+        <v>9571.82</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>1110.22</v>
       </c>
       <c r="S231">
         <v>0</v>
@@ -32413,10 +33974,10 @@
         <v>2358.44</v>
       </c>
       <c r="Q232">
-        <v>2064.59</v>
+        <v>2105.9899999999998</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>346.8</v>
       </c>
       <c r="S232">
         <v>0</v>
@@ -32493,7 +34054,7 @@
         <v>4342.83</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>489.9</v>
       </c>
       <c r="S233">
         <v>0</v>
@@ -32564,13 +34125,13 @@
         <v>2024.05</v>
       </c>
       <c r="P234">
-        <v>3903.29</v>
+        <v>3863.39</v>
       </c>
       <c r="Q234">
-        <v>4283.58</v>
+        <v>4788.7299999999996</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>1423.58</v>
       </c>
       <c r="S234">
         <v>0</v>
@@ -32641,13 +34202,13 @@
         <v>10644.94</v>
       </c>
       <c r="P235">
-        <v>9683.18</v>
+        <v>9586.25</v>
       </c>
       <c r="Q235">
-        <v>11938.2</v>
+        <v>12439.75</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>5618.29</v>
       </c>
       <c r="S235">
         <v>0</v>
@@ -33334,13 +34895,13 @@
         <v>3516.16</v>
       </c>
       <c r="P244">
-        <v>4185.03</v>
+        <v>4190.76</v>
       </c>
       <c r="Q244">
-        <v>7223.84</v>
+        <v>7216.1</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>1818.87</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -33568,10 +35129,10 @@
         <v>4026.26</v>
       </c>
       <c r="Q247">
-        <v>162.44999999999999</v>
+        <v>316.77</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>170.7</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -33642,13 +35203,13 @@
         <v>4351.96</v>
       </c>
       <c r="P248">
-        <v>3153.16</v>
+        <v>3143.16</v>
       </c>
       <c r="Q248">
-        <v>2023.52</v>
+        <v>2066.3200000000002</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>886.46</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -33719,13 +35280,13 @@
         <v>6772.9</v>
       </c>
       <c r="P249">
-        <v>10828.47</v>
+        <v>10817.69</v>
       </c>
       <c r="Q249">
-        <v>2343.33</v>
+        <v>2638.73</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>1259.94</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -33796,13 +35357,13 @@
         <v>10251.93</v>
       </c>
       <c r="P250">
-        <v>10305.14</v>
+        <v>10301.9</v>
       </c>
       <c r="Q250">
-        <v>3386.84</v>
+        <v>3844.17</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>1835.89</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -33873,13 +35434,13 @@
         <v>1478.26</v>
       </c>
       <c r="P251">
-        <v>698.55</v>
+        <v>697.6</v>
       </c>
       <c r="Q251">
         <v>210.15</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>273.2</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -34027,13 +35588,13 @@
         <v>3188.47</v>
       </c>
       <c r="P253">
-        <v>1426.9</v>
+        <v>1425.9</v>
       </c>
       <c r="Q253">
-        <v>314.25</v>
+        <v>312.61</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2405.6999999999998</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -34107,10 +35668,10 @@
         <v>588.35</v>
       </c>
       <c r="Q254">
-        <v>125.9</v>
+        <v>115.9</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>161.9</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -34181,13 +35742,13 @@
         <v>29857.48</v>
       </c>
       <c r="P255">
-        <v>24549.61</v>
+        <v>24550.31</v>
       </c>
       <c r="Q255">
-        <v>16771.03</v>
+        <v>16715.03</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>5321.42</v>
       </c>
       <c r="S255">
         <v>0</v>
@@ -34261,10 +35822,10 @@
         <v>5359.38</v>
       </c>
       <c r="Q256">
-        <v>4042.43</v>
+        <v>4180.05</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>3333.23</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -34338,10 +35899,10 @@
         <v>1671.86</v>
       </c>
       <c r="Q257">
-        <v>438.2</v>
+        <v>443.1</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>165.7</v>
       </c>
       <c r="S257">
         <v>0</v>
@@ -34418,7 +35979,7 @@
         <v>1259.8</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -34489,13 +36050,13 @@
         <v>4746.4399999999996</v>
       </c>
       <c r="P259">
-        <v>4179.3599999999997</v>
+        <v>4177.3599999999997</v>
       </c>
       <c r="Q259">
-        <v>1815.35</v>
+        <v>1892.34</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="S259">
         <v>0</v>
@@ -34569,10 +36130,10 @@
         <v>22340.61</v>
       </c>
       <c r="Q260">
-        <v>5642.79</v>
+        <v>5960.89</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2778.15</v>
       </c>
       <c r="S260">
         <v>0</v>
@@ -37118,15 +38679,15 @@
       </c>
       <c r="P299">
         <f t="shared" si="0"/>
-        <v>461561.68999999977</v>
+        <v>462585.31999999983</v>
       </c>
       <c r="Q299">
         <f t="shared" si="0"/>
-        <v>529713.63000000012</v>
+        <v>552857.35000000009</v>
       </c>
       <c r="R299">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>162546.64000000004</v>
       </c>
       <c r="S299">
         <f t="shared" si="0"/>
